--- a/research/traditional_assets/database/data/turkey/turkey_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_telecom_wireless.xlsx
@@ -650,10 +650,10 @@
         <v>0.7594327000267594</v>
       </c>
       <c r="X2">
-        <v>0.1385267556197375</v>
+        <v>0.1385279426424763</v>
       </c>
       <c r="Y2">
-        <v>0.620905944407022</v>
+        <v>0.6209047573842832</v>
       </c>
       <c r="Z2">
         <v>1.065433169509492</v>
@@ -662,10 +662,10 @@
         <v>0.1163149272429411</v>
       </c>
       <c r="AB2">
-        <v>0.1183925977501974</v>
+        <v>0.1183933655875272</v>
       </c>
       <c r="AC2">
-        <v>-0.002077670507256296</v>
+        <v>-0.002078438344586042</v>
       </c>
       <c r="AD2">
         <v>3121.3</v>
@@ -787,10 +787,10 @@
         <v>0.7594327000267594</v>
       </c>
       <c r="X3">
-        <v>0.1385267556197375</v>
+        <v>0.1385279426424763</v>
       </c>
       <c r="Y3">
-        <v>0.620905944407022</v>
+        <v>0.6209047573842832</v>
       </c>
       <c r="Z3">
         <v>1.065433169509492</v>
@@ -799,10 +799,10 @@
         <v>0.1163149272429411</v>
       </c>
       <c r="AB3">
-        <v>0.1183925977501974</v>
+        <v>0.1183933655875272</v>
       </c>
       <c r="AC3">
-        <v>-0.002077670507256296</v>
+        <v>-0.002078438344586042</v>
       </c>
       <c r="AD3">
         <v>3121.3</v>
@@ -1157,13 +1157,13 @@
         <v>5717.4</v>
       </c>
       <c r="L2">
-        <v>9507.709074938481</v>
+        <v>9507.69319925502</v>
       </c>
       <c r="M2">
         <v>6469.6</v>
       </c>
       <c r="N2">
-        <v>7138.60907493847</v>
+        <v>7138.59319925502</v>
       </c>
       <c r="O2">
         <v>3121.3</v>
@@ -1172,16 +1172,16 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.118392597750197</v>
+        <v>0.118393365587527</v>
       </c>
       <c r="R2">
-        <v>0.111589436776061</v>
+        <v>0.11159027896618</v>
       </c>
       <c r="S2">
         <v>0.0815121203198611</v>
       </c>
       <c r="T2">
-        <v>0.0722121203198612</v>
+        <v>0.07116212031986111</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.138526755619738</v>
+        <v>0.138527942642476</v>
       </c>
       <c r="X2">
-        <v>0.111589436776061</v>
+        <v>0.11159027896618</v>
       </c>
       <c r="Y2">
         <v>0.8967500756868459</v>
@@ -1236,7 +1236,7 @@
         <v>5717.4</v>
       </c>
       <c r="AK2">
-        <v>0.1034031199258227</v>
+        <v>0.1034044436198718</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1115894367760606</v>
+        <v>0.1115902789661804</v>
       </c>
       <c r="C2">
-        <v>9507.709074938475</v>
+        <v>9507.693199255018</v>
       </c>
       <c r="D2">
-        <v>7138.609074938475</v>
+        <v>7138.593199255018</v>
       </c>
       <c r="E2">
         <v>-3121.3</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1115894367760606</v>
+        <v>0.1115902789661804</v>
       </c>
       <c r="T2">
         <v>0.6362422799549506</v>
       </c>
       <c r="U2">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1116890843873191</v>
+        <v>0.1116794244719635</v>
       </c>
       <c r="C3">
-        <v>9408.525971932335</v>
+        <v>9409.646529237736</v>
       </c>
       <c r="D3">
-        <v>7127.812971932335</v>
+        <v>7128.933529237736</v>
       </c>
       <c r="E3">
         <v>-3032.913</v>
@@ -1539,37 +1539,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M3">
-        <v>8.51015023828209</v>
+        <v>8.386408438282091</v>
       </c>
       <c r="N3">
-        <v>504.9565164283846</v>
+        <v>505.0802582283846</v>
       </c>
       <c r="O3">
-        <v>126.2391291070961</v>
+        <v>126.2700645570961</v>
       </c>
       <c r="P3">
-        <v>378.7173873212885</v>
+        <v>378.8101936712885</v>
       </c>
       <c r="Q3">
-        <v>470.7173873212885</v>
+        <v>470.8101936712885</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1120878416001217</v>
+        <v>0.1120886901704696</v>
       </c>
       <c r="T3">
         <v>0.6410622972273367</v>
       </c>
       <c r="U3">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>60.33579341018991</v>
+        <v>61.22605051320962</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1117887319985775</v>
+        <v>0.1117685699777467</v>
       </c>
       <c r="C4">
-        <v>9309.375474670933</v>
+        <v>9311.625966082238</v>
       </c>
       <c r="D4">
-        <v>7117.049474670933</v>
+        <v>7119.299966082237</v>
       </c>
       <c r="E4">
         <v>-2944.526</v>
@@ -1621,37 +1621,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M4">
-        <v>17.02030047656418</v>
+        <v>16.77281687656418</v>
       </c>
       <c r="N4">
-        <v>496.4463661901025</v>
+        <v>496.6938497901025</v>
       </c>
       <c r="O4">
-        <v>124.1115915475256</v>
+        <v>124.1734624475256</v>
       </c>
       <c r="P4">
-        <v>372.3347746425769</v>
+        <v>372.5203873425769</v>
       </c>
       <c r="Q4">
-        <v>464.3347746425769</v>
+        <v>464.5203873425769</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1125964179512044</v>
+        <v>0.1125972730319892</v>
       </c>
       <c r="T4">
         <v>0.6459806821991592</v>
       </c>
       <c r="U4">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>30.16789670509496</v>
+        <v>30.61302525660481</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.111888379609836</v>
+        <v>0.1118577154835298</v>
       </c>
       <c r="C5">
-        <v>9210.257435666104</v>
+        <v>9213.631404094169</v>
       </c>
       <c r="D5">
-        <v>7106.318435666105</v>
+        <v>7109.692404094169</v>
       </c>
       <c r="E5">
         <v>-2856.139</v>
@@ -1703,37 +1703,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M5">
-        <v>25.53045071484627</v>
+        <v>25.15922531484627</v>
       </c>
       <c r="N5">
-        <v>487.9362159518204</v>
+        <v>488.3074413518204</v>
       </c>
       <c r="O5">
-        <v>121.9840539879551</v>
+        <v>122.0768603379551</v>
       </c>
       <c r="P5">
-        <v>365.9521619638653</v>
+        <v>366.2305810138653</v>
       </c>
       <c r="Q5">
-        <v>457.9521619638653</v>
+        <v>458.2305810138653</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1131154804126187</v>
+        <v>0.1131163421380763</v>
       </c>
       <c r="T5">
         <v>0.6510004771704004</v>
       </c>
       <c r="U5">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>20.11193113672997</v>
+        <v>20.40868350440321</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1119880272210944</v>
+        <v>0.111946860989313</v>
       </c>
       <c r="C6">
-        <v>9111.171708317868</v>
+        <v>9115.662738148931</v>
       </c>
       <c r="D6">
-        <v>7095.619708317869</v>
+        <v>7100.110738148931</v>
       </c>
       <c r="E6">
         <v>-2767.752</v>
@@ -1785,37 +1785,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M6">
-        <v>34.04060095312836</v>
+        <v>33.54563375312836</v>
       </c>
       <c r="N6">
-        <v>479.4260657135383</v>
+        <v>479.9210329135383</v>
       </c>
       <c r="O6">
-        <v>119.8565164283846</v>
+        <v>119.9802582283846</v>
       </c>
       <c r="P6">
-        <v>359.5695492851538</v>
+        <v>359.9407746851538</v>
       </c>
       <c r="Q6">
-        <v>451.5695492851538</v>
+        <v>451.9407746851538</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1136453566753125</v>
+        <v>0.1136462251838735</v>
       </c>
       <c r="T6">
         <v>0.6561248512035428</v>
       </c>
       <c r="U6">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>15.08394835254748</v>
+        <v>15.30651262830241</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1120876748323529</v>
+        <v>0.1120360064950962</v>
       </c>
       <c r="C7">
-        <v>9012.118146907766</v>
+        <v>9017.719863687873</v>
       </c>
       <c r="D7">
-        <v>7084.953146907765</v>
+        <v>7090.554863687873</v>
       </c>
       <c r="E7">
         <v>-2679.365</v>
@@ -1867,37 +1867,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M7">
-        <v>42.55075119141046</v>
+        <v>41.93204219141045</v>
       </c>
       <c r="N7">
-        <v>470.9159154752563</v>
+        <v>471.5346244752562</v>
       </c>
       <c r="O7">
-        <v>117.7289788688141</v>
+        <v>117.8836561188141</v>
       </c>
       <c r="P7">
-        <v>353.1869366064422</v>
+        <v>353.6509683564421</v>
       </c>
       <c r="Q7">
-        <v>445.1869366064422</v>
+        <v>445.6509683564421</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1141863882277472</v>
+        <v>0.1141872636622138</v>
       </c>
       <c r="T7">
         <v>0.6613571067952776</v>
       </c>
       <c r="U7">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>12.06715868203798</v>
+        <v>12.24521010264192</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1121873224436113</v>
+        <v>0.1121251520008793</v>
       </c>
       <c r="C8">
-        <v>8913.09660659222</v>
+        <v>8919.802676714486</v>
       </c>
       <c r="D8">
-        <v>7074.318606592221</v>
+        <v>7081.024676714486</v>
       </c>
       <c r="E8">
         <v>-2590.978</v>
@@ -1949,37 +1949,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M8">
-        <v>51.06090142969254</v>
+        <v>50.31845062969253</v>
       </c>
       <c r="N8">
-        <v>462.4057652369742</v>
+        <v>463.1482160369742</v>
       </c>
       <c r="O8">
-        <v>115.6014413092435</v>
+        <v>115.7870540092435</v>
       </c>
       <c r="P8">
-        <v>346.8043239277306</v>
+        <v>347.3611620277306</v>
       </c>
       <c r="Q8">
-        <v>438.8043239277306</v>
+        <v>439.3611620277306</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1147389310898082</v>
+        <v>0.1147398135975401</v>
       </c>
       <c r="T8">
         <v>0.6667006869740706</v>
       </c>
       <c r="U8">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>10.05596556836499</v>
+        <v>10.20434175220161</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1122869700548698</v>
+        <v>0.1122142975066625</v>
       </c>
       <c r="C9">
-        <v>8814.106943396013</v>
+        <v>8821.911073790616</v>
       </c>
       <c r="D9">
-        <v>7063.715943396014</v>
+        <v>7071.520073790616</v>
       </c>
       <c r="E9">
         <v>-2502.591</v>
@@ -2031,37 +2031,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M9">
-        <v>59.57105166797464</v>
+        <v>58.70485906797462</v>
       </c>
       <c r="N9">
-        <v>453.8956149986921</v>
+        <v>454.7618075986921</v>
       </c>
       <c r="O9">
-        <v>113.473903749673</v>
+        <v>113.690451899673</v>
       </c>
       <c r="P9">
-        <v>340.421711249019</v>
+        <v>341.0713556990191</v>
       </c>
       <c r="Q9">
-        <v>432.421711249019</v>
+        <v>433.0713556990191</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.115303356594064</v>
+        <v>0.1153042463271744</v>
       </c>
       <c r="T9">
         <v>0.6721591828556333</v>
       </c>
       <c r="U9">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>8.619399058598558</v>
+        <v>8.746578644744233</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1124526176661283</v>
+        <v>0.1123934430124457</v>
       </c>
       <c r="C10">
-        <v>8708.164928850401</v>
+        <v>8714.500713787464</v>
       </c>
       <c r="D10">
-        <v>7046.160928850401</v>
+        <v>7052.496713787463</v>
       </c>
       <c r="E10">
         <v>-2414.204</v>
@@ -2113,37 +2113,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M10">
-        <v>68.85900750625672</v>
+        <v>68.15191150625672</v>
       </c>
       <c r="N10">
-        <v>444.60765916041</v>
+        <v>445.31475516041</v>
       </c>
       <c r="O10">
-        <v>111.1519147901025</v>
+        <v>111.3286887901025</v>
       </c>
       <c r="P10">
-        <v>333.4557443703075</v>
+        <v>333.9860663703075</v>
       </c>
       <c r="Q10">
-        <v>425.4557443703075</v>
+        <v>425.9860663703075</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1158800522179776</v>
+        <v>0.11588094933354</v>
       </c>
       <c r="T10">
         <v>0.6777363416911432</v>
       </c>
       <c r="U10">
-        <v>0.09738282709314819</v>
+        <v>0.09638282709314819</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.07303712031986115</v>
+        <v>0.07228712031986115</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.456782856186415</v>
+        <v>7.534149157643621</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1127090152773867</v>
+        <v>0.1124938385182288</v>
       </c>
       <c r="C11">
-        <v>8592.776801674787</v>
+        <v>8615.497456118905</v>
       </c>
       <c r="D11">
-        <v>7019.159801674787</v>
+        <v>7041.880456118905</v>
       </c>
       <c r="E11">
         <v>-2325.817</v>
@@ -2195,45 +2195,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M11">
-        <v>79.21644604453881</v>
+        <v>76.6709004445388</v>
       </c>
       <c r="N11">
-        <v>434.2502206221279</v>
+        <v>436.7957662221279</v>
       </c>
       <c r="O11">
-        <v>108.562555155532</v>
+        <v>109.198941555532</v>
       </c>
       <c r="P11">
-        <v>325.6876654665959</v>
+        <v>327.5968246665959</v>
       </c>
       <c r="Q11">
-        <v>417.6876654665959</v>
+        <v>419.5968246665959</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1164694224709882</v>
+        <v>0.1164703271312542</v>
       </c>
       <c r="T11">
         <v>0.6834360754461145</v>
       </c>
       <c r="U11">
-        <v>0.0995828270931482</v>
+        <v>0.09638282709314819</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.07468712031986115</v>
+        <v>0.07228712031986115</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.481819019979439</v>
+        <v>6.697021473460998</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1128334128886452</v>
+        <v>0.112721734024012</v>
       </c>
       <c r="C12">
-        <v>8491.363958669894</v>
+        <v>8503.130011923662</v>
       </c>
       <c r="D12">
-        <v>7006.133958669895</v>
+        <v>7017.900011923663</v>
       </c>
       <c r="E12">
         <v>-2237.43</v>
@@ -2277,37 +2277,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M12">
-        <v>88.01827338282091</v>
+        <v>86.69246838282091</v>
       </c>
       <c r="N12">
-        <v>425.4483932838458</v>
+        <v>426.7741982838458</v>
       </c>
       <c r="O12">
-        <v>106.3620983209615</v>
+        <v>106.6935495709615</v>
       </c>
       <c r="P12">
-        <v>319.0862949628844</v>
+        <v>320.0806487128843</v>
       </c>
       <c r="Q12">
-        <v>411.0862949628844</v>
+        <v>412.0806487128843</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1170718898407323</v>
+        <v>0.1170728022133621</v>
       </c>
       <c r="T12">
         <v>0.6892624699511964</v>
       </c>
       <c r="U12">
-        <v>0.0995828270931482</v>
+        <v>0.09808282709314819</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.07468712031986115</v>
+        <v>0.07356212031986115</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.833637117981495</v>
+        <v>5.922852079828608</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1130815604999036</v>
+        <v>0.1129008795297951</v>
       </c>
       <c r="C13">
-        <v>8377.136960413563</v>
+        <v>8396.006666647987</v>
       </c>
       <c r="D13">
-        <v>6980.293960413564</v>
+        <v>6999.163666647987</v>
       </c>
       <c r="E13">
         <v>-2149.043</v>
@@ -2359,37 +2359,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M13">
-        <v>98.27848622110299</v>
+        <v>96.13952082110299</v>
       </c>
       <c r="N13">
-        <v>415.1881804455637</v>
+        <v>417.3271458455637</v>
       </c>
       <c r="O13">
-        <v>103.7970451113909</v>
+        <v>104.3317864613909</v>
       </c>
       <c r="P13">
-        <v>311.3911353341728</v>
+        <v>312.9953593841727</v>
       </c>
       <c r="Q13">
-        <v>403.3911353341728</v>
+        <v>404.9953593841727</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.117687895803055</v>
+        <v>0.11768881606136</v>
       </c>
       <c r="T13">
         <v>0.6952197946698758</v>
       </c>
       <c r="U13">
-        <v>0.1010828270931482</v>
+        <v>0.09888282709314819</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.07581212031986115</v>
+        <v>0.07416212031986114</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.224609031029335</v>
+        <v>5.340849031504209</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1132172081111621</v>
+        <v>0.1130200250355783</v>
       </c>
       <c r="C14">
-        <v>8274.705175289106</v>
+        <v>8295.213856107444</v>
       </c>
       <c r="D14">
-        <v>6966.249175289106</v>
+        <v>6986.757856107445</v>
       </c>
       <c r="E14">
         <v>-2060.656</v>
@@ -2441,37 +2441,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M14">
-        <v>107.2128940593851</v>
+        <v>104.8794772593851</v>
       </c>
       <c r="N14">
-        <v>406.2537726072816</v>
+        <v>408.5871894072816</v>
       </c>
       <c r="O14">
-        <v>101.5634431518204</v>
+        <v>102.1467973518204</v>
       </c>
       <c r="P14">
-        <v>304.6903294554612</v>
+        <v>306.4403920554612</v>
       </c>
       <c r="Q14">
-        <v>396.6903294554612</v>
+        <v>398.4403920554612</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.118317901900885</v>
+        <v>0.1183188302240852</v>
       </c>
       <c r="T14">
         <v>0.7013125131321615</v>
       </c>
       <c r="U14">
-        <v>0.1010828270931482</v>
+        <v>0.09888282709314819</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.07581212031986115</v>
+        <v>0.07416212031986114</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>4.789224945110224</v>
+        <v>4.89577827887886</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1133528557224206</v>
+        <v>0.1131391705413614</v>
       </c>
       <c r="C15">
-        <v>8172.329794635859</v>
+        <v>8194.464945619713</v>
       </c>
       <c r="D15">
-        <v>6952.260794635859</v>
+        <v>6974.395945619714</v>
       </c>
       <c r="E15">
         <v>-1972.269</v>
@@ -2523,37 +2523,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M15">
-        <v>116.1473018976672</v>
+        <v>113.6194336976672</v>
       </c>
       <c r="N15">
-        <v>397.3193647689995</v>
+        <v>399.8472329689995</v>
       </c>
       <c r="O15">
-        <v>99.32984119224987</v>
+        <v>99.96180824224987</v>
       </c>
       <c r="P15">
-        <v>297.9895235767496</v>
+        <v>299.8854247267496</v>
       </c>
       <c r="Q15">
-        <v>389.9895235767496</v>
+        <v>391.8854247267496</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1189623908975156</v>
+        <v>0.1189633274710109</v>
       </c>
       <c r="T15">
         <v>0.707545294087833</v>
       </c>
       <c r="U15">
-        <v>0.1010828270931482</v>
+        <v>0.09888282709314819</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.07581212031986115</v>
+        <v>0.07416212031986114</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.42082302625559</v>
+        <v>4.519179949734331</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1136355033336791</v>
+        <v>0.1133633160471446</v>
       </c>
       <c r="C16">
-        <v>8054.97507404884</v>
+        <v>8082.93995301923</v>
       </c>
       <c r="D16">
-        <v>6923.293074048839</v>
+        <v>6951.25795301923</v>
       </c>
       <c r="E16">
         <v>-1883.882</v>
@@ -2605,37 +2605,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M16">
-        <v>126.8140949359493</v>
+        <v>123.5968081359493</v>
       </c>
       <c r="N16">
-        <v>386.6525717307175</v>
+        <v>389.8698585307175</v>
       </c>
       <c r="O16">
-        <v>96.66314293267936</v>
+        <v>97.46746463267937</v>
       </c>
       <c r="P16">
-        <v>289.9894287980381</v>
+        <v>292.4023938980381</v>
       </c>
       <c r="Q16">
-        <v>381.9894287980381</v>
+        <v>384.4023938980381</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1196218680103471</v>
+        <v>0.1196228130260047</v>
       </c>
       <c r="T16">
         <v>0.7139230234378225</v>
       </c>
       <c r="U16">
-        <v>0.1024828270931482</v>
+        <v>0.09988282709314819</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.07686212031986114</v>
+        <v>0.07491212031986114</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.0489715825832</v>
+        <v>4.154368340174962</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1137816509449375</v>
+        <v>0.1134899615529278</v>
       </c>
       <c r="C17">
-        <v>7951.704311581318</v>
+        <v>7981.547397112674</v>
       </c>
       <c r="D17">
-        <v>6908.409311581318</v>
+        <v>6938.252397112674</v>
       </c>
       <c r="E17">
         <v>-1795.495</v>
@@ -2687,37 +2687,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M17">
-        <v>135.8722445742314</v>
+        <v>132.4251515742313</v>
       </c>
       <c r="N17">
-        <v>377.5944220924354</v>
+        <v>381.0415150924354</v>
       </c>
       <c r="O17">
-        <v>94.39860552310884</v>
+        <v>95.26037877310884</v>
       </c>
       <c r="P17">
-        <v>283.1958165693266</v>
+        <v>285.7811363193265</v>
       </c>
       <c r="Q17">
-        <v>375.1958165693266</v>
+        <v>377.7811363193265</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1202968622317157</v>
+        <v>0.1202978158881748</v>
       </c>
       <c r="T17">
         <v>0.7204508170078118</v>
       </c>
       <c r="U17">
-        <v>0.1024828270931482</v>
+        <v>0.09988282709314819</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.07686212031986114</v>
+        <v>0.07491212031986114</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.77904014374432</v>
+        <v>3.877410450829964</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1139277985561959</v>
+        <v>0.1136166070587109</v>
       </c>
       <c r="C18">
-        <v>7848.497406346155</v>
+        <v>7880.203416187293</v>
       </c>
       <c r="D18">
-        <v>6893.589406346155</v>
+        <v>6925.295416187294</v>
       </c>
       <c r="E18">
         <v>-1707.108</v>
@@ -2769,37 +2769,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M18">
-        <v>144.9303942125134</v>
+        <v>141.2534950125134</v>
       </c>
       <c r="N18">
-        <v>368.5362724541533</v>
+        <v>372.2131716541533</v>
       </c>
       <c r="O18">
-        <v>92.13406811353832</v>
+        <v>93.05329291353831</v>
       </c>
       <c r="P18">
-        <v>276.402204340615</v>
+        <v>279.1598787406149</v>
       </c>
       <c r="Q18">
-        <v>368.402204340615</v>
+        <v>371.1598787406149</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1209879277440692</v>
+        <v>0.1209888902470633</v>
       </c>
       <c r="T18">
         <v>0.7271340342342293</v>
       </c>
       <c r="U18">
-        <v>0.1024828270931482</v>
+        <v>0.09988282709314819</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.07686212031986114</v>
+        <v>0.07491212031986114</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.5428501347603</v>
+        <v>3.635072297653091</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1140739461674544</v>
+        <v>0.1137432525644941</v>
       </c>
       <c r="C19">
-        <v>7745.353948263841</v>
+        <v>7778.907738613339</v>
       </c>
       <c r="D19">
-        <v>6878.83294826384</v>
+        <v>6912.386738613339</v>
       </c>
       <c r="E19">
         <v>-1618.721</v>
@@ -2851,37 +2851,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M19">
-        <v>153.9885438507955</v>
+        <v>150.0818384507955</v>
       </c>
       <c r="N19">
-        <v>359.4781228158712</v>
+        <v>363.3848282158712</v>
       </c>
       <c r="O19">
-        <v>89.8695307039678</v>
+        <v>90.84620705396779</v>
       </c>
       <c r="P19">
-        <v>269.6085921119034</v>
+        <v>272.5386211619034</v>
       </c>
       <c r="Q19">
-        <v>361.6085921119034</v>
+        <v>364.5386211619034</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1216956454374434</v>
+        <v>0.1216966170001418</v>
       </c>
       <c r="T19">
         <v>0.7339782928395967</v>
       </c>
       <c r="U19">
-        <v>0.1024828270931482</v>
+        <v>0.09988282709314819</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.07686212031986114</v>
+        <v>0.07491212031986114</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.334447185656753</v>
+        <v>3.421244515438203</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1142200937787129</v>
+        <v>0.1138698980702773</v>
       </c>
       <c r="C20">
-        <v>7642.27353075865</v>
+        <v>7677.660094782541</v>
       </c>
       <c r="D20">
-        <v>6864.139530758651</v>
+        <v>6899.526094782542</v>
       </c>
       <c r="E20">
         <v>-1530.334</v>
@@ -2933,37 +2933,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M20">
-        <v>163.0466934890776</v>
+        <v>158.9101818890776</v>
       </c>
       <c r="N20">
-        <v>350.4199731775891</v>
+        <v>354.556484777589</v>
       </c>
       <c r="O20">
-        <v>87.60499329439727</v>
+        <v>88.63912119439726</v>
       </c>
       <c r="P20">
-        <v>262.8149798831918</v>
+        <v>265.9173635831918</v>
       </c>
       <c r="Q20">
-        <v>354.8149798831918</v>
+        <v>357.9173635831918</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.122420624537973</v>
+        <v>0.1224216053813442</v>
       </c>
       <c r="T20">
         <v>0.7409894845816802</v>
       </c>
       <c r="U20">
-        <v>0.1024828270931482</v>
+        <v>0.09988282709314819</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.07686212031986114</v>
+        <v>0.07491212031986114</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.149200119786934</v>
+        <v>3.231175375691636</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1147367413899713</v>
+        <v>0.1139965435760604</v>
       </c>
       <c r="C21">
-        <v>7502.443117269614</v>
+        <v>7576.460217089357</v>
       </c>
       <c r="D21">
-        <v>6812.696117269614</v>
+        <v>6886.713217089357</v>
       </c>
       <c r="E21">
         <v>-1441.947</v>
@@ -3015,45 +3015,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M21">
-        <v>176.4711609273597</v>
+        <v>167.7385253273597</v>
       </c>
       <c r="N21">
-        <v>336.995505739307</v>
+        <v>345.728141339307</v>
       </c>
       <c r="O21">
-        <v>84.24887643482674</v>
+        <v>86.43203533482675</v>
       </c>
       <c r="P21">
-        <v>252.7466293044802</v>
+        <v>259.2961060044802</v>
       </c>
       <c r="Q21">
-        <v>344.7466293044802</v>
+        <v>351.2961060044802</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1231635043570342</v>
+        <v>0.1231644947102306</v>
       </c>
       <c r="T21">
         <v>0.7481737921692476</v>
       </c>
       <c r="U21">
-        <v>0.1050828270931482</v>
+        <v>0.09988282709314819</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.07881212031986115</v>
+        <v>0.07491212031986114</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>2.909635001936794</v>
+        <v>3.06111351381313</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1149023890012298</v>
+        <v>0.1144981890818436</v>
       </c>
       <c r="C22">
-        <v>7397.725179159275</v>
+        <v>7437.785301481355</v>
       </c>
       <c r="D22">
-        <v>6796.365179159276</v>
+        <v>6836.425301481356</v>
       </c>
       <c r="E22">
         <v>-1353.56</v>
@@ -3097,37 +3097,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M22">
-        <v>185.7591167656418</v>
+        <v>180.9862187656418</v>
       </c>
       <c r="N22">
-        <v>327.7075499010249</v>
+        <v>332.4804479010249</v>
       </c>
       <c r="O22">
-        <v>81.92688747525622</v>
+        <v>83.12011197525622</v>
       </c>
       <c r="P22">
-        <v>245.7806624257687</v>
+        <v>249.3603359257687</v>
       </c>
       <c r="Q22">
-        <v>337.7806624257687</v>
+        <v>341.3603359257687</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.123924956171572</v>
+        <v>0.1239259562723392</v>
       </c>
       <c r="T22">
         <v>0.7555377074465038</v>
       </c>
       <c r="U22">
-        <v>0.1050828270931482</v>
+        <v>0.1023828270931482</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.07881212031986115</v>
+        <v>0.07678712031986115</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.764153251839955</v>
+        <v>2.837048423734142</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1150680366124883</v>
+        <v>0.1146435845876267</v>
       </c>
       <c r="C23">
-        <v>7293.085348673172</v>
+        <v>7334.959984237828</v>
       </c>
       <c r="D23">
-        <v>6780.112348673173</v>
+        <v>6821.986984237828</v>
       </c>
       <c r="E23">
         <v>-1265.173</v>
@@ -3179,37 +3179,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M23">
-        <v>195.0470726039239</v>
+        <v>190.0355297039239</v>
       </c>
       <c r="N23">
-        <v>318.4195940627428</v>
+        <v>323.4311369627428</v>
       </c>
       <c r="O23">
-        <v>79.6048985156857</v>
+        <v>80.8577842406857</v>
       </c>
       <c r="P23">
-        <v>238.8146955470571</v>
+        <v>242.5733527220571</v>
       </c>
       <c r="Q23">
-        <v>330.8146955470571</v>
+        <v>334.5733527220571</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1247056852472372</v>
+        <v>0.1247066953423492</v>
       </c>
       <c r="T23">
         <v>0.7630880509586275</v>
       </c>
       <c r="U23">
-        <v>0.1050828270931482</v>
+        <v>0.1023828270931482</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.07881212031986115</v>
+        <v>0.07678712031986115</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.632526906514243</v>
+        <v>2.701950879746802</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1152336842237467</v>
+        <v>0.1147889800934099</v>
       </c>
       <c r="C24">
-        <v>7188.52306678834</v>
+        <v>7232.195525016424</v>
       </c>
       <c r="D24">
-        <v>6763.93706678834</v>
+        <v>6807.609525016424</v>
       </c>
       <c r="E24">
         <v>-1176.786</v>
@@ -3261,37 +3261,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M24">
-        <v>204.335028442206</v>
+        <v>199.084840642206</v>
       </c>
       <c r="N24">
-        <v>309.1316382244607</v>
+        <v>314.3818260244607</v>
       </c>
       <c r="O24">
-        <v>77.28290955611519</v>
+        <v>78.59545650611517</v>
       </c>
       <c r="P24">
-        <v>231.8487286683456</v>
+        <v>235.7863695183455</v>
       </c>
       <c r="Q24">
-        <v>323.8487286683455</v>
+        <v>327.7863695183455</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1255064330171503</v>
+        <v>0.1255074533628724</v>
       </c>
       <c r="T24">
         <v>0.770831993022344</v>
       </c>
       <c r="U24">
-        <v>0.1050828270931482</v>
+        <v>0.1023828270931482</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.07881212031986115</v>
+        <v>0.07678712031986115</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.512866592581777</v>
+        <v>2.579134930667402</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1158650818350052</v>
+        <v>0.115538125599193</v>
       </c>
       <c r="C25">
-        <v>7039.182256490511</v>
+        <v>7070.679371673483</v>
       </c>
       <c r="D25">
-        <v>6702.983256490511</v>
+        <v>6734.480371673483</v>
       </c>
       <c r="E25">
         <v>-1088.399</v>
@@ -3343,37 +3343,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M25">
-        <v>219.1118169804881</v>
+        <v>215.2493050804881</v>
       </c>
       <c r="N25">
-        <v>294.3548496861786</v>
+        <v>298.2173615861786</v>
       </c>
       <c r="O25">
-        <v>73.58871242154464</v>
+        <v>74.55434039654466</v>
       </c>
       <c r="P25">
-        <v>220.7661372646339</v>
+        <v>223.663021189634</v>
       </c>
       <c r="Q25">
-        <v>312.7661372646339</v>
+        <v>315.663021189634</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1263279794304378</v>
+        <v>0.1263290102930195</v>
       </c>
       <c r="T25">
         <v>0.7787770764383649</v>
       </c>
       <c r="U25">
-        <v>0.1077828270931482</v>
+        <v>0.1058828270931482</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.08083712031986115</v>
+        <v>0.07941212031986114</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.343400158615776</v>
+        <v>2.385450984265275</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1168969794462636</v>
+        <v>0.1157097711049762</v>
       </c>
       <c r="C26">
-        <v>6853.508529761059</v>
+        <v>6965.757583026456</v>
       </c>
       <c r="D26">
-        <v>6605.69652976106</v>
+        <v>6717.945583026457</v>
       </c>
       <c r="E26">
         <v>-1000.012</v>
@@ -3425,45 +3425,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M26">
-        <v>238.6084713187701</v>
+        <v>224.6079705187701</v>
       </c>
       <c r="N26">
-        <v>274.8581953478965</v>
+        <v>288.8586961478966</v>
       </c>
       <c r="O26">
-        <v>68.71454883697413</v>
+        <v>72.21467403697415</v>
       </c>
       <c r="P26">
-        <v>206.1436465109224</v>
+        <v>216.6440221109224</v>
       </c>
       <c r="Q26">
-        <v>298.1436465109224</v>
+        <v>308.6440221109224</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1271711454861802</v>
+        <v>0.127172187142381</v>
       </c>
       <c r="T26">
         <v>0.7869312409969127</v>
       </c>
       <c r="U26">
-        <v>0.1124828270931482</v>
+        <v>0.1058828270931482</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.08436212031986115</v>
+        <v>0.07941212031986114</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.151921362342154</v>
+        <v>2.286057193254222</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1171181270575221</v>
+        <v>0.1164064166107594</v>
       </c>
       <c r="C27">
-        <v>6744.638181858828</v>
+        <v>6811.087278715585</v>
       </c>
       <c r="D27">
-        <v>6585.213181858828</v>
+        <v>6651.662278715586</v>
       </c>
       <c r="E27">
         <v>-911.625</v>
@@ -3507,37 +3507,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M27">
-        <v>248.5504909570523</v>
+        <v>240.1537259570522</v>
       </c>
       <c r="N27">
-        <v>264.9161757096144</v>
+        <v>273.3129407096145</v>
       </c>
       <c r="O27">
-        <v>66.22904392740361</v>
+        <v>68.32823517740361</v>
       </c>
       <c r="P27">
-        <v>198.6871317822108</v>
+        <v>204.9847055322109</v>
       </c>
       <c r="Q27">
-        <v>290.6871317822108</v>
+        <v>296.9847055322109</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1280367959700758</v>
+        <v>0.1280378487077254</v>
       </c>
       <c r="T27">
         <v>0.7953028499436883</v>
       </c>
       <c r="U27">
-        <v>0.1124828270931482</v>
+        <v>0.1086828270931482</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.08436212031986115</v>
+        <v>0.08151212031986114</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.065844507848468</v>
+        <v>2.138074954366905</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1191527746687806</v>
+        <v>0.1165990621165425</v>
       </c>
       <c r="C28">
-        <v>6473.591584718879</v>
+        <v>6704.600987486661</v>
       </c>
       <c r="D28">
-        <v>6402.553584718879</v>
+        <v>6633.562987486662</v>
       </c>
       <c r="E28">
         <v>-823.2379999999998</v>
@@ -3589,45 +3589,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M28">
-        <v>279.8644871953344</v>
+        <v>249.7598749953344</v>
       </c>
       <c r="N28">
-        <v>233.6021794713323</v>
+        <v>263.7067916713323</v>
       </c>
       <c r="O28">
-        <v>58.40054486783308</v>
+        <v>65.92669791783308</v>
       </c>
       <c r="P28">
-        <v>175.2016346034992</v>
+        <v>197.7800937534992</v>
       </c>
       <c r="Q28">
-        <v>267.2016346034992</v>
+        <v>289.7800937534993</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1289258424129955</v>
+        <v>0.1289269065315927</v>
       </c>
       <c r="T28">
         <v>0.8039007185917282</v>
       </c>
       <c r="U28">
-        <v>0.1217828270931482</v>
+        <v>0.1086828270931482</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.09133712031986115</v>
+        <v>0.08151212031986114</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>1.834697470237755</v>
+        <v>2.05584130227587</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.119443672280039</v>
+        <v>0.1183712076223257</v>
       </c>
       <c r="C29">
-        <v>6359.914054167024</v>
+        <v>6454.226344993753</v>
       </c>
       <c r="D29">
-        <v>6377.263054167025</v>
+        <v>6471.575344993753</v>
       </c>
       <c r="E29">
         <v>-734.8509999999997</v>
@@ -3671,37 +3671,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M29">
-        <v>290.6285059336165</v>
+        <v>277.9803262336165</v>
       </c>
       <c r="N29">
-        <v>222.8381607330502</v>
+        <v>235.4863404330502</v>
       </c>
       <c r="O29">
-        <v>55.70954018326256</v>
+        <v>58.87158510826255</v>
       </c>
       <c r="P29">
-        <v>167.1286205497877</v>
+        <v>176.6147553247877</v>
       </c>
       <c r="Q29">
-        <v>259.1286205497877</v>
+        <v>268.6147553247877</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1298392462927075</v>
+        <v>0.1298403221040592</v>
       </c>
       <c r="T29">
         <v>0.8127341452849199</v>
       </c>
       <c r="U29">
-        <v>0.1217828270931482</v>
+        <v>0.1164828270931482</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.09133712031986115</v>
+        <v>0.08736212031986115</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.766745712080802</v>
+        <v>1.847133117741383</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1207215698912975</v>
+        <v>0.1186223531281089</v>
       </c>
       <c r="C30">
-        <v>6162.753449514709</v>
+        <v>6343.520551472028</v>
       </c>
       <c r="D30">
-        <v>6268.48944951471</v>
+        <v>6449.256551472028</v>
       </c>
       <c r="E30">
         <v>-646.4639999999999</v>
@@ -3753,45 +3753,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M30">
-        <v>313.0242538718986</v>
+        <v>288.2758938718985</v>
       </c>
       <c r="N30">
-        <v>200.4424127947681</v>
+        <v>225.1907727947682</v>
       </c>
       <c r="O30">
-        <v>50.11060319869203</v>
+        <v>56.29769319869204</v>
       </c>
       <c r="P30">
-        <v>150.3318095960761</v>
+        <v>168.8930795960761</v>
       </c>
       <c r="Q30">
-        <v>242.3318095960761</v>
+        <v>260.8930795960761</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1307780225024116</v>
+        <v>0.1307791103313163</v>
       </c>
       <c r="T30">
         <v>0.8218129449418113</v>
       </c>
       <c r="U30">
-        <v>0.1264828270931482</v>
+        <v>0.1164828270931482</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.09486212031986116</v>
+        <v>0.08736212031986115</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>1.640341476148991</v>
+        <v>1.781164077822048</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1210477175025559</v>
+        <v>0.119721748633892</v>
       </c>
       <c r="C31">
-        <v>6047.196816627327</v>
+        <v>6159.217480770745</v>
       </c>
       <c r="D31">
-        <v>6241.319816627327</v>
+        <v>6353.340480770745</v>
       </c>
       <c r="E31">
         <v>-558.0770000000002</v>
@@ -3835,37 +3835,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M31">
-        <v>324.2036915101806</v>
+        <v>308.5680312101806</v>
       </c>
       <c r="N31">
-        <v>189.2629751564861</v>
+        <v>204.8986354564861</v>
       </c>
       <c r="O31">
-        <v>47.31574378912153</v>
+        <v>51.22465886412152</v>
       </c>
       <c r="P31">
-        <v>141.9472313673646</v>
+        <v>153.6739765923646</v>
       </c>
       <c r="Q31">
-        <v>233.9472313673646</v>
+        <v>245.6739765923646</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.131743243112389</v>
+        <v>0.1317443432973694</v>
       </c>
       <c r="T31">
         <v>0.831147485434108</v>
       </c>
       <c r="U31">
-        <v>0.1264828270931482</v>
+        <v>0.1203828270931482</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.09486212031986116</v>
+        <v>0.09028712031986116</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.58377797697144</v>
+        <v>1.664030666601751</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1213738651138144</v>
+        <v>0.1200021441396752</v>
       </c>
       <c r="C32">
-        <v>5931.874691022362</v>
+        <v>6046.822439787926</v>
       </c>
       <c r="D32">
-        <v>6214.384691022362</v>
+        <v>6329.332439787927</v>
       </c>
       <c r="E32">
         <v>-469.6900000000001</v>
@@ -3917,37 +3917,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M32">
-        <v>335.3831291484627</v>
+        <v>319.2083081484627</v>
       </c>
       <c r="N32">
-        <v>178.083537518204</v>
+        <v>194.258358518204</v>
       </c>
       <c r="O32">
-        <v>44.52088437955099</v>
+        <v>48.56458962955099</v>
       </c>
       <c r="P32">
-        <v>133.562653138653</v>
+        <v>145.693768888653</v>
       </c>
       <c r="Q32">
-        <v>225.562653138653</v>
+        <v>237.693768888653</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1327360414540801</v>
+        <v>0.1327371543481669</v>
       </c>
       <c r="T32">
         <v>0.8407487270833276</v>
       </c>
       <c r="U32">
-        <v>0.1264828270931482</v>
+        <v>0.1203828270931482</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.09486212031986116</v>
+        <v>0.09028712031986116</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.530985377739059</v>
+        <v>1.608562977715026</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1254897627250728</v>
+        <v>0.1202825396454583</v>
       </c>
       <c r="C33">
-        <v>5522.520853745377</v>
+        <v>5934.608159204158</v>
       </c>
       <c r="D33">
-        <v>5893.417853745378</v>
+        <v>6305.505159204158</v>
       </c>
       <c r="E33">
         <v>-381.3029999999999</v>
@@ -3999,45 +3999,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M33">
-        <v>391.2245178867449</v>
+        <v>329.8485850867448</v>
       </c>
       <c r="N33">
-        <v>122.2421487799218</v>
+        <v>183.6180815799219</v>
       </c>
       <c r="O33">
-        <v>30.56053719498045</v>
+        <v>45.90452039498047</v>
       </c>
       <c r="P33">
-        <v>91.68161158494136</v>
+        <v>137.7135611849414</v>
       </c>
       <c r="Q33">
-        <v>183.6816115849414</v>
+        <v>229.7135611849414</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1337576165592984</v>
+        <v>0.1337587425308716</v>
       </c>
       <c r="T33">
         <v>0.8506282655919448</v>
       </c>
       <c r="U33">
-        <v>0.1427828270931482</v>
+        <v>0.1203828270931482</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.1070871203198612</v>
+        <v>0.09028712031986116</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y33">
-        <v>1.31246034742462</v>
+        <v>1.556673849401638</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1259381603363313</v>
+        <v>0.1205629351512415</v>
       </c>
       <c r="C34">
-        <v>5401.15837144485</v>
+        <v>5822.572605214713</v>
       </c>
       <c r="D34">
-        <v>5860.44237144485</v>
+        <v>6281.856605214713</v>
       </c>
       <c r="E34">
         <v>-292.9159999999997</v>
@@ -4081,45 +4081,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M34">
-        <v>403.844663625027</v>
+        <v>340.4888620250269</v>
       </c>
       <c r="N34">
-        <v>109.6220030416397</v>
+        <v>172.9778046416398</v>
       </c>
       <c r="O34">
-        <v>27.40550076040994</v>
+        <v>43.24445116040994</v>
       </c>
       <c r="P34">
-        <v>82.21650228122981</v>
+        <v>129.7333534812298</v>
       </c>
       <c r="Q34">
-        <v>174.2165022812298</v>
+        <v>221.7333534812298</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1348092379911408</v>
+        <v>0.1348103774248323</v>
       </c>
       <c r="T34">
         <v>0.8607983787625804</v>
       </c>
       <c r="U34">
-        <v>0.1427828270931482</v>
+        <v>0.1203828270931482</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.1070871203198612</v>
+        <v>0.09028712031986116</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y34">
-        <v>1.271445961567601</v>
+        <v>1.508027791607836</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1344798079475898</v>
+        <v>0.1243578306570247</v>
       </c>
       <c r="C35">
-        <v>4748.292999857102</v>
+        <v>5430.727767851788</v>
       </c>
       <c r="D35">
-        <v>5295.963999857102</v>
+        <v>5978.398767851789</v>
       </c>
       <c r="E35">
         <v>-204.529</v>
@@ -4163,45 +4163,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M35">
-        <v>511.843221063309</v>
+        <v>392.547287163309</v>
       </c>
       <c r="N35">
-        <v>1.623445603357709</v>
+        <v>120.9193795033577</v>
       </c>
       <c r="O35">
-        <v>0.4058614008394272</v>
+        <v>30.22984487583943</v>
       </c>
       <c r="P35">
-        <v>1.217584202518282</v>
+        <v>90.6895346275183</v>
       </c>
       <c r="Q35">
-        <v>93.21758420251828</v>
+        <v>182.6895346275183</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1358922511075158</v>
+        <v>0.1358934044051798</v>
       </c>
       <c r="T35">
         <v>0.8712720774009959</v>
       </c>
       <c r="U35">
-        <v>0.1754828270931482</v>
+        <v>0.1345828270931482</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.1316121203198611</v>
+        <v>0.1009371203198612</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>1.00317176341612</v>
+        <v>1.308037740821407</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1357135023889824</v>
+        <v>0.1247447261628078</v>
       </c>
       <c r="C36">
-        <v>4587.240591716581</v>
+        <v>5313.041589458398</v>
       </c>
       <c r="D36">
-        <v>5223.298591716581</v>
+        <v>5949.099589458398</v>
       </c>
       <c r="E36">
         <v>-116.1419999999998</v>
@@ -4245,45 +4245,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M36">
-        <v>527.3536217015911</v>
+        <v>404.4426595015911</v>
       </c>
       <c r="N36">
-        <v>-13.88695503492443</v>
+        <v>109.0240071650756</v>
       </c>
       <c r="O36">
-        <v>-3.471738758731107</v>
+        <v>27.2560017912689</v>
       </c>
       <c r="P36">
-        <v>-10.41521627619332</v>
+        <v>81.7680053738067</v>
       </c>
       <c r="Q36">
-        <v>81.58478372380668</v>
+        <v>173.7680053738067</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1372312016491138</v>
+        <v>0.1370092503849319</v>
       </c>
       <c r="T36">
-        <v>0.8842209182344104</v>
+        <v>0.8820631608466362</v>
       </c>
       <c r="U36">
-        <v>0.1754828270931482</v>
+        <v>0.1345828270931482</v>
       </c>
       <c r="V36">
-        <v>0.243416677887735</v>
+        <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.1327673802957862</v>
+        <v>0.1009371203198612</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.9736667115509401</v>
+        <v>1.269566042561954</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1370103306599139</v>
+        <v>0.132639121668591</v>
       </c>
       <c r="C37">
-        <v>4424.588744387924</v>
+        <v>4683.832156434371</v>
       </c>
       <c r="D37">
-        <v>5149.033744387924</v>
+        <v>5408.277156434371</v>
       </c>
       <c r="E37">
         <v>-27.75499999999965</v>
@@ -4327,37 +4327,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M37">
-        <v>542.8640223398733</v>
+        <v>504.8134188398733</v>
       </c>
       <c r="N37">
-        <v>-29.39735567320656</v>
+        <v>8.653247826793404</v>
       </c>
       <c r="O37">
-        <v>-7.34933891830164</v>
+        <v>2.163311956698351</v>
       </c>
       <c r="P37">
-        <v>-22.04801675490492</v>
+        <v>6.489935870095053</v>
       </c>
       <c r="Q37">
-        <v>69.95198324509508</v>
+        <v>98.48993587009505</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1386378355206386</v>
+        <v>0.1381594300871378</v>
       </c>
       <c r="T37">
-        <v>0.8978243169764782</v>
+        <v>0.8931862776290654</v>
       </c>
       <c r="U37">
-        <v>0.1754828270931482</v>
+        <v>0.1631828270931482</v>
       </c>
       <c r="V37">
-        <v>0.2364619156623712</v>
+        <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.1339878216328537</v>
+        <v>0.1223871203198612</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.9458476626494846</v>
+        <v>1.017141477432751</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1383071589308454</v>
+        <v>0.133469517923128</v>
       </c>
       <c r="C38">
-        <v>4264.019087338709</v>
+        <v>4544.218536275024</v>
       </c>
       <c r="D38">
-        <v>5076.85108733871</v>
+        <v>5357.050536275025</v>
       </c>
       <c r="E38">
         <v>60.63200000000006</v>
@@ -4409,37 +4409,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M38">
-        <v>558.3744229781553</v>
+        <v>519.2366593781553</v>
       </c>
       <c r="N38">
-        <v>-44.90775631148858</v>
+        <v>-5.769992711488612</v>
       </c>
       <c r="O38">
-        <v>-11.22693907787215</v>
+        <v>-1.442498177872153</v>
       </c>
       <c r="P38">
-        <v>-33.68081723361644</v>
+        <v>-4.327494533616459</v>
       </c>
       <c r="Q38">
-        <v>58.31918276638356</v>
+        <v>87.67250546638354</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1400884267006486</v>
+        <v>0.1394483626260901</v>
       </c>
       <c r="T38">
-        <v>0.9118528219292357</v>
+        <v>0.9056512403891822</v>
       </c>
       <c r="U38">
-        <v>0.1754828270931482</v>
+        <v>0.1631828270931482</v>
       </c>
       <c r="V38">
-        <v>0.2298935291161942</v>
+        <v>0.2472218868760158</v>
       </c>
       <c r="W38">
-        <v>0.1351404606734175</v>
+        <v>0.1228404606734175</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.9195741164647768</v>
+        <v>0.9888875475040633</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1396039872017769</v>
+        <v>0.1346433461940595</v>
       </c>
       <c r="C39">
-        <v>4105.445262516348</v>
+        <v>4385.052376803106</v>
       </c>
       <c r="D39">
-        <v>5006.664262516349</v>
+        <v>5286.271376803106</v>
       </c>
       <c r="E39">
         <v>149.0190000000002</v>
@@ -4491,37 +4491,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M39">
-        <v>573.8848236164374</v>
+        <v>533.6598999164374</v>
       </c>
       <c r="N39">
-        <v>-60.41815694977072</v>
+        <v>-20.19323324977074</v>
       </c>
       <c r="O39">
-        <v>-15.10453923744268</v>
+        <v>-5.048308312442686</v>
       </c>
       <c r="P39">
-        <v>-45.31361771232804</v>
+        <v>-15.14492493732806</v>
       </c>
       <c r="Q39">
-        <v>46.68638228767196</v>
+        <v>76.85507506267194</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1415850683943096</v>
+        <v>0.140934844572536</v>
       </c>
       <c r="T39">
-        <v>0.9263266762455727</v>
+        <v>0.9200266569032963</v>
       </c>
       <c r="U39">
-        <v>0.1754828270931482</v>
+        <v>0.1631828270931482</v>
       </c>
       <c r="V39">
-        <v>0.2236801904914322</v>
+        <v>0.2405402142577451</v>
       </c>
       <c r="W39">
-        <v>0.1362307949009778</v>
+        <v>0.1239307949009778</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8947207619657287</v>
+        <v>0.9621608570309804</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1409008154727083</v>
+        <v>0.1358171744649909</v>
       </c>
       <c r="C40">
-        <v>3948.785622303743</v>
+        <v>4227.732144597283</v>
       </c>
       <c r="D40">
-        <v>4938.391622303744</v>
+        <v>5217.338144597284</v>
       </c>
       <c r="E40">
         <v>237.4059999999999</v>
@@ -4573,37 +4573,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M40">
-        <v>589.3952242547194</v>
+        <v>548.0831404547195</v>
       </c>
       <c r="N40">
-        <v>-75.92855758805274</v>
+        <v>-34.61647378805276</v>
       </c>
       <c r="O40">
-        <v>-18.98213939701319</v>
+        <v>-8.65411844701319</v>
       </c>
       <c r="P40">
-        <v>-56.94641819103956</v>
+        <v>-25.96235534103957</v>
       </c>
       <c r="Q40">
-        <v>35.05358180896044</v>
+        <v>66.03764465896043</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1431299888522824</v>
+        <v>0.1424692775495124</v>
       </c>
       <c r="T40">
-        <v>0.9412674290882432</v>
+        <v>0.9348657965307687</v>
       </c>
       <c r="U40">
-        <v>0.1754828270931482</v>
+        <v>0.1631828270931482</v>
       </c>
       <c r="V40">
-        <v>0.2177938696890261</v>
+        <v>0.2342102086193834</v>
       </c>
       <c r="W40">
-        <v>0.1372637431165612</v>
+        <v>0.1249637431165612</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8711754787561043</v>
+        <v>0.9368408344775337</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1421976437436398</v>
+        <v>0.1369910027359224</v>
       </c>
       <c r="C41">
-        <v>3793.962912674097</v>
+        <v>4072.186556256362</v>
       </c>
       <c r="D41">
-        <v>4871.955912674098</v>
+        <v>5150.179556256363</v>
       </c>
       <c r="E41">
         <v>325.7930000000001</v>
@@ -4655,37 +4655,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M41">
-        <v>604.9056248930016</v>
+        <v>562.5063809930016</v>
       </c>
       <c r="N41">
-        <v>-91.43895822633488</v>
+        <v>-49.03971432633489</v>
       </c>
       <c r="O41">
-        <v>-22.85973955658372</v>
+        <v>-12.25992858158372</v>
       </c>
       <c r="P41">
-        <v>-68.57921866975116</v>
+        <v>-36.77978574475117</v>
       </c>
       <c r="Q41">
-        <v>23.42078133024884</v>
+        <v>55.22021425524883</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1447255624400247</v>
+        <v>0.1440540198044224</v>
       </c>
       <c r="T41">
-        <v>0.9566980426798538</v>
+        <v>0.9501914653263551</v>
       </c>
       <c r="U41">
-        <v>0.1754828270931482</v>
+        <v>0.1631828270931482</v>
       </c>
       <c r="V41">
-        <v>0.2122094114918716</v>
+        <v>0.2282048186547838</v>
       </c>
       <c r="W41">
-        <v>0.1382437196287813</v>
+        <v>0.1259437196287814</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8488376459674862</v>
+        <v>0.9128192746191354</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1434944720145713</v>
+        <v>0.1381648310068539</v>
       </c>
       <c r="C42">
-        <v>3640.903981581157</v>
+        <v>3918.347952029872</v>
       </c>
       <c r="D42">
-        <v>4807.283981581157</v>
+        <v>5084.727952029873</v>
       </c>
       <c r="E42">
         <v>414.1800000000003</v>
@@ -4737,37 +4737,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M42">
-        <v>620.4160255312836</v>
+        <v>576.9296215312837</v>
       </c>
       <c r="N42">
-        <v>-106.9493588646169</v>
+        <v>-63.46295486461702</v>
       </c>
       <c r="O42">
-        <v>-26.73733971615422</v>
+        <v>-15.86573871615425</v>
       </c>
       <c r="P42">
-        <v>-80.21201914846267</v>
+        <v>-47.59721614846276</v>
       </c>
       <c r="Q42">
-        <v>11.78798085153733</v>
+        <v>44.40278385153724</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1463743218140251</v>
+        <v>0.1456915868011628</v>
       </c>
       <c r="T42">
-        <v>0.9726430100578514</v>
+        <v>0.9660279897484612</v>
       </c>
       <c r="U42">
-        <v>0.1754828270931482</v>
+        <v>0.1631828270931482</v>
       </c>
       <c r="V42">
-        <v>0.2069041762045748</v>
+        <v>0.2224996981884142</v>
       </c>
       <c r="W42">
-        <v>0.1391746973153905</v>
+        <v>0.1268746973153906</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8276167048182992</v>
+        <v>0.8899987927536569</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1447913002855028</v>
+        <v>0.1393386592777854</v>
       </c>
       <c r="C43">
-        <v>3489.539510270744</v>
+        <v>3766.152068449844</v>
       </c>
       <c r="D43">
-        <v>4744.306510270744</v>
+        <v>5020.919068449845</v>
       </c>
       <c r="E43">
         <v>502.5670000000005</v>
@@ -4819,37 +4819,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M43">
-        <v>635.9264261695657</v>
+        <v>591.3528620695658</v>
       </c>
       <c r="N43">
-        <v>-122.459759502899</v>
+        <v>-77.88619540289915</v>
       </c>
       <c r="O43">
-        <v>-30.61493987572476</v>
+        <v>-19.47154885072479</v>
       </c>
       <c r="P43">
-        <v>-91.84481962717427</v>
+        <v>-58.41464655217436</v>
       </c>
       <c r="Q43">
-        <v>0.1551803728257255</v>
+        <v>33.58535344782564</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1480789713362968</v>
+        <v>0.1473846645435554</v>
       </c>
       <c r="T43">
-        <v>0.9891284848045947</v>
+        <v>0.9824013455069095</v>
       </c>
       <c r="U43">
-        <v>0.1754828270931482</v>
+        <v>0.1631828270931482</v>
       </c>
       <c r="V43">
-        <v>0.201857732882512</v>
+        <v>0.2170728762813797</v>
       </c>
       <c r="W43">
-        <v>0.1400602614563115</v>
+        <v>0.1277602614563115</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8074309315300479</v>
+        <v>0.8682915051255189</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1606773690730132</v>
+        <v>0.1405124875487169</v>
       </c>
       <c r="C44">
-        <v>2745.075685223574</v>
+        <v>3615.537827870043</v>
       </c>
       <c r="D44">
-        <v>4088.229685223574</v>
+        <v>4958.691827870044</v>
       </c>
       <c r="E44">
         <v>590.9540000000002</v>
@@ -4901,45 +4901,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M44">
-        <v>772.8275326078478</v>
+        <v>605.7761026078479</v>
       </c>
       <c r="N44">
-        <v>-259.3608659411811</v>
+        <v>-92.30943594118116</v>
       </c>
       <c r="O44">
-        <v>-64.84021648529529</v>
+        <v>-23.07735898529529</v>
       </c>
       <c r="P44">
-        <v>-194.5206494558859</v>
+        <v>-69.23207695588587</v>
       </c>
       <c r="Q44">
-        <v>-102.5206494558859</v>
+        <v>22.76792304411413</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.151316954491369</v>
+        <v>0.149136124277065</v>
       </c>
       <c r="T44">
-        <v>1.020442657504558</v>
+        <v>0.9993392997397872</v>
       </c>
       <c r="U44">
-        <v>0.2081828270931482</v>
+        <v>0.1631828270931482</v>
       </c>
       <c r="V44">
-        <v>0.1661000174689728</v>
+        <v>0.2119044744651564</v>
       </c>
       <c r="W44">
-        <v>0.1736036558762361</v>
+        <v>0.1286036558762362</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.6644000698758912</v>
+        <v>0.8476178978606257</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1856672936813424</v>
+        <v>0.1416863158196484</v>
       </c>
       <c r="C45">
-        <v>1926.249503008248</v>
+        <v>3466.447143463827</v>
       </c>
       <c r="D45">
-        <v>3357.790503008248</v>
+        <v>4897.988143463827</v>
       </c>
       <c r="E45">
         <v>679.3409999999999</v>
@@ -4983,45 +4983,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M45">
-        <v>989.6216483461299</v>
+        <v>620.1993431461299</v>
       </c>
       <c r="N45">
-        <v>-476.1549816794632</v>
+        <v>-106.7326764794632</v>
       </c>
       <c r="O45">
-        <v>-119.0387454198658</v>
+        <v>-26.68316911986579</v>
       </c>
       <c r="P45">
-        <v>-357.1162362595974</v>
+        <v>-80.04950735959738</v>
       </c>
       <c r="Q45">
-        <v>-265.1162362595974</v>
+        <v>11.95049264040262</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1547823332322663</v>
+        <v>0.1509490387380661</v>
       </c>
       <c r="T45">
-        <v>1.053955947465085</v>
+        <v>1.016871568156275</v>
       </c>
       <c r="U45">
-        <v>0.2603828270931482</v>
+        <v>0.1631828270931482</v>
       </c>
       <c r="V45">
-        <v>0.1297128724712065</v>
+        <v>0.206976463431083</v>
       </c>
       <c r="W45">
-        <v>0.2266078226487225</v>
+        <v>0.1294078226487225</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.5188514898848259</v>
+        <v>0.8279058537243322</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1878131219522739</v>
+        <v>0.1428601440905798</v>
       </c>
       <c r="C46">
-        <v>1787.126052107311</v>
+        <v>3318.824738371912</v>
       </c>
       <c r="D46">
-        <v>3307.054052107311</v>
+        <v>4838.752738371913</v>
       </c>
       <c r="E46">
         <v>767.7280000000001</v>
@@ -5065,45 +5065,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M46">
-        <v>1012.636105284412</v>
+        <v>634.622583684412</v>
       </c>
       <c r="N46">
-        <v>-499.1694386177453</v>
+        <v>-121.1559170177453</v>
       </c>
       <c r="O46">
-        <v>-124.7923596544363</v>
+        <v>-30.28897925443633</v>
       </c>
       <c r="P46">
-        <v>-374.377078963309</v>
+        <v>-90.86693776330898</v>
       </c>
       <c r="Q46">
-        <v>-282.377078963309</v>
+        <v>1.133062236691018</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1567284463256996</v>
+        <v>0.152826700144103</v>
       </c>
       <c r="T46">
-        <v>1.072776589384105</v>
+        <v>1.035029989016208</v>
       </c>
       <c r="U46">
-        <v>0.2603828270931482</v>
+        <v>0.1631828270931482</v>
       </c>
       <c r="V46">
-        <v>0.1267648526423154</v>
+        <v>0.2022724528985584</v>
       </c>
       <c r="W46">
-        <v>0.2273754363860958</v>
+        <v>0.1301754363860958</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.5070594105692616</v>
+        <v>0.8090898115942337</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1899589502232054</v>
+        <v>0.1575867468365181</v>
       </c>
       <c r="C47">
-        <v>1649.513041044363</v>
+        <v>2592.988386097303</v>
       </c>
       <c r="D47">
-        <v>3257.828041044364</v>
+        <v>4201.303386097303</v>
       </c>
       <c r="E47">
         <v>856.1150000000002</v>
@@ -5147,45 +5147,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M47">
-        <v>1035.650562222694</v>
+        <v>761.2089272226942</v>
       </c>
       <c r="N47">
-        <v>-522.1838955560274</v>
+        <v>-247.7422605560275</v>
       </c>
       <c r="O47">
-        <v>-130.5459738890069</v>
+        <v>-61.93556513900688</v>
       </c>
       <c r="P47">
-        <v>-391.6379216670206</v>
+        <v>-185.8066954170206</v>
       </c>
       <c r="Q47">
-        <v>-299.6379216670206</v>
+        <v>-93.80669541702065</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.158745327167985</v>
+        <v>0.1563413210103718</v>
       </c>
       <c r="T47">
-        <v>1.092281618281997</v>
+        <v>1.069019058955881</v>
       </c>
       <c r="U47">
-        <v>0.2603828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V47">
-        <v>0.1239478559169306</v>
+        <v>0.1686352617211392</v>
       </c>
       <c r="W47">
-        <v>0.2281089339573636</v>
+        <v>0.1591089339573636</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.4957914236677224</v>
+        <v>0.674541046884557</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1921047784941369</v>
+        <v>0.1590425751074496</v>
       </c>
       <c r="C48">
-        <v>1513.344009696792</v>
+        <v>2450.590107755767</v>
       </c>
       <c r="D48">
-        <v>3210.046009696792</v>
+        <v>4147.292107755768</v>
       </c>
       <c r="E48">
         <v>944.5020000000004</v>
@@ -5229,45 +5229,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M48">
-        <v>1058.665019160976</v>
+        <v>778.1246811609764</v>
       </c>
       <c r="N48">
-        <v>-545.1983524943096</v>
+        <v>-264.6580144943097</v>
       </c>
       <c r="O48">
-        <v>-136.2995881235774</v>
+        <v>-66.16450362357742</v>
       </c>
       <c r="P48">
-        <v>-408.8987643707322</v>
+        <v>-198.4935108707323</v>
       </c>
       <c r="Q48">
-        <v>-316.8987643707322</v>
+        <v>-106.4935108707323</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1608369073007255</v>
+        <v>0.1583883825105639</v>
       </c>
       <c r="T48">
-        <v>1.11250905565759</v>
+        <v>1.088815708195805</v>
       </c>
       <c r="U48">
-        <v>0.2603828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V48">
-        <v>0.1212533373100408</v>
+        <v>0.1649692777706797</v>
       </c>
       <c r="W48">
-        <v>0.2288105403298807</v>
+        <v>0.1598105403298807</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.4850133492401633</v>
+        <v>0.6598771110827187</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1942506067650684</v>
+        <v>0.1869770859282539</v>
       </c>
       <c r="C49">
-        <v>1378.556340621056</v>
+        <v>1541.584269369941</v>
       </c>
       <c r="D49">
-        <v>3163.645340621056</v>
+        <v>3326.673269369942</v>
       </c>
       <c r="E49">
         <v>1032.889</v>
@@ -5311,37 +5311,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M49">
-        <v>1081.679476099258</v>
+        <v>1019.366641099258</v>
       </c>
       <c r="N49">
-        <v>-568.2128094325915</v>
+        <v>-505.8999744325916</v>
       </c>
       <c r="O49">
-        <v>-142.0532023581479</v>
+        <v>-126.4749936081479</v>
       </c>
       <c r="P49">
-        <v>-426.1596070744436</v>
+        <v>-379.4249808244438</v>
       </c>
       <c r="Q49">
-        <v>-334.1596070744436</v>
+        <v>-287.4249808244438</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1630074149856448</v>
+        <v>0.162585677557693</v>
       </c>
       <c r="T49">
-        <v>1.13349979255679</v>
+        <v>1.129406759220256</v>
       </c>
       <c r="U49">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V49">
-        <v>0.1186734790694017</v>
+        <v>0.1259278668647028</v>
       </c>
       <c r="W49">
-        <v>0.2294822911120779</v>
+        <v>0.2144822911120778</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4746939162776067</v>
+        <v>0.5037114674588112</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1963964350359998</v>
+        <v>0.1889729141991854</v>
       </c>
       <c r="C50">
-        <v>1245.090985283611</v>
+        <v>1406.823494020761</v>
       </c>
       <c r="D50">
-        <v>3118.566985283611</v>
+        <v>3280.299494020762</v>
       </c>
       <c r="E50">
         <v>1121.276</v>
@@ -5393,37 +5393,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M50">
-        <v>1104.69393303754</v>
+        <v>1041.05529303754</v>
       </c>
       <c r="N50">
-        <v>-591.2272663708736</v>
+        <v>-527.5886263708737</v>
       </c>
       <c r="O50">
-        <v>-147.8068165927184</v>
+        <v>-131.8971565927184</v>
       </c>
       <c r="P50">
-        <v>-443.4204497781552</v>
+        <v>-395.6914697781553</v>
       </c>
       <c r="Q50">
-        <v>-351.4204497781552</v>
+        <v>-303.6914697781553</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1652614037353688</v>
+        <v>0.164831555972264</v>
       </c>
       <c r="T50">
-        <v>1.155297865490574</v>
+        <v>1.151126119974491</v>
       </c>
       <c r="U50">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V50">
-        <v>0.1162011149221225</v>
+        <v>0.1233043696383548</v>
       </c>
       <c r="W50">
-        <v>0.2301260522783501</v>
+        <v>0.2151260522783502</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4648044596884898</v>
+        <v>0.4932174785534192</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1985422633069313</v>
+        <v>0.1909687424701169</v>
       </c>
       <c r="C51">
-        <v>1112.892213368407</v>
+        <v>1273.337842920738</v>
       </c>
       <c r="D51">
-        <v>3074.755213368408</v>
+        <v>3235.200842920739</v>
       </c>
       <c r="E51">
         <v>1209.663</v>
@@ -5475,37 +5475,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M51">
-        <v>1127.708389975822</v>
+        <v>1062.743944975823</v>
       </c>
       <c r="N51">
-        <v>-614.2417233091558</v>
+        <v>-549.2772783091559</v>
       </c>
       <c r="O51">
-        <v>-153.5604308272889</v>
+        <v>-137.319319577289</v>
       </c>
       <c r="P51">
-        <v>-460.6812924818668</v>
+        <v>-411.9579587318669</v>
       </c>
       <c r="Q51">
-        <v>-368.6812924818668</v>
+        <v>-319.9579587318669</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1676037842007682</v>
+        <v>0.1671655080501516</v>
       </c>
       <c r="T51">
-        <v>1.177950764813919</v>
+        <v>1.173697220366148</v>
       </c>
       <c r="U51">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V51">
-        <v>0.1138296635971812</v>
+        <v>0.1207879539314496</v>
       </c>
       <c r="W51">
-        <v>0.2307435374786521</v>
+        <v>0.2157435374786522</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4553186543887248</v>
+        <v>0.4831518157257985</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.2006880915778628</v>
+        <v>0.1929645707410483</v>
       </c>
       <c r="C52">
-        <v>981.9073829230429</v>
+        <v>1141.075436823137</v>
       </c>
       <c r="D52">
-        <v>3032.157382923043</v>
+        <v>3191.325436823138</v>
       </c>
       <c r="E52">
         <v>1298.05</v>
@@ -5557,37 +5557,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M52">
-        <v>1150.722846914105</v>
+        <v>1084.432596914105</v>
       </c>
       <c r="N52">
-        <v>-637.2561802474379</v>
+        <v>-570.9659302474379</v>
       </c>
       <c r="O52">
-        <v>-159.3140450618595</v>
+        <v>-142.7414825618595</v>
       </c>
       <c r="P52">
-        <v>-477.9421351855784</v>
+        <v>-428.2244476855784</v>
       </c>
       <c r="Q52">
-        <v>-385.9421351855784</v>
+        <v>-336.2244476855784</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1700398598847835</v>
+        <v>0.1695928182111546</v>
       </c>
       <c r="T52">
-        <v>1.201509780110197</v>
+        <v>1.197171164773471</v>
       </c>
       <c r="U52">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V52">
-        <v>0.1115530703252375</v>
+        <v>0.1183721948528206</v>
       </c>
       <c r="W52">
-        <v>0.2313363232709421</v>
+        <v>0.2163363232709421</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4462122813009503</v>
+        <v>0.4734887794112825</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.2028339198487943</v>
+        <v>0.1949603990119798</v>
       </c>
       <c r="C53">
-        <v>852.0867293502679</v>
+        <v>1009.987173144948</v>
       </c>
       <c r="D53">
-        <v>2990.723729350268</v>
+        <v>3148.624173144949</v>
       </c>
       <c r="E53">
         <v>1386.437</v>
@@ -5639,37 +5639,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M53">
-        <v>1173.737303852387</v>
+        <v>1106.121248852387</v>
       </c>
       <c r="N53">
-        <v>-660.2706371857198</v>
+        <v>-592.6545821857198</v>
       </c>
       <c r="O53">
-        <v>-165.06765929643</v>
+        <v>-148.16364554643</v>
       </c>
       <c r="P53">
-        <v>-495.2029778892899</v>
+        <v>-444.4909366392899</v>
       </c>
       <c r="Q53">
-        <v>-403.2029778892899</v>
+        <v>-352.4909366392899</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.172575367229371</v>
+        <v>0.1721192022562802</v>
       </c>
       <c r="T53">
-        <v>1.226030387867548</v>
+        <v>1.221603229360685</v>
       </c>
       <c r="U53">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V53">
-        <v>0.1093657552208211</v>
+        <v>0.116051171424334</v>
       </c>
       <c r="W53">
-        <v>0.2319058625615736</v>
+        <v>0.2169058625615736</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4374630208832846</v>
+        <v>0.4642046856973359</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.2049797481197258</v>
+        <v>0.1969562272829113</v>
       </c>
       <c r="C54">
-        <v>723.3831714665439</v>
+        <v>880.0265426550895</v>
       </c>
       <c r="D54">
-        <v>2950.407171466545</v>
+        <v>3107.05054265509</v>
       </c>
       <c r="E54">
         <v>1474.824000000001</v>
@@ -5721,37 +5721,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M54">
-        <v>1196.751760790669</v>
+        <v>1127.809900790669</v>
       </c>
       <c r="N54">
-        <v>-683.2850941240022</v>
+        <v>-614.3432341240023</v>
       </c>
       <c r="O54">
-        <v>-170.8212735310005</v>
+        <v>-153.5858085310006</v>
       </c>
       <c r="P54">
-        <v>-512.4638205930016</v>
+        <v>-460.7574255930017</v>
       </c>
       <c r="Q54">
-        <v>-420.4638205930016</v>
+        <v>-368.7574255930017</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1752165207133162</v>
+        <v>0.174750852303286</v>
       </c>
       <c r="T54">
-        <v>1.251572687614789</v>
+        <v>1.247053296639032</v>
       </c>
       <c r="U54">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V54">
-        <v>0.1072625676204207</v>
+        <v>0.1138194181277121</v>
       </c>
       <c r="W54">
-        <v>0.2324534964948731</v>
+        <v>0.2174534964948731</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4290502704816829</v>
+        <v>0.4552776725108485</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.2071255763906573</v>
+        <v>0.1989520555538428</v>
       </c>
       <c r="C55">
-        <v>595.7521330385589</v>
+        <v>751.1494604957679</v>
       </c>
       <c r="D55">
-        <v>2911.163133038559</v>
+        <v>3066.560460495768</v>
       </c>
       <c r="E55">
         <v>1563.211</v>
@@ -5803,37 +5803,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M55">
-        <v>1219.766217728951</v>
+        <v>1149.498552728951</v>
       </c>
       <c r="N55">
-        <v>-706.2995510622841</v>
+        <v>-636.0318860622842</v>
       </c>
       <c r="O55">
-        <v>-176.574887765571</v>
+        <v>-159.0079715155711</v>
       </c>
       <c r="P55">
-        <v>-529.7246632967131</v>
+        <v>-477.0239145467132</v>
       </c>
       <c r="Q55">
-        <v>-437.7246632967131</v>
+        <v>-385.0239145467132</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1779700637072165</v>
+        <v>0.1774944874586751</v>
       </c>
       <c r="T55">
-        <v>1.278201893734253</v>
+        <v>1.273586345503693</v>
       </c>
       <c r="U55">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V55">
-        <v>0.1052387455898467</v>
+        <v>0.1116718819366232</v>
       </c>
       <c r="W55">
-        <v>0.2329804649967273</v>
+        <v>0.2179804649967273</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.420954982359387</v>
+        <v>0.4466875277464929</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.2092714046615887</v>
+        <v>0.2009478838247743</v>
       </c>
       <c r="C56">
-        <v>469.1513783754745</v>
+        <v>623.3141102463342</v>
       </c>
       <c r="D56">
-        <v>2872.949378375476</v>
+        <v>3027.112110246335</v>
       </c>
       <c r="E56">
         <v>1651.598000000001</v>
@@ -5885,37 +5885,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M56">
-        <v>1242.780674667233</v>
+        <v>1171.187204667233</v>
       </c>
       <c r="N56">
-        <v>-729.3140080005664</v>
+        <v>-657.7205380005664</v>
       </c>
       <c r="O56">
-        <v>-182.3285020001416</v>
+        <v>-164.4301345001416</v>
       </c>
       <c r="P56">
-        <v>-546.9855060004248</v>
+        <v>-493.2904035004248</v>
       </c>
       <c r="Q56">
-        <v>-454.9855060004248</v>
+        <v>-401.2904035004248</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1808433259617212</v>
+        <v>0.1803574110990811</v>
       </c>
       <c r="T56">
-        <v>1.305988891424127</v>
+        <v>1.301273005188555</v>
       </c>
       <c r="U56">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V56">
-        <v>0.1032898799307755</v>
+        <v>0.109603884122982</v>
       </c>
       <c r="W56">
-        <v>0.233487916146661</v>
+        <v>0.218487916146661</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4131595197231019</v>
+        <v>0.4384155364919282</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.2114172329325202</v>
+        <v>0.2029437120957057</v>
       </c>
       <c r="C57">
-        <v>343.5408607021354</v>
+        <v>496.4807998700771</v>
       </c>
       <c r="D57">
-        <v>2835.725860702136</v>
+        <v>2988.665799870078</v>
       </c>
       <c r="E57">
         <v>1739.985000000001</v>
@@ -5967,37 +5967,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M57">
-        <v>1265.795131605515</v>
+        <v>1192.875856605515</v>
       </c>
       <c r="N57">
-        <v>-752.3284649388484</v>
+        <v>-679.4091899388484</v>
       </c>
       <c r="O57">
-        <v>-188.0821162347121</v>
+        <v>-169.8522974847121</v>
       </c>
       <c r="P57">
-        <v>-564.2463487041363</v>
+        <v>-509.5568924541363</v>
       </c>
       <c r="Q57">
-        <v>-472.2463487041363</v>
+        <v>-417.5568924541363</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1838442887608706</v>
+        <v>0.1833475757901718</v>
       </c>
       <c r="T57">
-        <v>1.335010866789108</v>
+        <v>1.330190183081635</v>
       </c>
       <c r="U57">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V57">
-        <v>0.1014118821138523</v>
+        <v>0.1076110862298369</v>
       </c>
       <c r="W57">
-        <v>0.2339769145275063</v>
+        <v>0.2189769145275063</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4056475284554093</v>
+        <v>0.4304443449193477</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2135630612034517</v>
+        <v>0.2049395403666373</v>
       </c>
       <c r="C58">
-        <v>218.8825821688561</v>
+        <v>370.6118285007715</v>
       </c>
       <c r="D58">
-        <v>2799.454582168857</v>
+        <v>2951.183828500772</v>
       </c>
       <c r="E58">
         <v>1828.372</v>
@@ -6049,37 +6049,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M58">
-        <v>1288.809588543797</v>
+        <v>1214.564508543797</v>
       </c>
       <c r="N58">
-        <v>-775.3429218771305</v>
+        <v>-701.0978418771306</v>
       </c>
       <c r="O58">
-        <v>-193.8357304692826</v>
+        <v>-175.2744604692826</v>
       </c>
       <c r="P58">
-        <v>-581.5071914078478</v>
+        <v>-525.8233814078479</v>
       </c>
       <c r="Q58">
-        <v>-489.5071914078478</v>
+        <v>-433.8233814078479</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1869816589599813</v>
+        <v>0.1864736570581303</v>
       </c>
       <c r="T58">
-        <v>1.365352022852497</v>
+        <v>1.360421778151672</v>
       </c>
       <c r="U58">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V58">
-        <v>0.09960095564753352</v>
+        <v>0.1056894596900184</v>
       </c>
       <c r="W58">
-        <v>0.2344484486804642</v>
+        <v>0.2194484486804642</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3984038225901341</v>
+        <v>0.4227578387600737</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2157088894743832</v>
+        <v>0.2069353686375687</v>
       </c>
       <c r="C59">
-        <v>95.14046446907014</v>
+        <v>245.6713631291441</v>
       </c>
       <c r="D59">
-        <v>2764.099464469071</v>
+        <v>2914.630363129145</v>
       </c>
       <c r="E59">
         <v>1916.759000000001</v>
@@ -6131,37 +6131,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M59">
-        <v>1311.824045482079</v>
+        <v>1236.253160482079</v>
       </c>
       <c r="N59">
-        <v>-798.3573788154126</v>
+        <v>-722.7864938154128</v>
       </c>
       <c r="O59">
-        <v>-199.5893447038532</v>
+        <v>-180.6966234538532</v>
       </c>
       <c r="P59">
-        <v>-598.7680341115595</v>
+        <v>-542.0898703615596</v>
       </c>
       <c r="Q59">
-        <v>-506.7680341115595</v>
+        <v>-450.0898703615596</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1902649533543995</v>
+        <v>0.189745137454831</v>
       </c>
       <c r="T59">
-        <v>1.397104395476974</v>
+        <v>1.392059493922641</v>
       </c>
       <c r="U59">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V59">
-        <v>0.09785357046073469</v>
+        <v>0.1038352586428251</v>
       </c>
       <c r="W59">
-        <v>0.2349034377754235</v>
+        <v>0.2199034377754235</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3914142818429387</v>
+        <v>0.4153410345713003</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.2178547177453146</v>
+        <v>0.2089311969085002</v>
       </c>
       <c r="C60">
-        <v>-27.71977086123843</v>
+        <v>121.6253243414194</v>
       </c>
       <c r="D60">
-        <v>2729.626229138762</v>
+        <v>2878.971324341419</v>
       </c>
       <c r="E60">
         <v>2005.146</v>
@@ -6213,37 +6213,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M60">
-        <v>1334.838502420361</v>
+        <v>1257.941812420361</v>
       </c>
       <c r="N60">
-        <v>-821.3718357536945</v>
+        <v>-744.4751457536945</v>
       </c>
       <c r="O60">
-        <v>-205.3429589384236</v>
+        <v>-186.1187864384236</v>
       </c>
       <c r="P60">
-        <v>-616.0288768152709</v>
+        <v>-558.3563593152709</v>
       </c>
       <c r="Q60">
-        <v>-524.0288768152709</v>
+        <v>-466.3563593152709</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1937045951009327</v>
+        <v>0.1931724026323269</v>
       </c>
       <c r="T60">
-        <v>1.430368785845473</v>
+        <v>1.425203767587465</v>
       </c>
       <c r="U60">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V60">
-        <v>0.09616643993554962</v>
+        <v>0.1020449955627764</v>
       </c>
       <c r="W60">
-        <v>0.2353427375912464</v>
+        <v>0.2203427375912464</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3846657597421985</v>
+        <v>0.4081799822511056</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.2200005460162461</v>
+        <v>0.2109270251794317</v>
       </c>
       <c r="C61">
-        <v>-149.7307132971937</v>
+        <v>-1.558719655939967</v>
       </c>
       <c r="D61">
-        <v>2696.002286702807</v>
+        <v>2844.174280344061</v>
       </c>
       <c r="E61">
         <v>2093.533</v>
@@ -6295,37 +6295,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M61">
-        <v>1357.852959358643</v>
+        <v>1279.630464358643</v>
       </c>
       <c r="N61">
-        <v>-844.3862926919767</v>
+        <v>-766.1637976919767</v>
       </c>
       <c r="O61">
-        <v>-211.0965731729942</v>
+        <v>-191.5409494229942</v>
       </c>
       <c r="P61">
-        <v>-633.2897195189826</v>
+        <v>-574.6228482689826</v>
       </c>
       <c r="Q61">
-        <v>-541.2897195189826</v>
+        <v>-482.6228482689826</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.197312024249736</v>
+        <v>0.1967668514770178</v>
       </c>
       <c r="T61">
-        <v>1.465255829402679</v>
+        <v>1.459964835089599</v>
       </c>
       <c r="U61">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V61">
-        <v>0.09453650027562505</v>
+        <v>0.1003154193667971</v>
       </c>
       <c r="W61">
-        <v>0.2357671458878887</v>
+        <v>0.2207671458878888</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3781460011025002</v>
+        <v>0.4012616774671885</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.2221463742871776</v>
+        <v>0.2129228534503632</v>
       </c>
       <c r="C62">
-        <v>-270.9233660852778</v>
+        <v>-123.9116514179468</v>
       </c>
       <c r="D62">
-        <v>2663.196633914722</v>
+        <v>2810.208348582054</v>
       </c>
       <c r="E62">
         <v>2181.92</v>
@@ -6377,37 +6377,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M62">
-        <v>1380.867416296926</v>
+        <v>1301.319116296926</v>
       </c>
       <c r="N62">
-        <v>-867.4007496302588</v>
+        <v>-787.8524496302589</v>
       </c>
       <c r="O62">
-        <v>-216.8501874075647</v>
+        <v>-196.9631124075647</v>
       </c>
       <c r="P62">
-        <v>-650.5505622226941</v>
+        <v>-590.8893372226942</v>
       </c>
       <c r="Q62">
-        <v>-558.5505622226941</v>
+        <v>-498.8893372226942</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.2010998248559794</v>
+        <v>0.2005410227639432</v>
       </c>
       <c r="T62">
-        <v>1.501887225137746</v>
+        <v>1.496463955966838</v>
       </c>
       <c r="U62">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V62">
-        <v>0.09296089193769796</v>
+        <v>0.09864349571068384</v>
       </c>
       <c r="W62">
-        <v>0.2361774072413098</v>
+        <v>0.2211774072413098</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3718435677507919</v>
+        <v>0.3945739828427354</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.2242922025581091</v>
+        <v>0.2149186817212946</v>
       </c>
       <c r="C63">
-        <v>-391.3272415913289</v>
+        <v>-245.4628956766073</v>
       </c>
       <c r="D63">
-        <v>2631.179758408671</v>
+        <v>2777.044104323393</v>
       </c>
       <c r="E63">
         <v>2270.307</v>
@@ -6459,37 +6459,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M63">
-        <v>1403.881873235207</v>
+        <v>1323.007768235208</v>
       </c>
       <c r="N63">
-        <v>-890.4152065685407</v>
+        <v>-809.5411015685409</v>
       </c>
       <c r="O63">
-        <v>-222.6038016421352</v>
+        <v>-202.3852753921352</v>
       </c>
       <c r="P63">
-        <v>-667.8114049264055</v>
+        <v>-607.1558261764056</v>
       </c>
       <c r="Q63">
-        <v>-575.8114049264055</v>
+        <v>-515.1558261764056</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.2050818716471584</v>
+        <v>0.204508741296352</v>
       </c>
       <c r="T63">
-        <v>1.540397153987432</v>
+        <v>1.534834826632655</v>
       </c>
       <c r="U63">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V63">
-        <v>0.09143694288953899</v>
+        <v>0.09702638922362347</v>
       </c>
       <c r="W63">
-        <v>0.2365742174028153</v>
+        <v>0.2215742174028153</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.365747771558156</v>
+        <v>0.3881055568944939</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2264380308290406</v>
+        <v>0.2169145099922261</v>
       </c>
       <c r="C64">
-        <v>-510.9704498525862</v>
+        <v>-366.2405043589688</v>
       </c>
       <c r="D64">
-        <v>2599.923550147414</v>
+        <v>2744.653495641032</v>
       </c>
       <c r="E64">
         <v>2358.694</v>
@@ -6541,37 +6541,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M64">
-        <v>1426.89633017349</v>
+        <v>1344.69642017349</v>
       </c>
       <c r="N64">
-        <v>-913.4296635068231</v>
+        <v>-831.229753506823</v>
       </c>
       <c r="O64">
-        <v>-228.3574158767058</v>
+        <v>-207.8074383767058</v>
       </c>
       <c r="P64">
-        <v>-685.0722476301173</v>
+        <v>-623.4223151301173</v>
       </c>
       <c r="Q64">
-        <v>-593.0722476301173</v>
+        <v>-531.4223151301173</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.2092734998483994</v>
+        <v>0.2086852871199403</v>
       </c>
       <c r="T64">
-        <v>1.580933921197628</v>
+        <v>1.575225216807199</v>
       </c>
       <c r="U64">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V64">
-        <v>0.08996215348809479</v>
+        <v>0.09546144746195211</v>
       </c>
       <c r="W64">
-        <v>0.2369582272365303</v>
+        <v>0.2219582272365304</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3598486139523792</v>
+        <v>0.3818457898478085</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2285838590999721</v>
+        <v>0.2189103382631576</v>
       </c>
       <c r="C65">
-        <v>-629.8797808923073</v>
+        <v>-486.2712357240134</v>
       </c>
       <c r="D65">
-        <v>2569.401219107693</v>
+        <v>2713.009764275987</v>
       </c>
       <c r="E65">
         <v>2447.081</v>
@@ -6623,37 +6623,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M65">
-        <v>1449.910787111772</v>
+        <v>1366.385072111772</v>
       </c>
       <c r="N65">
-        <v>-936.444120445105</v>
+        <v>-852.918405445105</v>
       </c>
       <c r="O65">
-        <v>-234.1110301112762</v>
+        <v>-213.2296013612763</v>
       </c>
       <c r="P65">
-        <v>-702.3330903338287</v>
+        <v>-639.6888040838287</v>
       </c>
       <c r="Q65">
-        <v>-610.3330903338287</v>
+        <v>-547.6888040838287</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.2136917025470048</v>
+        <v>0.2130875921772359</v>
       </c>
       <c r="T65">
-        <v>1.62366186501378</v>
+        <v>1.617798871315501</v>
       </c>
       <c r="U65">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V65">
-        <v>0.08853418279780759</v>
+        <v>0.09394618639112748</v>
       </c>
       <c r="W65">
-        <v>0.2373300462818735</v>
+        <v>0.2223300462818735</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3541367311912303</v>
+        <v>0.3757847455645099</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2307296873709035</v>
+        <v>0.2209061665340891</v>
       </c>
       <c r="C66">
-        <v>-748.0807813035499</v>
+        <v>-605.5806280876259</v>
       </c>
       <c r="D66">
-        <v>2539.587218696451</v>
+        <v>2682.087371912375</v>
       </c>
       <c r="E66">
         <v>2535.468000000001</v>
@@ -6705,37 +6705,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M66">
-        <v>1472.925244050054</v>
+        <v>1388.073724050054</v>
       </c>
       <c r="N66">
-        <v>-959.4585773833874</v>
+        <v>-874.6070573833874</v>
       </c>
       <c r="O66">
-        <v>-239.8646443458468</v>
+        <v>-218.6517643458469</v>
       </c>
       <c r="P66">
-        <v>-719.5939330375405</v>
+        <v>-655.9552930375405</v>
       </c>
       <c r="Q66">
-        <v>-627.5939330375405</v>
+        <v>-563.9552930375405</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.2183553609510882</v>
+        <v>0.2177344697377147</v>
       </c>
       <c r="T66">
-        <v>1.668763583486385</v>
+        <v>1.662737728852043</v>
       </c>
       <c r="U66">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V66">
-        <v>0.08715083619159182</v>
+        <v>0.0924782772287661</v>
       </c>
       <c r="W66">
-        <v>0.2376902459820497</v>
+        <v>0.2226902459820497</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3486033447663673</v>
+        <v>0.3699131089150643</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2328755156418351</v>
+        <v>0.2229019948050205</v>
       </c>
       <c r="C67">
-        <v>-865.5978255622995</v>
+        <v>-724.1930685625584</v>
       </c>
       <c r="D67">
-        <v>2510.457174437701</v>
+        <v>2651.861931437442</v>
       </c>
       <c r="E67">
         <v>2623.855</v>
@@ -6787,37 +6787,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M67">
-        <v>1495.939700988336</v>
+        <v>1409.762375988336</v>
       </c>
       <c r="N67">
-        <v>-982.4730343216693</v>
+        <v>-896.2957093216694</v>
       </c>
       <c r="O67">
-        <v>-245.6182585804173</v>
+        <v>-224.0739273304173</v>
       </c>
       <c r="P67">
-        <v>-736.854775741252</v>
+        <v>-672.2217819912521</v>
       </c>
       <c r="Q67">
-        <v>-644.854775741252</v>
+        <v>-580.2217819912521</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2232855141211194</v>
+        <v>0.2226468831587923</v>
       </c>
       <c r="T67">
-        <v>1.716442543014568</v>
+        <v>1.710244521104959</v>
       </c>
       <c r="U67">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V67">
-        <v>0.08581005409633657</v>
+        <v>0.0910555345021697</v>
       </c>
       <c r="W67">
-        <v>0.2380393626145281</v>
+        <v>0.2230393626145281</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3432402163853463</v>
+        <v>0.3642221380086789</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2350213439127665</v>
+        <v>0.224897823075952</v>
       </c>
       <c r="C68">
-        <v>-982.4541824883063</v>
+        <v>-842.1318572022519</v>
       </c>
       <c r="D68">
-        <v>2481.987817511695</v>
+        <v>2622.310142797749</v>
       </c>
       <c r="E68">
         <v>2712.242</v>
@@ -6869,37 +6869,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M68">
-        <v>1518.954157926618</v>
+        <v>1431.451027926618</v>
       </c>
       <c r="N68">
-        <v>-1005.487491259951</v>
+        <v>-917.9843612599514</v>
       </c>
       <c r="O68">
-        <v>-251.3718728149879</v>
+        <v>-229.4960903149878</v>
       </c>
       <c r="P68">
-        <v>-754.1156184449635</v>
+        <v>-688.4882709449635</v>
       </c>
       <c r="Q68">
-        <v>-662.1156184449635</v>
+        <v>-596.4882709449635</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2285056763011523</v>
+        <v>0.2278482620752273</v>
       </c>
       <c r="T68">
-        <v>1.766926147220878</v>
+        <v>1.760545830549222</v>
       </c>
       <c r="U68">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V68">
-        <v>0.08450990176154359</v>
+        <v>0.08967590519153078</v>
       </c>
       <c r="W68">
-        <v>0.2383778999551132</v>
+        <v>0.2233778999551133</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3380396070461744</v>
+        <v>0.3587036207661231</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.237167172183698</v>
+        <v>0.2268936513468836</v>
       </c>
       <c r="C69">
-        <v>-1098.672077234515</v>
+        <v>-959.4192669030936</v>
       </c>
       <c r="D69">
-        <v>2454.156922765486</v>
+        <v>2593.409733096907</v>
       </c>
       <c r="E69">
         <v>2800.629000000001</v>
@@ -6951,37 +6951,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M69">
-        <v>1541.9686148649</v>
+        <v>1453.1396798649</v>
       </c>
       <c r="N69">
-        <v>-1028.501948198234</v>
+        <v>-939.6730131982335</v>
       </c>
       <c r="O69">
-        <v>-257.1254870495584</v>
+        <v>-234.9182532995584</v>
       </c>
       <c r="P69">
-        <v>-771.3764611486752</v>
+        <v>-704.7547598986752</v>
       </c>
       <c r="Q69">
-        <v>-679.3764611486752</v>
+        <v>-612.7547598986752</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2340422119466417</v>
+        <v>0.233364876077507</v>
       </c>
       <c r="T69">
-        <v>1.820469363803329</v>
+        <v>1.813895704202229</v>
       </c>
       <c r="U69">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V69">
-        <v>0.08324855994420713</v>
+        <v>0.08833745884538852</v>
       </c>
       <c r="W69">
-        <v>0.2387063317034421</v>
+        <v>0.2237063317034421</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3329942397768285</v>
+        <v>0.3533498353815541</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2393130004546295</v>
+        <v>0.228889479617815</v>
       </c>
       <c r="C70">
-        <v>-1214.272749152165</v>
+        <v>-1076.076599388762</v>
       </c>
       <c r="D70">
-        <v>2426.943250847836</v>
+        <v>2565.139400611239</v>
       </c>
       <c r="E70">
         <v>2889.016000000001</v>
@@ -7033,37 +7033,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M70">
-        <v>1564.983071803182</v>
+        <v>1474.828331803182</v>
       </c>
       <c r="N70">
-        <v>-1051.516405136516</v>
+        <v>-961.3616651365157</v>
       </c>
       <c r="O70">
-        <v>-262.8791012841289</v>
+        <v>-240.3404162841289</v>
       </c>
       <c r="P70">
-        <v>-788.6373038523868</v>
+        <v>-721.0212488523869</v>
       </c>
       <c r="Q70">
-        <v>-696.6373038523868</v>
+        <v>-629.0212488523869</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2399247810699743</v>
+        <v>0.2392262784549291</v>
       </c>
       <c r="T70">
-        <v>1.877359031422184</v>
+        <v>1.870579944958549</v>
       </c>
       <c r="U70">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V70">
-        <v>0.08202431641561583</v>
+        <v>0.08703837856825045</v>
       </c>
       <c r="W70">
-        <v>0.2390251036944672</v>
+        <v>0.2240251036944672</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3280972656624633</v>
+        <v>0.3481535142730018</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.241458828725561</v>
+        <v>0.2308853078887465</v>
       </c>
       <c r="C71">
-        <v>-1329.276505848182</v>
+        <v>-1192.124237572413</v>
       </c>
       <c r="D71">
-        <v>2400.32649415182</v>
+        <v>2537.478762427588</v>
       </c>
       <c r="E71">
         <v>2977.403000000001</v>
@@ -7115,37 +7115,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M71">
-        <v>1587.997528741465</v>
+        <v>1496.516983741465</v>
       </c>
       <c r="N71">
-        <v>-1074.530862074798</v>
+        <v>-983.0503170747979</v>
       </c>
       <c r="O71">
-        <v>-268.6327155186995</v>
+        <v>-245.7625792686995</v>
       </c>
       <c r="P71">
-        <v>-805.8981465560984</v>
+        <v>-737.2877378060984</v>
       </c>
       <c r="Q71">
-        <v>-713.8981465560984</v>
+        <v>-645.2877378060984</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.246186870781909</v>
+        <v>0.2454658358244429</v>
       </c>
       <c r="T71">
-        <v>1.937919000177738</v>
+        <v>1.930921233505599</v>
       </c>
       <c r="U71">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V71">
-        <v>0.08083555820669387</v>
+        <v>0.08577695279189898</v>
       </c>
       <c r="W71">
-        <v>0.2393346359176365</v>
+        <v>0.2243346359176365</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3233422328267754</v>
+        <v>0.3431078111675959</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2436046569964924</v>
+        <v>0.232881136159678</v>
       </c>
       <c r="C72">
-        <v>-1443.702773724003</v>
+        <v>-1307.581694567171</v>
       </c>
       <c r="D72">
-        <v>2374.287226275997</v>
+        <v>2510.408305432829</v>
       </c>
       <c r="E72">
         <v>3065.790000000001</v>
@@ -7197,37 +7197,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M72">
-        <v>1611.011985679746</v>
+        <v>1518.205635679747</v>
       </c>
       <c r="N72">
-        <v>-1097.54531901308</v>
+        <v>-1004.73896901308</v>
       </c>
       <c r="O72">
-        <v>-274.3863297532699</v>
+        <v>-251.18474225327</v>
       </c>
       <c r="P72">
-        <v>-823.1589892598098</v>
+        <v>-753.5542267598099</v>
       </c>
       <c r="Q72">
-        <v>-731.1589892598098</v>
+        <v>-661.5542267598099</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2528664331413059</v>
+        <v>0.2521213636852577</v>
       </c>
       <c r="T72">
-        <v>2.002516300183662</v>
+        <v>1.995285274622452</v>
       </c>
       <c r="U72">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V72">
-        <v>0.07968076451802682</v>
+        <v>0.08455156775201472</v>
       </c>
       <c r="W72">
-        <v>0.2396353243630009</v>
+        <v>0.224635324363001</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3187230580721073</v>
+        <v>0.3382062710080589</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2457504852674239</v>
+        <v>0.2348769644306095</v>
       </c>
       <c r="C73">
-        <v>-1557.570145260189</v>
+        <v>-1422.467659592616</v>
       </c>
       <c r="D73">
-        <v>2348.806854739812</v>
+        <v>2483.909340407384</v>
       </c>
       <c r="E73">
         <v>3154.177</v>
@@ -7279,37 +7279,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M73">
-        <v>1634.026442618028</v>
+        <v>1539.894287618028</v>
       </c>
       <c r="N73">
-        <v>-1120.559775951362</v>
+        <v>-1026.427620951362</v>
       </c>
       <c r="O73">
-        <v>-280.1399439878404</v>
+        <v>-256.6069052378404</v>
       </c>
       <c r="P73">
-        <v>-840.4198319635212</v>
+        <v>-769.8207157135212</v>
       </c>
       <c r="Q73">
-        <v>-748.4198319635212</v>
+        <v>-677.8207157135212</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2600066549737647</v>
+        <v>0.2592358934675079</v>
       </c>
       <c r="T73">
-        <v>2.071568586396892</v>
+        <v>2.064088215126674</v>
       </c>
       <c r="U73">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V73">
-        <v>0.07855850022904054</v>
+        <v>0.08336070060057792</v>
       </c>
       <c r="W73">
-        <v>0.2399275427113129</v>
+        <v>0.2249275427113129</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3142340009161622</v>
+        <v>0.3334428024023116</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2478963135383554</v>
+        <v>0.2368727927015409</v>
       </c>
       <c r="C74">
-        <v>-1670.896423288641</v>
+        <v>-1536.800041004189</v>
       </c>
       <c r="D74">
-        <v>2323.86757671136</v>
+        <v>2457.963958995812</v>
       </c>
       <c r="E74">
         <v>3242.564</v>
@@ -7361,37 +7361,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M74">
-        <v>1657.04089955631</v>
+        <v>1561.582939556311</v>
       </c>
       <c r="N74">
-        <v>-1143.574232889644</v>
+        <v>-1048.116272889644</v>
       </c>
       <c r="O74">
-        <v>-285.8935582224109</v>
+        <v>-262.029068222411</v>
       </c>
       <c r="P74">
-        <v>-857.6806746672328</v>
+        <v>-786.087204667233</v>
       </c>
       <c r="Q74">
-        <v>-765.6806746672328</v>
+        <v>-694.087204667233</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2676568926513991</v>
+        <v>0.2668586039484903</v>
       </c>
       <c r="T74">
-        <v>2.145553178768209</v>
+        <v>2.137805651381198</v>
       </c>
       <c r="U74">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V74">
-        <v>0.07746740994808164</v>
+        <v>0.08220291309223654</v>
       </c>
       <c r="W74">
-        <v>0.2402116438832828</v>
+        <v>0.2252116438832828</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3098696397923265</v>
+        <v>0.3288116523689462</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2500421418092869</v>
+        <v>0.2388686209724724</v>
       </c>
       <c r="C75">
-        <v>-1783.698662474022</v>
+        <v>-1650.596006653734</v>
       </c>
       <c r="D75">
-        <v>2299.452337525979</v>
+        <v>2432.554993346267</v>
       </c>
       <c r="E75">
         <v>3330.951</v>
@@ -7443,37 +7443,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M75">
-        <v>1680.055356494593</v>
+        <v>1583.271591494593</v>
       </c>
       <c r="N75">
-        <v>-1166.588689827926</v>
+        <v>-1069.804924827926</v>
       </c>
       <c r="O75">
-        <v>-291.6471724569815</v>
+        <v>-267.4512312069815</v>
       </c>
       <c r="P75">
-        <v>-874.9415173709444</v>
+        <v>-802.3536936209446</v>
       </c>
       <c r="Q75">
-        <v>-782.9415173709444</v>
+        <v>-710.3536936209446</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2758738146014509</v>
+        <v>0.2750459596502863</v>
       </c>
       <c r="T75">
-        <v>2.22501811131518</v>
+        <v>2.216983638469391</v>
       </c>
       <c r="U75">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V75">
-        <v>0.07640621255153257</v>
+        <v>0.08107684578960317</v>
       </c>
       <c r="W75">
-        <v>0.2404879614615002</v>
+        <v>0.2254879614615002</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3056248502061303</v>
+        <v>0.3243073831584127</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2521879700802184</v>
+        <v>0.2408644492434039</v>
       </c>
       <c r="C76">
-        <v>-1895.993208207454</v>
+        <v>-1763.872021772311</v>
       </c>
       <c r="D76">
-        <v>2275.544791792548</v>
+        <v>2407.66597822769</v>
       </c>
       <c r="E76">
         <v>3419.338000000001</v>
@@ -7525,37 +7525,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M76">
-        <v>1703.069813432875</v>
+        <v>1604.960243432875</v>
       </c>
       <c r="N76">
-        <v>-1189.603146766208</v>
+        <v>-1091.493576766208</v>
       </c>
       <c r="O76">
-        <v>-297.400786691552</v>
+        <v>-272.8733941915521</v>
       </c>
       <c r="P76">
-        <v>-892.2023600746561</v>
+        <v>-818.6201825746562</v>
       </c>
       <c r="Q76">
-        <v>-800.2023600746561</v>
+        <v>-726.6201825746562</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2847228074707375</v>
+        <v>0.2838631119445281</v>
       </c>
       <c r="T76">
-        <v>2.310595730981148</v>
+        <v>2.302252239948983</v>
       </c>
       <c r="U76">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V76">
-        <v>0.07537369616570105</v>
+        <v>0.0799812127383923</v>
       </c>
       <c r="W76">
-        <v>0.240756810997063</v>
+        <v>0.225756810997063</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3014947846628042</v>
+        <v>0.3199248509535693</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2543337983511498</v>
+        <v>0.2428602775143354</v>
       </c>
       <c r="C77">
-        <v>-2007.7957330989</v>
+        <v>-1876.643884550945</v>
       </c>
       <c r="D77">
-        <v>2252.129266901101</v>
+        <v>2383.281115449056</v>
       </c>
       <c r="E77">
         <v>3507.725</v>
@@ -7607,37 +7607,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M77">
-        <v>1726.084270371157</v>
+        <v>1626.648895371157</v>
       </c>
       <c r="N77">
-        <v>-1212.61760370449</v>
+        <v>-1113.18222870449</v>
       </c>
       <c r="O77">
-        <v>-303.1544009261225</v>
+        <v>-278.2955571761225</v>
       </c>
       <c r="P77">
-        <v>-909.4632027783676</v>
+        <v>-834.8866715283676</v>
       </c>
       <c r="Q77">
-        <v>-817.4632027783676</v>
+        <v>-742.8866715283676</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.294279719769567</v>
+        <v>0.2933856364223092</v>
       </c>
       <c r="T77">
-        <v>2.403019560220394</v>
+        <v>2.394342329546942</v>
       </c>
       <c r="U77">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V77">
-        <v>0.07436871355015837</v>
+        <v>0.07891479656854708</v>
       </c>
       <c r="W77">
-        <v>0.2410184912116774</v>
+        <v>0.2260184912116775</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2974748542006335</v>
+        <v>0.3156591862741883</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2564796266220813</v>
+        <v>0.2448561057852669</v>
       </c>
       <c r="C78">
-        <v>-2119.121271239455</v>
+        <v>-1988.92675958088</v>
       </c>
       <c r="D78">
-        <v>2229.190728760545</v>
+        <v>2359.38524041912</v>
       </c>
       <c r="E78">
         <v>3596.112</v>
@@ -7689,37 +7689,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M78">
-        <v>1749.098727309439</v>
+        <v>1648.337547309439</v>
       </c>
       <c r="N78">
-        <v>-1235.632060642772</v>
+        <v>-1134.870880642772</v>
       </c>
       <c r="O78">
-        <v>-308.908015160693</v>
+        <v>-283.7177201606931</v>
       </c>
       <c r="P78">
-        <v>-926.7240454820791</v>
+        <v>-851.1531604820793</v>
       </c>
       <c r="Q78">
-        <v>-834.7240454820791</v>
+        <v>-759.1531604820793</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.3046330414266324</v>
+        <v>0.3037017046065721</v>
       </c>
       <c r="T78">
-        <v>2.503145375229578</v>
+        <v>2.494106593278065</v>
       </c>
       <c r="U78">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V78">
-        <v>0.07339017784555103</v>
+        <v>0.07787644398211883</v>
       </c>
       <c r="W78">
-        <v>0.2412732851048547</v>
+        <v>0.2262732851048547</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2935607113822041</v>
+        <v>0.3115057759284753</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2586254548930128</v>
+        <v>0.2468519340561984</v>
       </c>
       <c r="C79">
-        <v>-2229.984250390903</v>
+        <v>-2100.735209302079</v>
       </c>
       <c r="D79">
-        <v>2206.714749609098</v>
+        <v>2335.963790697922</v>
       </c>
       <c r="E79">
         <v>3684.499000000001</v>
@@ -7771,37 +7771,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M79">
-        <v>1772.113184247721</v>
+        <v>1670.026199247721</v>
       </c>
       <c r="N79">
-        <v>-1258.646517581054</v>
+        <v>-1156.559532581055</v>
       </c>
       <c r="O79">
-        <v>-314.6616293952636</v>
+        <v>-289.1398831452636</v>
       </c>
       <c r="P79">
-        <v>-943.9848881857909</v>
+        <v>-867.4196494357909</v>
       </c>
       <c r="Q79">
-        <v>-851.9848881857909</v>
+        <v>-775.4196494357909</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.3158866519234425</v>
+        <v>0.3149148221981622</v>
       </c>
       <c r="T79">
-        <v>2.611977782848255</v>
+        <v>2.602546010377111</v>
       </c>
       <c r="U79">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V79">
-        <v>0.07243705865275166</v>
+        <v>0.07686506159274066</v>
       </c>
       <c r="W79">
-        <v>0.2415214609748325</v>
+        <v>0.2265214609748326</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2897482346110066</v>
+        <v>0.3074602463709626</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2607712831639443</v>
+        <v>0.2488477623271299</v>
       </c>
       <c r="C80">
-        <v>-2340.398522247402</v>
+        <v>-2212.083223597011</v>
       </c>
       <c r="D80">
-        <v>2184.687477752599</v>
+        <v>2313.00277640299</v>
       </c>
       <c r="E80">
         <v>3772.886</v>
@@ -7853,37 +7853,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M80">
-        <v>1795.127641186003</v>
+        <v>1691.714851186003</v>
       </c>
       <c r="N80">
-        <v>-1281.660974519336</v>
+        <v>-1178.248184519337</v>
       </c>
       <c r="O80">
-        <v>-320.4152436298341</v>
+        <v>-294.5620461298341</v>
       </c>
       <c r="P80">
-        <v>-961.2457308895023</v>
+        <v>-883.6861383895024</v>
       </c>
       <c r="Q80">
-        <v>-869.2457308895023</v>
+        <v>-791.6861383895024</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.3281633179199626</v>
+        <v>0.3271473141162605</v>
       </c>
       <c r="T80">
-        <v>2.730704045704994</v>
+        <v>2.720843556303344</v>
       </c>
       <c r="U80">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V80">
-        <v>0.07150837841361382</v>
+        <v>0.07587961208514142</v>
       </c>
       <c r="W80">
-        <v>0.2417632733609648</v>
+        <v>0.2267632733609648</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2860335136544553</v>
+        <v>0.3035184483405657</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2629171114348758</v>
+        <v>0.2508435905980613</v>
       </c>
       <c r="C81">
-        <v>-2450.377390902664</v>
+        <v>-2322.984247656107</v>
       </c>
       <c r="D81">
-        <v>2163.095609097337</v>
+        <v>2290.488752343894</v>
       </c>
       <c r="E81">
         <v>3861.273000000001</v>
@@ -7935,37 +7935,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M81">
-        <v>1818.142098124285</v>
+        <v>1713.403503124285</v>
       </c>
       <c r="N81">
-        <v>-1304.675431457619</v>
+        <v>-1199.936836457619</v>
       </c>
       <c r="O81">
-        <v>-326.1688578644047</v>
+        <v>-299.9842091144047</v>
       </c>
       <c r="P81">
-        <v>-978.5065735932141</v>
+        <v>-899.9526273432141</v>
       </c>
       <c r="Q81">
-        <v>-886.5065735932141</v>
+        <v>-807.9526273432141</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.3416091902018656</v>
+        <v>0.3405448052646539</v>
       </c>
       <c r="T81">
-        <v>2.860737571690946</v>
+        <v>2.850407535174932</v>
       </c>
       <c r="U81">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V81">
-        <v>0.07060320906660604</v>
+        <v>0.07491911066634216</v>
       </c>
       <c r="W81">
-        <v>0.2419989639145367</v>
+        <v>0.2269989639145367</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2824128362664241</v>
+        <v>0.2996764426653686</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2650629397058073</v>
+        <v>0.2528394188689928</v>
       </c>
       <c r="C82">
-        <v>-2559.933639645551</v>
+        <v>-2433.451208231494</v>
       </c>
       <c r="D82">
-        <v>2141.92636035445</v>
+        <v>2268.408791768507</v>
       </c>
       <c r="E82">
         <v>3949.660000000001</v>
@@ -8017,37 +8017,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M82">
-        <v>1841.156555062567</v>
+        <v>1735.092155062568</v>
       </c>
       <c r="N82">
-        <v>-1327.689888395901</v>
+        <v>-1221.625488395901</v>
       </c>
       <c r="O82">
-        <v>-331.9224720989752</v>
+        <v>-305.4063720989752</v>
       </c>
       <c r="P82">
-        <v>-995.7674162969255</v>
+        <v>-916.2191162969257</v>
       </c>
       <c r="Q82">
-        <v>-903.7674162969255</v>
+        <v>-824.2191162969257</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3563996497119589</v>
+        <v>0.3552820455278866</v>
       </c>
       <c r="T82">
-        <v>3.003774450275494</v>
+        <v>2.992927911933678</v>
       </c>
       <c r="U82">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V82">
-        <v>0.06972066895327347</v>
+        <v>0.07398262178301288</v>
       </c>
       <c r="W82">
-        <v>0.2422287622042694</v>
+        <v>0.2272287622042694</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2788826758130939</v>
+        <v>0.2959304871320515</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2672087679767388</v>
+        <v>0.2548352471399243</v>
       </c>
       <c r="C83">
-        <v>-2669.079556197513</v>
+        <v>-2543.496538386747</v>
       </c>
       <c r="D83">
-        <v>2121.167443802487</v>
+        <v>2246.750461613255</v>
       </c>
       <c r="E83">
         <v>4038.047</v>
@@ -8099,37 +8099,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M83">
-        <v>1864.171012000849</v>
+        <v>1756.78080700085</v>
       </c>
       <c r="N83">
-        <v>-1350.704345334183</v>
+        <v>-1243.314140334183</v>
       </c>
       <c r="O83">
-        <v>-337.6760863335457</v>
+        <v>-310.8285350835457</v>
       </c>
       <c r="P83">
-        <v>-1013.028259000637</v>
+        <v>-932.4856052506371</v>
       </c>
       <c r="Q83">
-        <v>-921.028259000637</v>
+        <v>-840.4856052506371</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3727469996967989</v>
+        <v>0.3715705742398807</v>
       </c>
       <c r="T83">
-        <v>3.161867842395257</v>
+        <v>3.150450433614399</v>
       </c>
       <c r="U83">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V83">
-        <v>0.06885991995385034</v>
+        <v>0.07306925608198804</v>
       </c>
       <c r="W83">
-        <v>0.2424528864621568</v>
+        <v>0.2274528864621568</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2754396798154014</v>
+        <v>0.2922770243279521</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2693545962476702</v>
+        <v>0.2568310754108558</v>
       </c>
       <c r="C84">
-        <v>-2777.826956496545</v>
+        <v>-2653.132200842197</v>
       </c>
       <c r="D84">
-        <v>2100.807043503456</v>
+        <v>2225.501799157804</v>
       </c>
       <c r="E84">
         <v>4126.434000000001</v>
@@ -8181,37 +8181,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M84">
-        <v>1887.185468939132</v>
+        <v>1778.469458939132</v>
       </c>
       <c r="N84">
-        <v>-1373.718802272465</v>
+        <v>-1265.002792272465</v>
       </c>
       <c r="O84">
-        <v>-343.4297005681162</v>
+        <v>-316.2506980681163</v>
       </c>
       <c r="P84">
-        <v>-1030.289101704349</v>
+        <v>-948.7520942043489</v>
       </c>
       <c r="Q84">
-        <v>-938.2891017043487</v>
+        <v>-856.7520942043489</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3909107219021766</v>
+        <v>0.3896689394754295</v>
       </c>
       <c r="T84">
-        <v>3.337527166972771</v>
+        <v>3.325475457704087</v>
       </c>
       <c r="U84">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V84">
-        <v>0.06802016483246191</v>
+        <v>0.0721781675931833</v>
       </c>
       <c r="W84">
-        <v>0.2426715442747298</v>
+        <v>0.2276715442747298</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2720806593298477</v>
+        <v>0.2887126703727332</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2715004245186017</v>
+        <v>0.2588269036817873</v>
       </c>
       <c r="C85">
-        <v>-2886.187207124392</v>
+        <v>-2762.369710007945</v>
       </c>
       <c r="D85">
-        <v>2080.833792875608</v>
+        <v>2204.651289992056</v>
       </c>
       <c r="E85">
         <v>4214.821000000001</v>
@@ -8263,37 +8263,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M85">
-        <v>1910.199925877414</v>
+        <v>1800.158110877414</v>
       </c>
       <c r="N85">
-        <v>-1396.733259210747</v>
+        <v>-1286.691444210747</v>
       </c>
       <c r="O85">
-        <v>-349.1833148026868</v>
+        <v>-321.6728610526868</v>
       </c>
       <c r="P85">
-        <v>-1047.54994440806</v>
+        <v>-965.0185831580602</v>
       </c>
       <c r="Q85">
-        <v>-955.5499444080604</v>
+        <v>-873.0185831580602</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.4112113526023047</v>
+        <v>0.4098965241504549</v>
       </c>
       <c r="T85">
-        <v>3.533852294441758</v>
+        <v>3.521091661098446</v>
       </c>
       <c r="U85">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V85">
-        <v>0.06720064477423948</v>
+        <v>0.071308551116157</v>
       </c>
       <c r="W85">
-        <v>0.2428849332243493</v>
+        <v>0.2278849332243493</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2688025790969579</v>
+        <v>0.285234204464628</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2736462527895331</v>
+        <v>0.2608227319527188</v>
       </c>
       <c r="C86">
-        <v>-2994.171246466472</v>
+        <v>-2871.220152789797</v>
       </c>
       <c r="D86">
-        <v>2061.236753533529</v>
+        <v>2184.187847210204</v>
       </c>
       <c r="E86">
         <v>4303.208000000001</v>
@@ -8345,37 +8345,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M86">
-        <v>1933.214382815696</v>
+        <v>1821.846762815696</v>
       </c>
       <c r="N86">
-        <v>-1419.747716149029</v>
+        <v>-1308.380096149029</v>
       </c>
       <c r="O86">
-        <v>-354.9369290372572</v>
+        <v>-327.0950240372573</v>
       </c>
       <c r="P86">
-        <v>-1064.810787111772</v>
+        <v>-981.2850721117719</v>
       </c>
       <c r="Q86">
-        <v>-972.8107871117718</v>
+        <v>-889.2850721117719</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.4340495621399485</v>
+        <v>0.4326525569098581</v>
       </c>
       <c r="T86">
-        <v>3.754718062844366</v>
+        <v>3.741159889917097</v>
       </c>
       <c r="U86">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V86">
-        <v>0.06640063709835568</v>
+        <v>0.0704596397933456</v>
       </c>
       <c r="W86">
-        <v>0.2430932414846922</v>
+        <v>0.2280932414846922</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2656025483934228</v>
+        <v>0.2818385591733824</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2757920810604646</v>
+        <v>0.2628185602236502</v>
       </c>
       <c r="C87">
-        <v>-3101.789604687246</v>
+        <v>-2979.694208247147</v>
       </c>
       <c r="D87">
-        <v>2042.005395312755</v>
+        <v>2164.100791752854</v>
       </c>
       <c r="E87">
         <v>4391.595</v>
@@ -8427,37 +8427,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M87">
-        <v>1956.228839753978</v>
+        <v>1843.535414753978</v>
       </c>
       <c r="N87">
-        <v>-1442.762173087311</v>
+        <v>-1330.068748087311</v>
       </c>
       <c r="O87">
-        <v>-360.6905432718278</v>
+        <v>-332.5171870218278</v>
       </c>
       <c r="P87">
-        <v>-1082.071629815483</v>
+        <v>-997.5515610654834</v>
       </c>
       <c r="Q87">
-        <v>-990.0716298154834</v>
+        <v>-905.5515610654834</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.4599328662826117</v>
+        <v>0.4584427273705153</v>
       </c>
       <c r="T87">
-        <v>4.005032600367323</v>
+        <v>3.990570549244903</v>
       </c>
       <c r="U87">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V87">
-        <v>0.06561945313249268</v>
+        <v>0.06963070285460037</v>
       </c>
       <c r="W87">
-        <v>0.2432966483742034</v>
+        <v>0.2282966483742034</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2624778125299707</v>
+        <v>0.2785228114184014</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2779379093313962</v>
+        <v>0.2648143884945817</v>
       </c>
       <c r="C88">
-        <v>-3209.052422597717</v>
+        <v>-3087.802166176048</v>
       </c>
       <c r="D88">
-        <v>2023.129577402283</v>
+        <v>2144.379833823953</v>
       </c>
       <c r="E88">
         <v>4479.982</v>
@@ -8509,37 +8509,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M88">
-        <v>1979.24329669226</v>
+        <v>1865.22406669226</v>
       </c>
       <c r="N88">
-        <v>-1465.776630025593</v>
+        <v>-1351.757400025593</v>
       </c>
       <c r="O88">
-        <v>-366.4441575063983</v>
+        <v>-337.9393500063983</v>
       </c>
       <c r="P88">
-        <v>-1099.332472519195</v>
+        <v>-1013.818050019195</v>
       </c>
       <c r="Q88">
-        <v>-1007.332472519195</v>
+        <v>-921.8180500191949</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4895137853027983</v>
+        <v>0.4879172078969807</v>
       </c>
       <c r="T88">
-        <v>4.291106357536418</v>
+        <v>4.275611302762396</v>
       </c>
       <c r="U88">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V88">
-        <v>0.06485643623560323</v>
+        <v>0.06882104351908176</v>
       </c>
       <c r="W88">
-        <v>0.2434953248709353</v>
+        <v>0.2284953248709353</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2594257449424129</v>
+        <v>0.275284174076327</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2800837376023276</v>
+        <v>0.2668102167655132</v>
       </c>
       <c r="C89">
-        <v>-3315.969469486061</v>
+        <v>-3195.553944685369</v>
       </c>
       <c r="D89">
-        <v>2004.59953051394</v>
+        <v>2125.015055314632</v>
       </c>
       <c r="E89">
         <v>4568.369000000001</v>
@@ -8591,37 +8591,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M89">
-        <v>2002.257753630542</v>
+        <v>1886.912718630542</v>
       </c>
       <c r="N89">
-        <v>-1488.791086963875</v>
+        <v>-1373.446051963875</v>
       </c>
       <c r="O89">
-        <v>-372.1977717409688</v>
+        <v>-343.3615129909688</v>
       </c>
       <c r="P89">
-        <v>-1116.593315222907</v>
+        <v>-1030.084538972907</v>
       </c>
       <c r="Q89">
-        <v>-1024.593315222907</v>
+        <v>-938.0845389729066</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.5236456149414751</v>
+        <v>0.5219262238890561</v>
       </c>
       <c r="T89">
-        <v>4.621191461962296</v>
+        <v>4.604504479897965</v>
       </c>
       <c r="U89">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V89">
-        <v>0.06411095995703307</v>
+        <v>0.06802999704185093</v>
       </c>
       <c r="W89">
-        <v>0.2436894340918803</v>
+        <v>0.2286894340918803</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2564438398281322</v>
+        <v>0.2721199881674037</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2822295658732591</v>
+        <v>0.2688060450364447</v>
       </c>
       <c r="C90">
-        <v>-3422.550159977286</v>
+        <v>-3302.959106829175</v>
       </c>
       <c r="D90">
-        <v>1986.405840022715</v>
+        <v>2105.996893170826</v>
       </c>
       <c r="E90">
         <v>4656.756</v>
@@ -8673,37 +8673,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M90">
-        <v>2025.272210568824</v>
+        <v>1908.601370568824</v>
       </c>
       <c r="N90">
-        <v>-1511.805543902157</v>
+        <v>-1395.134703902157</v>
       </c>
       <c r="O90">
-        <v>-377.9513859755393</v>
+        <v>-348.7836759755393</v>
       </c>
       <c r="P90">
-        <v>-1133.854157926618</v>
+        <v>-1046.351027926618</v>
       </c>
       <c r="Q90">
-        <v>-1041.854157926618</v>
+        <v>-954.3510279266179</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.5634660828532647</v>
+        <v>0.5616034092131441</v>
       </c>
       <c r="T90">
-        <v>5.006290750459155</v>
+        <v>4.98821318655613</v>
       </c>
       <c r="U90">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V90">
-        <v>0.0633824263211577</v>
+        <v>0.06725692889364808</v>
       </c>
       <c r="W90">
-        <v>0.243879131739622</v>
+        <v>0.228879131739622</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2535297052846308</v>
+        <v>0.2690277155745924</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2843753941441906</v>
+        <v>0.2708018733073762</v>
       </c>
       <c r="C91">
-        <v>-3528.803569983039</v>
+        <v>-3410.02687635389</v>
       </c>
       <c r="D91">
-        <v>1968.539430016962</v>
+        <v>2087.316123646111</v>
       </c>
       <c r="E91">
         <v>4745.143000000001</v>
@@ -8755,37 +8755,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M91">
-        <v>2048.286667507106</v>
+        <v>1930.290022507106</v>
       </c>
       <c r="N91">
-        <v>-1534.82000084044</v>
+        <v>-1416.82335584044</v>
       </c>
       <c r="O91">
-        <v>-383.7050002101099</v>
+        <v>-354.2058389601099</v>
       </c>
       <c r="P91">
-        <v>-1151.11500063033</v>
+        <v>-1062.61751688033</v>
       </c>
       <c r="Q91">
-        <v>-1059.11500063033</v>
+        <v>-970.6175168803297</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.6105266358399252</v>
+        <v>0.608494628232521</v>
       </c>
       <c r="T91">
-        <v>5.461408091409989</v>
+        <v>5.441687112606687</v>
       </c>
       <c r="U91">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V91">
-        <v>0.06267026422766155</v>
+        <v>0.06650123306338236</v>
       </c>
       <c r="W91">
-        <v>0.2440645665188751</v>
+        <v>0.2290645665188751</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2506810569106461</v>
+        <v>0.2660049322535295</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2865212224151221</v>
+        <v>0.2727977015783076</v>
       </c>
       <c r="C92">
-        <v>-3634.738451798333</v>
+        <v>-3516.766152614744</v>
       </c>
       <c r="D92">
-        <v>1950.991548201668</v>
+        <v>2068.963847385257</v>
       </c>
       <c r="E92">
         <v>4833.530000000001</v>
@@ -8837,37 +8837,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M92">
-        <v>2071.301124445388</v>
+        <v>1951.978674445388</v>
       </c>
       <c r="N92">
-        <v>-1557.834457778722</v>
+        <v>-1438.512007778722</v>
       </c>
       <c r="O92">
-        <v>-389.4586144446804</v>
+        <v>-359.6280019446804</v>
       </c>
       <c r="P92">
-        <v>-1168.375843334041</v>
+        <v>-1078.884005834041</v>
       </c>
       <c r="Q92">
-        <v>-1076.375843334041</v>
+        <v>-986.8840058340413</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.6669992994239178</v>
+        <v>0.6647640910557731</v>
       </c>
       <c r="T92">
-        <v>6.007548900550987</v>
+        <v>5.985855823867356</v>
       </c>
       <c r="U92">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V92">
-        <v>0.06197392795846531</v>
+        <v>0.06576233047378924</v>
       </c>
       <c r="W92">
-        <v>0.2442458805252559</v>
+        <v>0.2292458805252559</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2478957118338613</v>
+        <v>0.263049321895157</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2886670506860535</v>
+        <v>0.2747935298492391</v>
       </c>
       <c r="C93">
-        <v>-3740.363248397967</v>
+        <v>-3623.185524712179</v>
       </c>
       <c r="D93">
-        <v>1933.753751602033</v>
+        <v>2050.931475287821</v>
       </c>
       <c r="E93">
         <v>4921.917</v>
@@ -8919,37 +8919,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M93">
-        <v>2094.31558138367</v>
+        <v>1973.66732638367</v>
       </c>
       <c r="N93">
-        <v>-1580.848914717003</v>
+        <v>-1460.200659717004</v>
       </c>
       <c r="O93">
-        <v>-395.2122286792509</v>
+        <v>-365.0501649292509</v>
       </c>
       <c r="P93">
-        <v>-1185.636686037752</v>
+        <v>-1095.150494787753</v>
       </c>
       <c r="Q93">
-        <v>-1093.636686037752</v>
+        <v>-1003.150494787753</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.7360214438043531</v>
+        <v>0.733537878950859</v>
       </c>
       <c r="T93">
-        <v>6.675054333945542</v>
+        <v>6.650950915408174</v>
       </c>
       <c r="U93">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V93">
-        <v>0.06129289578309756</v>
+        <v>0.0650396675015498</v>
       </c>
       <c r="W93">
-        <v>0.2444232096084195</v>
+        <v>0.2294232096084196</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2451715831323903</v>
+        <v>0.2601586700061992</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.290812878956985</v>
+        <v>0.2767893581201706</v>
       </c>
       <c r="C94">
-        <v>-3845.686106981697</v>
+        <v>-3729.293284895396</v>
       </c>
       <c r="D94">
-        <v>1916.817893018305</v>
+        <v>2033.210715104605</v>
       </c>
       <c r="E94">
         <v>5010.304000000001</v>
@@ -9001,37 +9001,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M94">
-        <v>2117.330038321953</v>
+        <v>1995.355978321953</v>
       </c>
       <c r="N94">
-        <v>-1603.863371655286</v>
+        <v>-1481.889311655286</v>
       </c>
       <c r="O94">
-        <v>-400.9658429138215</v>
+        <v>-370.4723279138215</v>
       </c>
       <c r="P94">
-        <v>-1202.897528741464</v>
+        <v>-1111.416983741464</v>
       </c>
       <c r="Q94">
-        <v>-1110.897528741464</v>
+        <v>-1019.416983741464</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.8222991242798975</v>
+        <v>0.8195051138197166</v>
       </c>
       <c r="T94">
-        <v>7.509436125688737</v>
+        <v>7.482319779834198</v>
       </c>
       <c r="U94">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V94">
-        <v>0.06062666865502041</v>
+        <v>0.06433271459392426</v>
       </c>
       <c r="W94">
-        <v>0.2445966837115144</v>
+        <v>0.2295966837115144</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2425066746200816</v>
+        <v>0.257330858375697</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2929587072279165</v>
+        <v>0.2787851863911021</v>
       </c>
       <c r="C95">
-        <v>-3950.714891813794</v>
+        <v>-3835.097441276982</v>
       </c>
       <c r="D95">
-        <v>1900.176108186209</v>
+        <v>2015.79355872302</v>
       </c>
       <c r="E95">
         <v>5098.691000000002</v>
@@ -9083,37 +9083,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M95">
-        <v>2140.344495260235</v>
+        <v>2017.044630260235</v>
       </c>
       <c r="N95">
-        <v>-1626.877828593568</v>
+        <v>-1503.577963593568</v>
       </c>
       <c r="O95">
-        <v>-406.7194571483921</v>
+        <v>-375.8944908983921</v>
       </c>
       <c r="P95">
-        <v>-1220.158371445176</v>
+        <v>-1127.683472695176</v>
       </c>
       <c r="Q95">
-        <v>-1128.158371445176</v>
+        <v>-1035.683472695176</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.9332275706055971</v>
+        <v>0.9300344157939618</v>
       </c>
       <c r="T95">
-        <v>8.582212715072842</v>
+        <v>8.551222605524798</v>
       </c>
       <c r="U95">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V95">
-        <v>0.05997476899206319</v>
+        <v>0.06364096497463473</v>
       </c>
       <c r="W95">
-        <v>0.2447664271887363</v>
+        <v>0.2297664271887363</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2398990759682528</v>
+        <v>0.2545638598985389</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.295104535498848</v>
+        <v>0.2807810146620336</v>
       </c>
       <c r="C96">
-        <v>-4055.45719639955</v>
+        <v>-3940.605729899586</v>
       </c>
       <c r="D96">
-        <v>1883.820803600452</v>
+        <v>1998.672270100416</v>
       </c>
       <c r="E96">
         <v>5187.078</v>
@@ -9165,37 +9165,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M96">
-        <v>2163.358952198516</v>
+        <v>2038.733282198517</v>
       </c>
       <c r="N96">
-        <v>-1649.89228553185</v>
+        <v>-1525.26661553185</v>
       </c>
       <c r="O96">
-        <v>-412.4730713829624</v>
+        <v>-381.3166538829625</v>
       </c>
       <c r="P96">
-        <v>-1237.419214148887</v>
+        <v>-1143.949961648887</v>
       </c>
       <c r="Q96">
-        <v>-1145.419214148887</v>
+        <v>-1051.949961648887</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>1.08113216570653</v>
+        <v>1.077406818426289</v>
       </c>
       <c r="T96">
-        <v>10.01258150091832</v>
+        <v>9.976426373112268</v>
       </c>
       <c r="U96">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V96">
-        <v>0.05933673953470083</v>
+        <v>0.06296393343235139</v>
       </c>
       <c r="W96">
-        <v>0.244932559102613</v>
+        <v>0.229932559102613</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2373469581388034</v>
+        <v>0.2518557337294056</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2972503637697795</v>
+        <v>0.2827768429329651</v>
       </c>
       <c r="C97">
-        <v>-4159.920355038301</v>
+        <v>-4045.825626192839</v>
       </c>
       <c r="D97">
-        <v>1867.7446449617</v>
+        <v>1981.839373807162</v>
       </c>
       <c r="E97">
         <v>5275.465000000001</v>
@@ -9247,37 +9247,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M97">
-        <v>2186.373409136799</v>
+        <v>2060.421934136799</v>
       </c>
       <c r="N97">
-        <v>-1672.906742470132</v>
+        <v>-1546.955267470132</v>
       </c>
       <c r="O97">
-        <v>-418.226685617533</v>
+        <v>-386.738816867533</v>
       </c>
       <c r="P97">
-        <v>-1254.680056852599</v>
+        <v>-1160.216450602599</v>
       </c>
       <c r="Q97">
-        <v>-1162.680056852599</v>
+        <v>-1068.216450602599</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.288198598847837</v>
+        <v>1.283728182111548</v>
       </c>
       <c r="T97">
-        <v>12.01509780110199</v>
+        <v>11.97171164773473</v>
       </c>
       <c r="U97">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V97">
-        <v>0.05871214227644082</v>
+        <v>0.06230115518569506</v>
       </c>
       <c r="W97">
-        <v>0.2450951935025134</v>
+        <v>0.2300951935025134</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2348485691057632</v>
+        <v>0.2492046207427803</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.299396192040711</v>
+        <v>0.2847726712038965</v>
       </c>
       <c r="C98">
-        <v>-4264.111453789895</v>
+        <v>-4150.764355856162</v>
       </c>
       <c r="D98">
-        <v>1851.940546210105</v>
+        <v>1965.287644143838</v>
       </c>
       <c r="E98">
         <v>5363.852</v>
@@ -9329,37 +9329,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M98">
-        <v>2209.387866075081</v>
+        <v>2082.110586075081</v>
       </c>
       <c r="N98">
-        <v>-1695.921199408414</v>
+        <v>-1568.643919408414</v>
       </c>
       <c r="O98">
-        <v>-423.9802998521035</v>
+        <v>-392.1609798521035</v>
       </c>
       <c r="P98">
-        <v>-1271.94089955631</v>
+        <v>-1176.482939556311</v>
       </c>
       <c r="Q98">
-        <v>-1179.94089955631</v>
+        <v>-1084.482939556311</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.598798248559793</v>
+        <v>1.593210227639431</v>
       </c>
       <c r="T98">
-        <v>15.01887225137745</v>
+        <v>14.96463955966838</v>
       </c>
       <c r="U98">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V98">
-        <v>0.05810055746106123</v>
+        <v>0.06165218481917741</v>
       </c>
       <c r="W98">
-        <v>0.2452544396857492</v>
+        <v>0.2302544396857492</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.232402229844245</v>
+        <v>0.2466087392767097</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.3015420203116425</v>
+        <v>0.286768499474828</v>
       </c>
       <c r="C99">
-        <v>-4368.037340889087</v>
+        <v>-4255.428905200758</v>
       </c>
       <c r="D99">
-        <v>1836.401659110913</v>
+        <v>1949.010094799243</v>
       </c>
       <c r="E99">
         <v>5452.239</v>
@@ -9411,37 +9411,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M99">
-        <v>2232.402323013363</v>
+        <v>2103.799238013363</v>
       </c>
       <c r="N99">
-        <v>-1718.935656346696</v>
+        <v>-1590.332571346696</v>
       </c>
       <c r="O99">
-        <v>-429.7339140866741</v>
+        <v>-397.583142836674</v>
       </c>
       <c r="P99">
-        <v>-1289.201742260022</v>
+        <v>-1192.749428510022</v>
       </c>
       <c r="Q99">
-        <v>-1197.201742260022</v>
+        <v>-1100.749428510022</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>2.116464331413057</v>
+        <v>2.109013636852575</v>
       </c>
       <c r="T99">
-        <v>20.02516300183661</v>
+        <v>19.9528527462245</v>
       </c>
       <c r="U99">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V99">
-        <v>0.05750158264187502</v>
+        <v>0.06101659528495909</v>
       </c>
       <c r="W99">
-        <v>0.2454104024425265</v>
+        <v>0.2304104024425265</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2300063305675001</v>
+        <v>0.2440663811398364</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.3036878485825739</v>
+        <v>0.2887643277457595</v>
       </c>
       <c r="C100">
-        <v>-4471.70463663999</v>
+        <v>-4359.826030981864</v>
       </c>
       <c r="D100">
-        <v>1821.121363360011</v>
+        <v>1932.999969018137</v>
       </c>
       <c r="E100">
         <v>5540.626000000001</v>
@@ -9493,37 +9493,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M100">
-        <v>2255.416779951645</v>
+        <v>2125.487889951645</v>
       </c>
       <c r="N100">
-        <v>-1741.950113284978</v>
+        <v>-1612.021223284979</v>
       </c>
       <c r="O100">
-        <v>-435.4875283212446</v>
+        <v>-403.0053058212446</v>
       </c>
       <c r="P100">
-        <v>-1306.462584963734</v>
+        <v>-1209.015917463734</v>
       </c>
       <c r="Q100">
-        <v>-1214.462584963734</v>
+        <v>-1117.015917463734</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>3.151796497119586</v>
+        <v>3.140620455278862</v>
       </c>
       <c r="T100">
-        <v>30.0377445027549</v>
+        <v>29.92927911933675</v>
       </c>
       <c r="U100">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V100">
-        <v>0.05691483179859059</v>
+        <v>0.0603939769657248</v>
       </c>
       <c r="W100">
-        <v>0.2455631822859002</v>
+        <v>0.2305631822859002</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2276593271943623</v>
+        <v>0.2415759078628992</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.3058336768535054</v>
+        <v>0.290760156016691</v>
       </c>
       <c r="C101">
-        <v>-4575.119742820623</v>
+        <v>-4463.962269750364</v>
       </c>
       <c r="D101">
-        <v>1806.093257179376</v>
+        <v>1917.250730249636</v>
       </c>
       <c r="E101">
         <v>5629.013</v>
@@ -9575,37 +9575,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M101">
-        <v>2278.431236889927</v>
+        <v>2147.176541889927</v>
       </c>
       <c r="N101">
-        <v>-1764.96457022326</v>
+        <v>-1633.70987522326</v>
       </c>
       <c r="O101">
-        <v>-441.241142555815</v>
+        <v>-408.4274688058151</v>
       </c>
       <c r="P101">
-        <v>-1323.723427667445</v>
+        <v>-1225.282406417445</v>
       </c>
       <c r="Q101">
-        <v>-1231.723427667445</v>
+        <v>-1133.282406417445</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>6.257792994239171</v>
+        <v>6.235440910557725</v>
       </c>
       <c r="T101">
-        <v>60.07548900550981</v>
+        <v>59.8585582386735</v>
       </c>
       <c r="U101">
-        <v>0.2603828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V101">
-        <v>0.05633993450769574</v>
+        <v>0.05978393679435385</v>
       </c>
       <c r="W101">
-        <v>0.2457128756677916</v>
+        <v>0.2307128756677916</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2253597380307829</v>
+        <v>0.2391357471774154</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/turkey/turkey_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_telecom_wireless.xlsx
@@ -1139,43 +1139,43 @@
         <v>1.41500586166471</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>61.2260505132096</v>
       </c>
       <c r="G2">
         <v>6.87359612420172</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.19464214930632</v>
       </c>
       <c r="I2">
         <v>0.353140167671716</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>5717.4</v>
       </c>
       <c r="L2">
-        <v>9507.69319925502</v>
+        <v>9409.64652923774</v>
       </c>
       <c r="M2">
         <v>6469.6</v>
       </c>
       <c r="N2">
-        <v>7138.59319925502</v>
+        <v>7128.93352923774</v>
       </c>
       <c r="O2">
         <v>3121.3</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>88.387</v>
       </c>
       <c r="Q2">
         <v>0.118393365587527</v>
       </c>
       <c r="R2">
-        <v>0.11159027896618</v>
+        <v>0.111679424471964</v>
       </c>
       <c r="S2">
         <v>0.0815121203198611</v>
@@ -1197,13 +1197,13 @@
         <v>0.138527942642476</v>
       </c>
       <c r="X2">
-        <v>0.11159027896618</v>
+        <v>0.11208869017047</v>
       </c>
       <c r="Y2">
         <v>0.8967500756868459</v>
       </c>
       <c r="Z2">
-        <v>0.636242279954951</v>
+        <v>0.641062297227337</v>
       </c>
       <c r="AA2">
         <v>3121.3</v>
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1115902789661804</v>
+        <v>0.1116794244719635</v>
       </c>
       <c r="C2">
-        <v>9507.693199255018</v>
+        <v>9409.646529237736</v>
       </c>
       <c r="D2">
-        <v>7138.593199255018</v>
+        <v>7128.933529237736</v>
       </c>
       <c r="E2">
-        <v>-3121.3</v>
+        <v>-3032.913</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>88.38700000000001</v>
       </c>
       <c r="G2">
         <v>2369.1</v>
@@ -1457,28 +1457,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>8.386408438282091</v>
       </c>
       <c r="N2">
-        <v>513.4666666666667</v>
+        <v>505.0802582283846</v>
       </c>
       <c r="O2">
-        <v>128.3666666666667</v>
+        <v>126.2700645570961</v>
       </c>
       <c r="P2">
-        <v>385.1</v>
+        <v>378.8101936712885</v>
       </c>
       <c r="Q2">
-        <v>477.1</v>
+        <v>470.8101936712885</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1115902789661804</v>
+        <v>0.1120886901704696</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549506</v>
+        <v>0.6410622972273367</v>
       </c>
       <c r="U2">
         <v>0.09488282709314819</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>61.22605051320962</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1116794244719635</v>
+        <v>0.1117685699777467</v>
       </c>
       <c r="C3">
-        <v>9409.646529237736</v>
+        <v>9311.625966082238</v>
       </c>
       <c r="D3">
-        <v>7128.933529237736</v>
+        <v>7119.299966082237</v>
       </c>
       <c r="E3">
-        <v>-3032.913</v>
+        <v>-2944.526</v>
       </c>
       <c r="F3">
-        <v>88.38700000000001</v>
+        <v>176.774</v>
       </c>
       <c r="G3">
         <v>2369.1</v>
@@ -1539,28 +1539,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M3">
-        <v>8.386408438282091</v>
+        <v>16.77281687656418</v>
       </c>
       <c r="N3">
-        <v>505.0802582283846</v>
+        <v>496.6938497901025</v>
       </c>
       <c r="O3">
-        <v>126.2700645570961</v>
+        <v>124.1734624475256</v>
       </c>
       <c r="P3">
-        <v>378.8101936712885</v>
+        <v>372.5203873425769</v>
       </c>
       <c r="Q3">
-        <v>470.8101936712885</v>
+        <v>464.5203873425769</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1120886901704696</v>
+        <v>0.1125972730319892</v>
       </c>
       <c r="T3">
-        <v>0.6410622972273367</v>
+        <v>0.6459806821991592</v>
       </c>
       <c r="U3">
         <v>0.09488282709314819</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>61.22605051320962</v>
+        <v>30.61302525660481</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1117685699777467</v>
+        <v>0.1118577154835298</v>
       </c>
       <c r="C4">
-        <v>9311.625966082238</v>
+        <v>9213.631404094169</v>
       </c>
       <c r="D4">
-        <v>7119.299966082237</v>
+        <v>7109.692404094169</v>
       </c>
       <c r="E4">
-        <v>-2944.526</v>
+        <v>-2856.139</v>
       </c>
       <c r="F4">
-        <v>176.774</v>
+        <v>265.161</v>
       </c>
       <c r="G4">
         <v>2369.1</v>
@@ -1621,28 +1621,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M4">
-        <v>16.77281687656418</v>
+        <v>25.15922531484627</v>
       </c>
       <c r="N4">
-        <v>496.6938497901025</v>
+        <v>488.3074413518204</v>
       </c>
       <c r="O4">
-        <v>124.1734624475256</v>
+        <v>122.0768603379551</v>
       </c>
       <c r="P4">
-        <v>372.5203873425769</v>
+        <v>366.2305810138653</v>
       </c>
       <c r="Q4">
-        <v>464.5203873425769</v>
+        <v>458.2305810138653</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1125972730319892</v>
+        <v>0.1131163421380763</v>
       </c>
       <c r="T4">
-        <v>0.6459806821991592</v>
+        <v>0.6510004771704004</v>
       </c>
       <c r="U4">
         <v>0.09488282709314819</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>30.61302525660481</v>
+        <v>20.40868350440321</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1118577154835298</v>
+        <v>0.111946860989313</v>
       </c>
       <c r="C5">
-        <v>9213.631404094169</v>
+        <v>9115.662738148931</v>
       </c>
       <c r="D5">
-        <v>7109.692404094169</v>
+        <v>7100.110738148931</v>
       </c>
       <c r="E5">
-        <v>-2856.139</v>
+        <v>-2767.752</v>
       </c>
       <c r="F5">
-        <v>265.161</v>
+        <v>353.5480000000001</v>
       </c>
       <c r="G5">
         <v>2369.1</v>
@@ -1703,28 +1703,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M5">
-        <v>25.15922531484627</v>
+        <v>33.54563375312836</v>
       </c>
       <c r="N5">
-        <v>488.3074413518204</v>
+        <v>479.9210329135383</v>
       </c>
       <c r="O5">
-        <v>122.0768603379551</v>
+        <v>119.9802582283846</v>
       </c>
       <c r="P5">
-        <v>366.2305810138653</v>
+        <v>359.9407746851538</v>
       </c>
       <c r="Q5">
-        <v>458.2305810138653</v>
+        <v>451.9407746851538</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1131163421380763</v>
+        <v>0.1136462251838735</v>
       </c>
       <c r="T5">
-        <v>0.6510004771704004</v>
+        <v>0.6561248512035428</v>
       </c>
       <c r="U5">
         <v>0.09488282709314819</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>20.40868350440321</v>
+        <v>15.30651262830241</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.111946860989313</v>
+        <v>0.1120360064950962</v>
       </c>
       <c r="C6">
-        <v>9115.662738148931</v>
+        <v>9017.719863687873</v>
       </c>
       <c r="D6">
-        <v>7100.110738148931</v>
+        <v>7090.554863687873</v>
       </c>
       <c r="E6">
-        <v>-2767.752</v>
+        <v>-2679.365</v>
       </c>
       <c r="F6">
-        <v>353.5480000000001</v>
+        <v>441.9350000000001</v>
       </c>
       <c r="G6">
         <v>2369.1</v>
@@ -1785,28 +1785,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M6">
-        <v>33.54563375312836</v>
+        <v>41.93204219141045</v>
       </c>
       <c r="N6">
-        <v>479.9210329135383</v>
+        <v>471.5346244752562</v>
       </c>
       <c r="O6">
-        <v>119.9802582283846</v>
+        <v>117.8836561188141</v>
       </c>
       <c r="P6">
-        <v>359.9407746851538</v>
+        <v>353.6509683564421</v>
       </c>
       <c r="Q6">
-        <v>451.9407746851538</v>
+        <v>445.6509683564421</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1136462251838735</v>
+        <v>0.1141872636622138</v>
       </c>
       <c r="T6">
-        <v>0.6561248512035428</v>
+        <v>0.6613571067952776</v>
       </c>
       <c r="U6">
         <v>0.09488282709314819</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>15.30651262830241</v>
+        <v>12.24521010264192</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1120360064950962</v>
+        <v>0.1121251520008793</v>
       </c>
       <c r="C7">
-        <v>9017.719863687873</v>
+        <v>8919.802676714486</v>
       </c>
       <c r="D7">
-        <v>7090.554863687873</v>
+        <v>7081.024676714486</v>
       </c>
       <c r="E7">
-        <v>-2679.365</v>
+        <v>-2590.978</v>
       </c>
       <c r="F7">
-        <v>441.9350000000001</v>
+        <v>530.3220000000001</v>
       </c>
       <c r="G7">
         <v>2369.1</v>
@@ -1867,28 +1867,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M7">
-        <v>41.93204219141045</v>
+        <v>50.31845062969254</v>
       </c>
       <c r="N7">
-        <v>471.5346244752562</v>
+        <v>463.1482160369741</v>
       </c>
       <c r="O7">
-        <v>117.8836561188141</v>
+        <v>115.7870540092435</v>
       </c>
       <c r="P7">
-        <v>353.6509683564421</v>
+        <v>347.3611620277306</v>
       </c>
       <c r="Q7">
-        <v>445.6509683564421</v>
+        <v>439.3611620277306</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1141872636622138</v>
+        <v>0.1147398135975401</v>
       </c>
       <c r="T7">
-        <v>0.6613571067952776</v>
+        <v>0.6667006869740706</v>
       </c>
       <c r="U7">
         <v>0.09488282709314819</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>12.24521010264192</v>
+        <v>10.2043417522016</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1121251520008793</v>
+        <v>0.1122142975066625</v>
       </c>
       <c r="C8">
-        <v>8919.802676714486</v>
+        <v>8821.911073790614</v>
       </c>
       <c r="D8">
-        <v>7081.024676714486</v>
+        <v>7071.520073790614</v>
       </c>
       <c r="E8">
-        <v>-2590.978</v>
+        <v>-2502.591</v>
       </c>
       <c r="F8">
-        <v>530.322</v>
+        <v>618.7089999999999</v>
       </c>
       <c r="G8">
         <v>2369.1</v>
@@ -1949,28 +1949,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M8">
-        <v>50.31845062969253</v>
+        <v>58.70485906797462</v>
       </c>
       <c r="N8">
-        <v>463.1482160369742</v>
+        <v>454.7618075986921</v>
       </c>
       <c r="O8">
-        <v>115.7870540092435</v>
+        <v>113.690451899673</v>
       </c>
       <c r="P8">
-        <v>347.3611620277306</v>
+        <v>341.0713556990191</v>
       </c>
       <c r="Q8">
-        <v>439.3611620277306</v>
+        <v>433.0713556990191</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1147398135975401</v>
+        <v>0.1153042463271744</v>
       </c>
       <c r="T8">
-        <v>0.6667006869740706</v>
+        <v>0.6721591828556333</v>
       </c>
       <c r="U8">
         <v>0.09488282709314819</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>10.20434175220161</v>
+        <v>8.746578644744234</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1122142975066625</v>
+        <v>0.1123934430124457</v>
       </c>
       <c r="C9">
-        <v>8821.911073790616</v>
+        <v>8714.500713787464</v>
       </c>
       <c r="D9">
-        <v>7071.520073790616</v>
+        <v>7052.496713787463</v>
       </c>
       <c r="E9">
-        <v>-2502.591</v>
+        <v>-2414.204</v>
       </c>
       <c r="F9">
-        <v>618.7090000000001</v>
+        <v>707.0960000000001</v>
       </c>
       <c r="G9">
         <v>2369.1</v>
@@ -2031,45 +2031,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M9">
-        <v>58.70485906797462</v>
+        <v>68.15191150625672</v>
       </c>
       <c r="N9">
-        <v>454.7618075986921</v>
+        <v>445.31475516041</v>
       </c>
       <c r="O9">
-        <v>113.690451899673</v>
+        <v>111.3286887901025</v>
       </c>
       <c r="P9">
-        <v>341.0713556990191</v>
+        <v>333.9860663703075</v>
       </c>
       <c r="Q9">
-        <v>433.0713556990191</v>
+        <v>425.9860663703075</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1153042463271744</v>
+        <v>0.11588094933354</v>
       </c>
       <c r="T9">
-        <v>0.6721591828556333</v>
+        <v>0.6777363416911432</v>
       </c>
       <c r="U9">
-        <v>0.09488282709314819</v>
+        <v>0.09638282709314819</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.07116212031986113</v>
+        <v>0.07228712031986115</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>8.746578644744233</v>
+        <v>7.534149157643621</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1123934430124457</v>
+        <v>0.1124938385182288</v>
       </c>
       <c r="C10">
-        <v>8714.500713787464</v>
+        <v>8615.497456118905</v>
       </c>
       <c r="D10">
-        <v>7052.496713787463</v>
+        <v>7041.880456118905</v>
       </c>
       <c r="E10">
-        <v>-2414.204</v>
+        <v>-2325.817</v>
       </c>
       <c r="F10">
-        <v>707.0960000000001</v>
+        <v>795.4830000000001</v>
       </c>
       <c r="G10">
         <v>2369.1</v>
@@ -2113,28 +2113,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M10">
-        <v>68.15191150625672</v>
+        <v>76.6709004445388</v>
       </c>
       <c r="N10">
-        <v>445.31475516041</v>
+        <v>436.7957662221279</v>
       </c>
       <c r="O10">
-        <v>111.3286887901025</v>
+        <v>109.198941555532</v>
       </c>
       <c r="P10">
-        <v>333.9860663703075</v>
+        <v>327.5968246665959</v>
       </c>
       <c r="Q10">
-        <v>425.9860663703075</v>
+        <v>419.5968246665959</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.11588094933354</v>
+        <v>0.1164703271312542</v>
       </c>
       <c r="T10">
-        <v>0.6777363416911432</v>
+        <v>0.6834360754461145</v>
       </c>
       <c r="U10">
         <v>0.09638282709314819</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.534149157643621</v>
+        <v>6.697021473460998</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1124938385182288</v>
+        <v>0.112721734024012</v>
       </c>
       <c r="C11">
-        <v>8615.497456118905</v>
+        <v>8503.130011923662</v>
       </c>
       <c r="D11">
-        <v>7041.880456118905</v>
+        <v>7017.900011923663</v>
       </c>
       <c r="E11">
-        <v>-2325.817</v>
+        <v>-2237.43</v>
       </c>
       <c r="F11">
-        <v>795.4830000000001</v>
+        <v>883.87</v>
       </c>
       <c r="G11">
         <v>2369.1</v>
@@ -2195,45 +2195,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M11">
-        <v>76.6709004445388</v>
+        <v>86.69246838282089</v>
       </c>
       <c r="N11">
-        <v>436.7957662221279</v>
+        <v>426.7741982838458</v>
       </c>
       <c r="O11">
-        <v>109.198941555532</v>
+        <v>106.6935495709615</v>
       </c>
       <c r="P11">
-        <v>327.5968246665959</v>
+        <v>320.0806487128843</v>
       </c>
       <c r="Q11">
-        <v>419.5968246665959</v>
+        <v>412.0806487128843</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1164703271312542</v>
+        <v>0.1170728022133621</v>
       </c>
       <c r="T11">
-        <v>0.6834360754461145</v>
+        <v>0.6892624699511964</v>
       </c>
       <c r="U11">
-        <v>0.09638282709314819</v>
+        <v>0.09808282709314819</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.07228712031986115</v>
+        <v>0.07356212031986115</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.697021473460998</v>
+        <v>5.922852079828609</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.112721734024012</v>
+        <v>0.1129008795297951</v>
       </c>
       <c r="C12">
-        <v>8503.130011923662</v>
+        <v>8396.006666647987</v>
       </c>
       <c r="D12">
-        <v>7017.900011923663</v>
+        <v>6999.163666647987</v>
       </c>
       <c r="E12">
-        <v>-2237.43</v>
+        <v>-2149.043</v>
       </c>
       <c r="F12">
-        <v>883.8700000000001</v>
+        <v>972.2570000000001</v>
       </c>
       <c r="G12">
         <v>2369.1</v>
@@ -2277,45 +2277,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M12">
-        <v>86.69246838282091</v>
+        <v>96.13952082110299</v>
       </c>
       <c r="N12">
-        <v>426.7741982838458</v>
+        <v>417.3271458455637</v>
       </c>
       <c r="O12">
-        <v>106.6935495709615</v>
+        <v>104.3317864613909</v>
       </c>
       <c r="P12">
-        <v>320.0806487128843</v>
+        <v>312.9953593841727</v>
       </c>
       <c r="Q12">
-        <v>412.0806487128843</v>
+        <v>404.9953593841727</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1170728022133621</v>
+        <v>0.11768881606136</v>
       </c>
       <c r="T12">
-        <v>0.6892624699511964</v>
+        <v>0.6952197946698758</v>
       </c>
       <c r="U12">
-        <v>0.09808282709314819</v>
+        <v>0.09888282709314819</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.07356212031986115</v>
+        <v>0.07416212031986114</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>5.922852079828608</v>
+        <v>5.340849031504209</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1129008795297951</v>
+        <v>0.1130200250355783</v>
       </c>
       <c r="C13">
-        <v>8396.006666647987</v>
+        <v>8295.213856107444</v>
       </c>
       <c r="D13">
-        <v>6999.163666647987</v>
+        <v>6986.757856107445</v>
       </c>
       <c r="E13">
-        <v>-2149.043</v>
+        <v>-2060.656</v>
       </c>
       <c r="F13">
-        <v>972.2570000000001</v>
+        <v>1060.644</v>
       </c>
       <c r="G13">
         <v>2369.1</v>
@@ -2359,28 +2359,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M13">
-        <v>96.13952082110299</v>
+        <v>104.8794772593851</v>
       </c>
       <c r="N13">
-        <v>417.3271458455637</v>
+        <v>408.5871894072816</v>
       </c>
       <c r="O13">
-        <v>104.3317864613909</v>
+        <v>102.1467973518204</v>
       </c>
       <c r="P13">
-        <v>312.9953593841727</v>
+        <v>306.4403920554612</v>
       </c>
       <c r="Q13">
-        <v>404.9953593841727</v>
+        <v>398.4403920554612</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.11768881606136</v>
+        <v>0.1183188302240852</v>
       </c>
       <c r="T13">
-        <v>0.6952197946698758</v>
+        <v>0.7013125131321615</v>
       </c>
       <c r="U13">
         <v>0.09888282709314819</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.340849031504209</v>
+        <v>4.89577827887886</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1130200250355783</v>
+        <v>0.1131391705413614</v>
       </c>
       <c r="C14">
-        <v>8295.213856107444</v>
+        <v>8194.464945619713</v>
       </c>
       <c r="D14">
-        <v>6986.757856107445</v>
+        <v>6974.395945619714</v>
       </c>
       <c r="E14">
-        <v>-2060.656</v>
+        <v>-1972.269</v>
       </c>
       <c r="F14">
-        <v>1060.644</v>
+        <v>1149.031</v>
       </c>
       <c r="G14">
         <v>2369.1</v>
@@ -2441,28 +2441,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M14">
-        <v>104.8794772593851</v>
+        <v>113.6194336976672</v>
       </c>
       <c r="N14">
-        <v>408.5871894072816</v>
+        <v>399.8472329689995</v>
       </c>
       <c r="O14">
-        <v>102.1467973518204</v>
+        <v>99.96180824224987</v>
       </c>
       <c r="P14">
-        <v>306.4403920554612</v>
+        <v>299.8854247267496</v>
       </c>
       <c r="Q14">
-        <v>398.4403920554612</v>
+        <v>391.8854247267496</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1183188302240852</v>
+        <v>0.1189633274710109</v>
       </c>
       <c r="T14">
-        <v>0.7013125131321615</v>
+        <v>0.707545294087833</v>
       </c>
       <c r="U14">
         <v>0.09888282709314819</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>4.89577827887886</v>
+        <v>4.519179949734331</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1131391705413614</v>
+        <v>0.1133633160471446</v>
       </c>
       <c r="C15">
-        <v>8194.464945619713</v>
+        <v>8082.93995301923</v>
       </c>
       <c r="D15">
-        <v>6974.395945619714</v>
+        <v>6951.25795301923</v>
       </c>
       <c r="E15">
-        <v>-1972.269</v>
+        <v>-1883.882</v>
       </c>
       <c r="F15">
-        <v>1149.031</v>
+        <v>1237.418</v>
       </c>
       <c r="G15">
         <v>2369.1</v>
@@ -2523,45 +2523,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M15">
-        <v>113.6194336976672</v>
+        <v>123.5968081359493</v>
       </c>
       <c r="N15">
-        <v>399.8472329689995</v>
+        <v>389.8698585307175</v>
       </c>
       <c r="O15">
-        <v>99.96180824224987</v>
+        <v>97.46746463267937</v>
       </c>
       <c r="P15">
-        <v>299.8854247267496</v>
+        <v>292.4023938980381</v>
       </c>
       <c r="Q15">
-        <v>391.8854247267496</v>
+        <v>384.4023938980381</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1189633274710109</v>
+        <v>0.1196228130260047</v>
       </c>
       <c r="T15">
-        <v>0.707545294087833</v>
+        <v>0.7139230234378225</v>
       </c>
       <c r="U15">
-        <v>0.09888282709314819</v>
+        <v>0.09988282709314819</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.07416212031986114</v>
+        <v>0.07491212031986114</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.519179949734331</v>
+        <v>4.154368340174962</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1133633160471446</v>
+        <v>0.1134899615529278</v>
       </c>
       <c r="C16">
-        <v>8082.93995301923</v>
+        <v>7981.547397112674</v>
       </c>
       <c r="D16">
-        <v>6951.25795301923</v>
+        <v>6938.252397112674</v>
       </c>
       <c r="E16">
-        <v>-1883.882</v>
+        <v>-1795.495</v>
       </c>
       <c r="F16">
-        <v>1237.418</v>
+        <v>1325.805</v>
       </c>
       <c r="G16">
         <v>2369.1</v>
@@ -2605,28 +2605,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M16">
-        <v>123.5968081359493</v>
+        <v>132.4251515742314</v>
       </c>
       <c r="N16">
-        <v>389.8698585307175</v>
+        <v>381.0415150924354</v>
       </c>
       <c r="O16">
-        <v>97.46746463267937</v>
+        <v>95.26037877310884</v>
       </c>
       <c r="P16">
-        <v>292.4023938980381</v>
+        <v>285.7811363193265</v>
       </c>
       <c r="Q16">
-        <v>384.4023938980381</v>
+        <v>377.7811363193265</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1196228130260047</v>
+        <v>0.1202978158881748</v>
       </c>
       <c r="T16">
-        <v>0.7139230234378225</v>
+        <v>0.7204508170078118</v>
       </c>
       <c r="U16">
         <v>0.09988282709314819</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.154368340174962</v>
+        <v>3.877410450829964</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1134899615529278</v>
+        <v>0.1136166070587109</v>
       </c>
       <c r="C17">
-        <v>7981.547397112674</v>
+        <v>7880.203416187293</v>
       </c>
       <c r="D17">
-        <v>6938.252397112674</v>
+        <v>6925.295416187294</v>
       </c>
       <c r="E17">
-        <v>-1795.495</v>
+        <v>-1707.108</v>
       </c>
       <c r="F17">
-        <v>1325.805</v>
+        <v>1414.192</v>
       </c>
       <c r="G17">
         <v>2369.1</v>
@@ -2687,28 +2687,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M17">
-        <v>132.4251515742313</v>
+        <v>141.2534950125134</v>
       </c>
       <c r="N17">
-        <v>381.0415150924354</v>
+        <v>372.2131716541533</v>
       </c>
       <c r="O17">
-        <v>95.26037877310884</v>
+        <v>93.05329291353831</v>
       </c>
       <c r="P17">
-        <v>285.7811363193265</v>
+        <v>279.1598787406149</v>
       </c>
       <c r="Q17">
-        <v>377.7811363193265</v>
+        <v>371.1598787406149</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1202978158881748</v>
+        <v>0.1209888902470633</v>
       </c>
       <c r="T17">
-        <v>0.7204508170078118</v>
+        <v>0.7271340342342293</v>
       </c>
       <c r="U17">
         <v>0.09988282709314819</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.877410450829964</v>
+        <v>3.635072297653091</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1136166070587109</v>
+        <v>0.1137432525644941</v>
       </c>
       <c r="C18">
-        <v>7880.203416187293</v>
+        <v>7778.907738613339</v>
       </c>
       <c r="D18">
-        <v>6925.295416187294</v>
+        <v>6912.386738613339</v>
       </c>
       <c r="E18">
-        <v>-1707.108</v>
+        <v>-1618.721</v>
       </c>
       <c r="F18">
-        <v>1414.192</v>
+        <v>1502.579</v>
       </c>
       <c r="G18">
         <v>2369.1</v>
@@ -2769,28 +2769,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M18">
-        <v>141.2534950125134</v>
+        <v>150.0818384507955</v>
       </c>
       <c r="N18">
-        <v>372.2131716541533</v>
+        <v>363.3848282158712</v>
       </c>
       <c r="O18">
-        <v>93.05329291353831</v>
+        <v>90.84620705396779</v>
       </c>
       <c r="P18">
-        <v>279.1598787406149</v>
+        <v>272.5386211619034</v>
       </c>
       <c r="Q18">
-        <v>371.1598787406149</v>
+        <v>364.5386211619034</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1209888902470633</v>
+        <v>0.1216966170001418</v>
       </c>
       <c r="T18">
-        <v>0.7271340342342293</v>
+        <v>0.7339782928395967</v>
       </c>
       <c r="U18">
         <v>0.09988282709314819</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.635072297653091</v>
+        <v>3.421244515438203</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1137432525644941</v>
+        <v>0.1138698980702772</v>
       </c>
       <c r="C19">
-        <v>7778.907738613339</v>
+        <v>7677.660094782543</v>
       </c>
       <c r="D19">
-        <v>6912.386738613339</v>
+        <v>6899.526094782543</v>
       </c>
       <c r="E19">
-        <v>-1618.721</v>
+        <v>-1530.334</v>
       </c>
       <c r="F19">
-        <v>1502.579</v>
+        <v>1590.966</v>
       </c>
       <c r="G19">
         <v>2369.1</v>
@@ -2851,28 +2851,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M19">
-        <v>150.0818384507955</v>
+        <v>158.9101818890776</v>
       </c>
       <c r="N19">
-        <v>363.3848282158712</v>
+        <v>354.556484777589</v>
       </c>
       <c r="O19">
-        <v>90.84620705396779</v>
+        <v>88.63912119439726</v>
       </c>
       <c r="P19">
-        <v>272.5386211619034</v>
+        <v>265.9173635831918</v>
       </c>
       <c r="Q19">
-        <v>364.5386211619034</v>
+        <v>357.9173635831918</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1216966170001418</v>
+        <v>0.1224216053813442</v>
       </c>
       <c r="T19">
-        <v>0.7339782928395967</v>
+        <v>0.7409894845816802</v>
       </c>
       <c r="U19">
         <v>0.09988282709314819</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.421244515438203</v>
+        <v>3.231175375691636</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1138698980702773</v>
+        <v>0.1139965435760604</v>
       </c>
       <c r="C20">
-        <v>7677.660094782541</v>
+        <v>7576.460217089357</v>
       </c>
       <c r="D20">
-        <v>6899.526094782542</v>
+        <v>6886.713217089357</v>
       </c>
       <c r="E20">
-        <v>-1530.334</v>
+        <v>-1441.947</v>
       </c>
       <c r="F20">
-        <v>1590.966</v>
+        <v>1679.353</v>
       </c>
       <c r="G20">
         <v>2369.1</v>
@@ -2933,28 +2933,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M20">
-        <v>158.9101818890776</v>
+        <v>167.7385253273597</v>
       </c>
       <c r="N20">
-        <v>354.556484777589</v>
+        <v>345.728141339307</v>
       </c>
       <c r="O20">
-        <v>88.63912119439726</v>
+        <v>86.43203533482675</v>
       </c>
       <c r="P20">
-        <v>265.9173635831918</v>
+        <v>259.2961060044802</v>
       </c>
       <c r="Q20">
-        <v>357.9173635831918</v>
+        <v>351.2961060044802</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1224216053813442</v>
+        <v>0.1231644947102306</v>
       </c>
       <c r="T20">
-        <v>0.7409894845816802</v>
+        <v>0.7481737921692476</v>
       </c>
       <c r="U20">
         <v>0.09988282709314819</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.231175375691636</v>
+        <v>3.06111351381313</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1139965435760604</v>
+        <v>0.1144981890818436</v>
       </c>
       <c r="C21">
-        <v>7576.460217089357</v>
+        <v>7437.785301481355</v>
       </c>
       <c r="D21">
-        <v>6886.713217089357</v>
+        <v>6836.425301481356</v>
       </c>
       <c r="E21">
-        <v>-1441.947</v>
+        <v>-1353.56</v>
       </c>
       <c r="F21">
-        <v>1679.353</v>
+        <v>1767.74</v>
       </c>
       <c r="G21">
         <v>2369.1</v>
@@ -3015,45 +3015,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M21">
-        <v>167.7385253273597</v>
+        <v>180.9862187656418</v>
       </c>
       <c r="N21">
-        <v>345.728141339307</v>
+        <v>332.4804479010249</v>
       </c>
       <c r="O21">
-        <v>86.43203533482675</v>
+        <v>83.12011197525622</v>
       </c>
       <c r="P21">
-        <v>259.2961060044802</v>
+        <v>249.3603359257687</v>
       </c>
       <c r="Q21">
-        <v>351.2961060044802</v>
+        <v>341.3603359257687</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1231644947102306</v>
+        <v>0.1239259562723392</v>
       </c>
       <c r="T21">
-        <v>0.7481737921692476</v>
+        <v>0.7555377074465038</v>
       </c>
       <c r="U21">
-        <v>0.09988282709314819</v>
+        <v>0.1023828270931482</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.07491212031986114</v>
+        <v>0.07678712031986115</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.06111351381313</v>
+        <v>2.837048423734142</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1144981890818436</v>
+        <v>0.1146435845876267</v>
       </c>
       <c r="C22">
-        <v>7437.785301481355</v>
+        <v>7334.959984237828</v>
       </c>
       <c r="D22">
-        <v>6836.425301481356</v>
+        <v>6821.986984237828</v>
       </c>
       <c r="E22">
-        <v>-1353.56</v>
+        <v>-1265.173</v>
       </c>
       <c r="F22">
-        <v>1767.74</v>
+        <v>1856.127</v>
       </c>
       <c r="G22">
         <v>2369.1</v>
@@ -3097,28 +3097,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M22">
-        <v>180.9862187656418</v>
+        <v>190.0355297039239</v>
       </c>
       <c r="N22">
-        <v>332.4804479010249</v>
+        <v>323.4311369627428</v>
       </c>
       <c r="O22">
-        <v>83.12011197525622</v>
+        <v>80.8577842406857</v>
       </c>
       <c r="P22">
-        <v>249.3603359257687</v>
+        <v>242.5733527220571</v>
       </c>
       <c r="Q22">
-        <v>341.3603359257687</v>
+        <v>334.5733527220571</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1239259562723392</v>
+        <v>0.1247066953423492</v>
       </c>
       <c r="T22">
-        <v>0.7555377074465038</v>
+        <v>0.7630880509586275</v>
       </c>
       <c r="U22">
         <v>0.1023828270931482</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.837048423734142</v>
+        <v>2.701950879746802</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1146435845876267</v>
+        <v>0.1147889800934099</v>
       </c>
       <c r="C23">
-        <v>7334.959984237828</v>
+        <v>7232.195525016424</v>
       </c>
       <c r="D23">
-        <v>6821.986984237828</v>
+        <v>6807.609525016424</v>
       </c>
       <c r="E23">
-        <v>-1265.173</v>
+        <v>-1176.786</v>
       </c>
       <c r="F23">
-        <v>1856.127</v>
+        <v>1944.514</v>
       </c>
       <c r="G23">
         <v>2369.1</v>
@@ -3179,28 +3179,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M23">
-        <v>190.0355297039239</v>
+        <v>199.084840642206</v>
       </c>
       <c r="N23">
-        <v>323.4311369627428</v>
+        <v>314.3818260244607</v>
       </c>
       <c r="O23">
-        <v>80.8577842406857</v>
+        <v>78.59545650611517</v>
       </c>
       <c r="P23">
-        <v>242.5733527220571</v>
+        <v>235.7863695183455</v>
       </c>
       <c r="Q23">
-        <v>334.5733527220571</v>
+        <v>327.7863695183455</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1247066953423492</v>
+        <v>0.1255074533628724</v>
       </c>
       <c r="T23">
-        <v>0.7630880509586275</v>
+        <v>0.770831993022344</v>
       </c>
       <c r="U23">
         <v>0.1023828270931482</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.701950879746802</v>
+        <v>2.579134930667402</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1147889800934099</v>
+        <v>0.115538125599193</v>
       </c>
       <c r="C24">
-        <v>7232.195525016424</v>
+        <v>7070.679371673483</v>
       </c>
       <c r="D24">
-        <v>6807.609525016424</v>
+        <v>6734.480371673483</v>
       </c>
       <c r="E24">
-        <v>-1176.786</v>
+        <v>-1088.399</v>
       </c>
       <c r="F24">
-        <v>1944.514</v>
+        <v>2032.901</v>
       </c>
       <c r="G24">
         <v>2369.1</v>
@@ -3261,45 +3261,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M24">
-        <v>199.084840642206</v>
+        <v>215.2493050804881</v>
       </c>
       <c r="N24">
-        <v>314.3818260244607</v>
+        <v>298.2173615861786</v>
       </c>
       <c r="O24">
-        <v>78.59545650611517</v>
+        <v>74.55434039654466</v>
       </c>
       <c r="P24">
-        <v>235.7863695183455</v>
+        <v>223.663021189634</v>
       </c>
       <c r="Q24">
-        <v>327.7863695183455</v>
+        <v>315.663021189634</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1255074533628724</v>
+        <v>0.1263290102930195</v>
       </c>
       <c r="T24">
-        <v>0.770831993022344</v>
+        <v>0.7787770764383649</v>
       </c>
       <c r="U24">
-        <v>0.1023828270931482</v>
+        <v>0.1058828270931482</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.07678712031986115</v>
+        <v>0.07941212031986114</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.579134930667402</v>
+        <v>2.385450984265275</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.115538125599193</v>
+        <v>0.1157097711049762</v>
       </c>
       <c r="C25">
-        <v>7070.679371673483</v>
+        <v>6965.757583026456</v>
       </c>
       <c r="D25">
-        <v>6734.480371673483</v>
+        <v>6717.945583026457</v>
       </c>
       <c r="E25">
-        <v>-1088.399</v>
+        <v>-1000.012</v>
       </c>
       <c r="F25">
-        <v>2032.901</v>
+        <v>2121.288</v>
       </c>
       <c r="G25">
         <v>2369.1</v>
@@ -3343,28 +3343,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M25">
-        <v>215.2493050804881</v>
+        <v>224.6079705187702</v>
       </c>
       <c r="N25">
-        <v>298.2173615861786</v>
+        <v>288.8586961478965</v>
       </c>
       <c r="O25">
-        <v>74.55434039654466</v>
+        <v>72.21467403697412</v>
       </c>
       <c r="P25">
-        <v>223.663021189634</v>
+        <v>216.6440221109224</v>
       </c>
       <c r="Q25">
-        <v>315.663021189634</v>
+        <v>308.6440221109224</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1263290102930195</v>
+        <v>0.127172187142381</v>
       </c>
       <c r="T25">
-        <v>0.7787770764383649</v>
+        <v>0.7869312409969127</v>
       </c>
       <c r="U25">
         <v>0.1058828270931482</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.385450984265275</v>
+        <v>2.286057193254221</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1157097711049762</v>
+        <v>0.1164064166107594</v>
       </c>
       <c r="C26">
-        <v>6965.757583026456</v>
+        <v>6811.087278715585</v>
       </c>
       <c r="D26">
-        <v>6717.945583026457</v>
+        <v>6651.662278715586</v>
       </c>
       <c r="E26">
-        <v>-1000.012</v>
+        <v>-911.625</v>
       </c>
       <c r="F26">
-        <v>2121.288</v>
+        <v>2209.675</v>
       </c>
       <c r="G26">
         <v>2369.1</v>
@@ -3425,45 +3425,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M26">
-        <v>224.6079705187701</v>
+        <v>240.1537259570522</v>
       </c>
       <c r="N26">
-        <v>288.8586961478966</v>
+        <v>273.3129407096145</v>
       </c>
       <c r="O26">
-        <v>72.21467403697415</v>
+        <v>68.32823517740361</v>
       </c>
       <c r="P26">
-        <v>216.6440221109224</v>
+        <v>204.9847055322109</v>
       </c>
       <c r="Q26">
-        <v>308.6440221109224</v>
+        <v>296.9847055322109</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.127172187142381</v>
+        <v>0.1280378487077254</v>
       </c>
       <c r="T26">
-        <v>0.7869312409969127</v>
+        <v>0.7953028499436883</v>
       </c>
       <c r="U26">
-        <v>0.1058828270931482</v>
+        <v>0.1086828270931482</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.07941212031986114</v>
+        <v>0.08151212031986114</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.286057193254222</v>
+        <v>2.138074954366905</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1164064166107594</v>
+        <v>0.1165990621165425</v>
       </c>
       <c r="C27">
-        <v>6811.087278715585</v>
+        <v>6704.600987486661</v>
       </c>
       <c r="D27">
-        <v>6651.662278715586</v>
+        <v>6633.562987486662</v>
       </c>
       <c r="E27">
-        <v>-911.625</v>
+        <v>-823.2379999999998</v>
       </c>
       <c r="F27">
-        <v>2209.675</v>
+        <v>2298.062</v>
       </c>
       <c r="G27">
         <v>2369.1</v>
@@ -3507,28 +3507,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M27">
-        <v>240.1537259570522</v>
+        <v>249.7598749953344</v>
       </c>
       <c r="N27">
-        <v>273.3129407096145</v>
+        <v>263.7067916713323</v>
       </c>
       <c r="O27">
-        <v>68.32823517740361</v>
+        <v>65.92669791783308</v>
       </c>
       <c r="P27">
-        <v>204.9847055322109</v>
+        <v>197.7800937534992</v>
       </c>
       <c r="Q27">
-        <v>296.9847055322109</v>
+        <v>289.7800937534993</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1280378487077254</v>
+        <v>0.1289269065315927</v>
       </c>
       <c r="T27">
-        <v>0.7953028499436883</v>
+        <v>0.8039007185917282</v>
       </c>
       <c r="U27">
         <v>0.1086828270931482</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.138074954366905</v>
+        <v>2.05584130227587</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1165990621165425</v>
+        <v>0.1183712076223257</v>
       </c>
       <c r="C28">
-        <v>6704.600987486661</v>
+        <v>6454.226344993753</v>
       </c>
       <c r="D28">
-        <v>6633.562987486662</v>
+        <v>6471.575344993753</v>
       </c>
       <c r="E28">
-        <v>-823.2379999999998</v>
+        <v>-734.8509999999997</v>
       </c>
       <c r="F28">
-        <v>2298.062</v>
+        <v>2386.449000000001</v>
       </c>
       <c r="G28">
         <v>2369.1</v>
@@ -3589,45 +3589,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M28">
-        <v>249.7598749953344</v>
+        <v>277.9803262336165</v>
       </c>
       <c r="N28">
-        <v>263.7067916713323</v>
+        <v>235.4863404330502</v>
       </c>
       <c r="O28">
-        <v>65.92669791783308</v>
+        <v>58.87158510826255</v>
       </c>
       <c r="P28">
-        <v>197.7800937534992</v>
+        <v>176.6147553247877</v>
       </c>
       <c r="Q28">
-        <v>289.7800937534993</v>
+        <v>268.6147553247877</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1289269065315927</v>
+        <v>0.1298403221040592</v>
       </c>
       <c r="T28">
-        <v>0.8039007185917282</v>
+        <v>0.8127341452849199</v>
       </c>
       <c r="U28">
-        <v>0.1086828270931482</v>
+        <v>0.1164828270931482</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.08151212031986114</v>
+        <v>0.08736212031986115</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.05584130227587</v>
+        <v>1.847133117741383</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1183712076223257</v>
+        <v>0.1186223531281089</v>
       </c>
       <c r="C29">
-        <v>6454.226344993753</v>
+        <v>6343.520551472028</v>
       </c>
       <c r="D29">
-        <v>6471.575344993753</v>
+        <v>6449.256551472028</v>
       </c>
       <c r="E29">
-        <v>-734.8509999999997</v>
+        <v>-646.4639999999999</v>
       </c>
       <c r="F29">
-        <v>2386.449000000001</v>
+        <v>2474.836</v>
       </c>
       <c r="G29">
         <v>2369.1</v>
@@ -3671,28 +3671,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M29">
-        <v>277.9803262336165</v>
+        <v>288.2758938718985</v>
       </c>
       <c r="N29">
-        <v>235.4863404330502</v>
+        <v>225.1907727947682</v>
       </c>
       <c r="O29">
-        <v>58.87158510826255</v>
+        <v>56.29769319869204</v>
       </c>
       <c r="P29">
-        <v>176.6147553247877</v>
+        <v>168.8930795960761</v>
       </c>
       <c r="Q29">
-        <v>268.6147553247877</v>
+        <v>260.8930795960761</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1298403221040592</v>
+        <v>0.1307791103313163</v>
       </c>
       <c r="T29">
-        <v>0.8127341452849199</v>
+        <v>0.8218129449418113</v>
       </c>
       <c r="U29">
         <v>0.1164828270931482</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.847133117741383</v>
+        <v>1.781164077822048</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1186223531281089</v>
+        <v>0.119721748633892</v>
       </c>
       <c r="C30">
-        <v>6343.520551472028</v>
+        <v>6159.217480770745</v>
       </c>
       <c r="D30">
-        <v>6449.256551472028</v>
+        <v>6353.340480770745</v>
       </c>
       <c r="E30">
-        <v>-646.4639999999999</v>
+        <v>-558.0769999999998</v>
       </c>
       <c r="F30">
-        <v>2474.836</v>
+        <v>2563.223</v>
       </c>
       <c r="G30">
         <v>2369.1</v>
@@ -3753,45 +3753,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M30">
-        <v>288.2758938718985</v>
+        <v>308.5680312101807</v>
       </c>
       <c r="N30">
-        <v>225.1907727947682</v>
+        <v>204.898635456486</v>
       </c>
       <c r="O30">
-        <v>56.29769319869204</v>
+        <v>51.22465886412151</v>
       </c>
       <c r="P30">
-        <v>168.8930795960761</v>
+        <v>153.6739765923645</v>
       </c>
       <c r="Q30">
-        <v>260.8930795960761</v>
+        <v>245.6739765923645</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1307791103313163</v>
+        <v>0.1317443432973694</v>
       </c>
       <c r="T30">
-        <v>0.8218129449418113</v>
+        <v>0.831147485434108</v>
       </c>
       <c r="U30">
-        <v>0.1164828270931482</v>
+        <v>0.1203828270931482</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.08736212031986115</v>
+        <v>0.09028712031986116</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y30">
-        <v>1.781164077822048</v>
+        <v>1.664030666601751</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.119721748633892</v>
+        <v>0.1200021441396752</v>
       </c>
       <c r="C31">
-        <v>6159.217480770745</v>
+        <v>6046.822439787926</v>
       </c>
       <c r="D31">
-        <v>6353.340480770745</v>
+        <v>6329.332439787927</v>
       </c>
       <c r="E31">
-        <v>-558.0770000000002</v>
+        <v>-469.6900000000001</v>
       </c>
       <c r="F31">
-        <v>2563.223</v>
+        <v>2651.61</v>
       </c>
       <c r="G31">
         <v>2369.1</v>
@@ -3835,28 +3835,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M31">
-        <v>308.5680312101806</v>
+        <v>319.2083081484627</v>
       </c>
       <c r="N31">
-        <v>204.8986354564861</v>
+        <v>194.258358518204</v>
       </c>
       <c r="O31">
-        <v>51.22465886412152</v>
+        <v>48.56458962955099</v>
       </c>
       <c r="P31">
-        <v>153.6739765923646</v>
+        <v>145.693768888653</v>
       </c>
       <c r="Q31">
-        <v>245.6739765923646</v>
+        <v>237.693768888653</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1317443432973694</v>
+        <v>0.1327371543481669</v>
       </c>
       <c r="T31">
-        <v>0.831147485434108</v>
+        <v>0.8407487270833276</v>
       </c>
       <c r="U31">
         <v>0.1203828270931482</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.664030666601751</v>
+        <v>1.608562977715026</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1200021441396752</v>
+        <v>0.1202825396454583</v>
       </c>
       <c r="C32">
-        <v>6046.822439787926</v>
+        <v>5934.608159204158</v>
       </c>
       <c r="D32">
-        <v>6329.332439787927</v>
+        <v>6305.505159204158</v>
       </c>
       <c r="E32">
-        <v>-469.6900000000001</v>
+        <v>-381.3029999999999</v>
       </c>
       <c r="F32">
-        <v>2651.61</v>
+        <v>2739.997</v>
       </c>
       <c r="G32">
         <v>2369.1</v>
@@ -3917,28 +3917,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M32">
-        <v>319.2083081484627</v>
+        <v>329.8485850867448</v>
       </c>
       <c r="N32">
-        <v>194.258358518204</v>
+        <v>183.6180815799219</v>
       </c>
       <c r="O32">
-        <v>48.56458962955099</v>
+        <v>45.90452039498047</v>
       </c>
       <c r="P32">
-        <v>145.693768888653</v>
+        <v>137.7135611849414</v>
       </c>
       <c r="Q32">
-        <v>237.693768888653</v>
+        <v>229.7135611849414</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1327371543481669</v>
+        <v>0.1337587425308716</v>
       </c>
       <c r="T32">
-        <v>0.8407487270833276</v>
+        <v>0.8506282655919448</v>
       </c>
       <c r="U32">
         <v>0.1203828270931482</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.608562977715026</v>
+        <v>1.556673849401638</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1202825396454583</v>
+        <v>0.1205629351512415</v>
       </c>
       <c r="C33">
-        <v>5934.608159204158</v>
+        <v>5822.572605214713</v>
       </c>
       <c r="D33">
-        <v>6305.505159204158</v>
+        <v>6281.856605214713</v>
       </c>
       <c r="E33">
-        <v>-381.3029999999999</v>
+        <v>-292.9159999999997</v>
       </c>
       <c r="F33">
-        <v>2739.997</v>
+        <v>2828.384</v>
       </c>
       <c r="G33">
         <v>2369.1</v>
@@ -3999,28 +3999,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M33">
-        <v>329.8485850867448</v>
+        <v>340.4888620250269</v>
       </c>
       <c r="N33">
-        <v>183.6180815799219</v>
+        <v>172.9778046416398</v>
       </c>
       <c r="O33">
-        <v>45.90452039498047</v>
+        <v>43.24445116040994</v>
       </c>
       <c r="P33">
-        <v>137.7135611849414</v>
+        <v>129.7333534812298</v>
       </c>
       <c r="Q33">
-        <v>229.7135611849414</v>
+        <v>221.7333534812298</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1337587425308716</v>
+        <v>0.1348103774248323</v>
       </c>
       <c r="T33">
-        <v>0.8506282655919448</v>
+        <v>0.8607983787625804</v>
       </c>
       <c r="U33">
         <v>0.1203828270931482</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.556673849401638</v>
+        <v>1.508027791607836</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1205629351512415</v>
+        <v>0.1243578306570247</v>
       </c>
       <c r="C34">
-        <v>5822.572605214713</v>
+        <v>5430.727767851788</v>
       </c>
       <c r="D34">
-        <v>6281.856605214713</v>
+        <v>5978.398767851789</v>
       </c>
       <c r="E34">
-        <v>-292.9159999999997</v>
+        <v>-204.529</v>
       </c>
       <c r="F34">
-        <v>2828.384</v>
+        <v>2916.771</v>
       </c>
       <c r="G34">
         <v>2369.1</v>
@@ -4081,45 +4081,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M34">
-        <v>340.4888620250269</v>
+        <v>392.547287163309</v>
       </c>
       <c r="N34">
-        <v>172.9778046416398</v>
+        <v>120.9193795033577</v>
       </c>
       <c r="O34">
-        <v>43.24445116040994</v>
+        <v>30.22984487583943</v>
       </c>
       <c r="P34">
-        <v>129.7333534812298</v>
+        <v>90.6895346275183</v>
       </c>
       <c r="Q34">
-        <v>221.7333534812298</v>
+        <v>182.6895346275183</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1348103774248323</v>
+        <v>0.1358934044051798</v>
       </c>
       <c r="T34">
-        <v>0.8607983787625804</v>
+        <v>0.8712720774009959</v>
       </c>
       <c r="U34">
-        <v>0.1203828270931482</v>
+        <v>0.1345828270931482</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.09028712031986116</v>
+        <v>0.1009371203198612</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>1.508027791607836</v>
+        <v>1.308037740821407</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1243578306570247</v>
+        <v>0.1247447261628078</v>
       </c>
       <c r="C35">
-        <v>5430.727767851788</v>
+        <v>5313.041589458398</v>
       </c>
       <c r="D35">
-        <v>5978.398767851789</v>
+        <v>5949.099589458398</v>
       </c>
       <c r="E35">
-        <v>-204.529</v>
+        <v>-116.1419999999998</v>
       </c>
       <c r="F35">
-        <v>2916.771</v>
+        <v>3005.158</v>
       </c>
       <c r="G35">
         <v>2369.1</v>
@@ -4163,28 +4163,28 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M35">
-        <v>392.547287163309</v>
+        <v>404.4426595015911</v>
       </c>
       <c r="N35">
-        <v>120.9193795033577</v>
+        <v>109.0240071650756</v>
       </c>
       <c r="O35">
-        <v>30.22984487583943</v>
+        <v>27.2560017912689</v>
       </c>
       <c r="P35">
-        <v>90.6895346275183</v>
+        <v>81.7680053738067</v>
       </c>
       <c r="Q35">
-        <v>182.6895346275183</v>
+        <v>173.7680053738067</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1358934044051798</v>
+        <v>0.1370092503849319</v>
       </c>
       <c r="T35">
-        <v>0.8712720774009959</v>
+        <v>0.8820631608466362</v>
       </c>
       <c r="U35">
         <v>0.1345828270931482</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.308037740821407</v>
+        <v>1.269566042561954</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1247447261628078</v>
+        <v>0.132639121668591</v>
       </c>
       <c r="C36">
-        <v>5313.041589458398</v>
+        <v>4683.832156434371</v>
       </c>
       <c r="D36">
-        <v>5949.099589458398</v>
+        <v>5408.277156434371</v>
       </c>
       <c r="E36">
-        <v>-116.1419999999998</v>
+        <v>-27.75499999999965</v>
       </c>
       <c r="F36">
-        <v>3005.158</v>
+        <v>3093.545000000001</v>
       </c>
       <c r="G36">
         <v>2369.1</v>
@@ -4245,45 +4245,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M36">
-        <v>404.4426595015911</v>
+        <v>504.8134188398733</v>
       </c>
       <c r="N36">
-        <v>109.0240071650756</v>
+        <v>8.653247826793404</v>
       </c>
       <c r="O36">
-        <v>27.2560017912689</v>
+        <v>2.163311956698351</v>
       </c>
       <c r="P36">
-        <v>81.7680053738067</v>
+        <v>6.489935870095053</v>
       </c>
       <c r="Q36">
-        <v>173.7680053738067</v>
+        <v>98.48993587009505</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1370092503849319</v>
+        <v>0.1381594300871378</v>
       </c>
       <c r="T36">
-        <v>0.8820631608466362</v>
+        <v>0.8931862776290654</v>
       </c>
       <c r="U36">
-        <v>0.1345828270931482</v>
+        <v>0.1631828270931482</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.1009371203198612</v>
+        <v>0.1223871203198612</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.269566042561954</v>
+        <v>1.017141477432751</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.132639121668591</v>
+        <v>0.133469517923128</v>
       </c>
       <c r="C37">
-        <v>4683.832156434371</v>
+        <v>4544.218536275024</v>
       </c>
       <c r="D37">
-        <v>5408.277156434371</v>
+        <v>5357.050536275025</v>
       </c>
       <c r="E37">
-        <v>-27.75499999999965</v>
+        <v>60.63200000000052</v>
       </c>
       <c r="F37">
-        <v>3093.545000000001</v>
+        <v>3181.932000000001</v>
       </c>
       <c r="G37">
         <v>2369.1</v>
@@ -4327,37 +4327,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M37">
-        <v>504.8134188398733</v>
+        <v>519.2366593781554</v>
       </c>
       <c r="N37">
-        <v>8.653247826793404</v>
+        <v>-5.769992711488726</v>
       </c>
       <c r="O37">
-        <v>2.163311956698351</v>
+        <v>-1.442498177872181</v>
       </c>
       <c r="P37">
-        <v>6.489935870095053</v>
+        <v>-4.327494533616544</v>
       </c>
       <c r="Q37">
-        <v>98.48993587009505</v>
+        <v>87.67250546638346</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1381594300871378</v>
+        <v>0.1394483626260901</v>
       </c>
       <c r="T37">
-        <v>0.8931862776290654</v>
+        <v>0.9056512403891823</v>
       </c>
       <c r="U37">
         <v>0.1631828270931482</v>
       </c>
       <c r="V37">
-        <v>0.25</v>
+        <v>0.2472218868760158</v>
       </c>
       <c r="W37">
-        <v>0.1223871203198612</v>
+        <v>0.1228404606734175</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.017141477432751</v>
+        <v>0.988887547504063</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.133469517923128</v>
+        <v>0.1346433461940595</v>
       </c>
       <c r="C38">
-        <v>4544.218536275024</v>
+        <v>4385.052376803106</v>
       </c>
       <c r="D38">
-        <v>5357.050536275025</v>
+        <v>5286.271376803106</v>
       </c>
       <c r="E38">
-        <v>60.63200000000006</v>
+        <v>149.0190000000002</v>
       </c>
       <c r="F38">
-        <v>3181.932</v>
+        <v>3270.319</v>
       </c>
       <c r="G38">
         <v>2369.1</v>
@@ -4409,37 +4409,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M38">
-        <v>519.2366593781553</v>
+        <v>533.6598999164374</v>
       </c>
       <c r="N38">
-        <v>-5.769992711488612</v>
+        <v>-20.19323324977074</v>
       </c>
       <c r="O38">
-        <v>-1.442498177872153</v>
+        <v>-5.048308312442686</v>
       </c>
       <c r="P38">
-        <v>-4.327494533616459</v>
+        <v>-15.14492493732806</v>
       </c>
       <c r="Q38">
-        <v>87.67250546638354</v>
+        <v>76.85507506267194</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1394483626260901</v>
+        <v>0.140934844572536</v>
       </c>
       <c r="T38">
-        <v>0.9056512403891822</v>
+        <v>0.9200266569032963</v>
       </c>
       <c r="U38">
         <v>0.1631828270931482</v>
       </c>
       <c r="V38">
-        <v>0.2472218868760158</v>
+        <v>0.2405402142577451</v>
       </c>
       <c r="W38">
-        <v>0.1228404606734175</v>
+        <v>0.1239307949009778</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.9888875475040633</v>
+        <v>0.9621608570309804</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1346433461940595</v>
+        <v>0.1358171744649909</v>
       </c>
       <c r="C39">
-        <v>4385.052376803106</v>
+        <v>4227.732144597283</v>
       </c>
       <c r="D39">
-        <v>5286.271376803106</v>
+        <v>5217.338144597284</v>
       </c>
       <c r="E39">
-        <v>149.0190000000002</v>
+        <v>237.4059999999999</v>
       </c>
       <c r="F39">
-        <v>3270.319</v>
+        <v>3358.706</v>
       </c>
       <c r="G39">
         <v>2369.1</v>
@@ -4491,37 +4491,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M39">
-        <v>533.6598999164374</v>
+        <v>548.0831404547195</v>
       </c>
       <c r="N39">
-        <v>-20.19323324977074</v>
+        <v>-34.61647378805276</v>
       </c>
       <c r="O39">
-        <v>-5.048308312442686</v>
+        <v>-8.65411844701319</v>
       </c>
       <c r="P39">
-        <v>-15.14492493732806</v>
+        <v>-25.96235534103957</v>
       </c>
       <c r="Q39">
-        <v>76.85507506267194</v>
+        <v>66.03764465896043</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.140934844572536</v>
+        <v>0.1424692775495124</v>
       </c>
       <c r="T39">
-        <v>0.9200266569032963</v>
+        <v>0.9348657965307687</v>
       </c>
       <c r="U39">
         <v>0.1631828270931482</v>
       </c>
       <c r="V39">
-        <v>0.2405402142577451</v>
+        <v>0.2342102086193834</v>
       </c>
       <c r="W39">
-        <v>0.1239307949009778</v>
+        <v>0.1249637431165612</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.9621608570309804</v>
+        <v>0.9368408344775337</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1358171744649909</v>
+        <v>0.1369910027359224</v>
       </c>
       <c r="C40">
-        <v>4227.732144597283</v>
+        <v>4072.186556256362</v>
       </c>
       <c r="D40">
-        <v>5217.338144597284</v>
+        <v>5150.179556256363</v>
       </c>
       <c r="E40">
-        <v>237.4059999999999</v>
+        <v>325.7930000000001</v>
       </c>
       <c r="F40">
-        <v>3358.706</v>
+        <v>3447.093</v>
       </c>
       <c r="G40">
         <v>2369.1</v>
@@ -4573,37 +4573,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M40">
-        <v>548.0831404547195</v>
+        <v>562.5063809930016</v>
       </c>
       <c r="N40">
-        <v>-34.61647378805276</v>
+        <v>-49.03971432633489</v>
       </c>
       <c r="O40">
-        <v>-8.65411844701319</v>
+        <v>-12.25992858158372</v>
       </c>
       <c r="P40">
-        <v>-25.96235534103957</v>
+        <v>-36.77978574475117</v>
       </c>
       <c r="Q40">
-        <v>66.03764465896043</v>
+        <v>55.22021425524883</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1424692775495124</v>
+        <v>0.1440540198044224</v>
       </c>
       <c r="T40">
-        <v>0.9348657965307687</v>
+        <v>0.9501914653263551</v>
       </c>
       <c r="U40">
         <v>0.1631828270931482</v>
       </c>
       <c r="V40">
-        <v>0.2342102086193834</v>
+        <v>0.2282048186547838</v>
       </c>
       <c r="W40">
-        <v>0.1249637431165612</v>
+        <v>0.1259437196287814</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.9368408344775337</v>
+        <v>0.9128192746191354</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1369910027359224</v>
+        <v>0.1381648310068539</v>
       </c>
       <c r="C41">
-        <v>4072.186556256362</v>
+        <v>3918.347952029872</v>
       </c>
       <c r="D41">
-        <v>5150.179556256363</v>
+        <v>5084.727952029873</v>
       </c>
       <c r="E41">
-        <v>325.7930000000001</v>
+        <v>414.1800000000003</v>
       </c>
       <c r="F41">
-        <v>3447.093</v>
+        <v>3535.48</v>
       </c>
       <c r="G41">
         <v>2369.1</v>
@@ -4655,37 +4655,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M41">
-        <v>562.5063809930016</v>
+        <v>576.9296215312837</v>
       </c>
       <c r="N41">
-        <v>-49.03971432633489</v>
+        <v>-63.46295486461702</v>
       </c>
       <c r="O41">
-        <v>-12.25992858158372</v>
+        <v>-15.86573871615425</v>
       </c>
       <c r="P41">
-        <v>-36.77978574475117</v>
+        <v>-47.59721614846276</v>
       </c>
       <c r="Q41">
-        <v>55.22021425524883</v>
+        <v>44.40278385153724</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1440540198044224</v>
+        <v>0.1456915868011628</v>
       </c>
       <c r="T41">
-        <v>0.9501914653263551</v>
+        <v>0.9660279897484612</v>
       </c>
       <c r="U41">
         <v>0.1631828270931482</v>
       </c>
       <c r="V41">
-        <v>0.2282048186547838</v>
+        <v>0.2224996981884142</v>
       </c>
       <c r="W41">
-        <v>0.1259437196287814</v>
+        <v>0.1268746973153906</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.9128192746191354</v>
+        <v>0.8899987927536569</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1381648310068539</v>
+        <v>0.1393386592777854</v>
       </c>
       <c r="C42">
-        <v>3918.347952029872</v>
+        <v>3766.152068449844</v>
       </c>
       <c r="D42">
-        <v>5084.727952029873</v>
+        <v>5020.919068449845</v>
       </c>
       <c r="E42">
-        <v>414.1800000000003</v>
+        <v>502.5670000000005</v>
       </c>
       <c r="F42">
-        <v>3535.48</v>
+        <v>3623.867000000001</v>
       </c>
       <c r="G42">
         <v>2369.1</v>
@@ -4737,37 +4737,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M42">
-        <v>576.9296215312837</v>
+        <v>591.3528620695658</v>
       </c>
       <c r="N42">
-        <v>-63.46295486461702</v>
+        <v>-77.88619540289915</v>
       </c>
       <c r="O42">
-        <v>-15.86573871615425</v>
+        <v>-19.47154885072479</v>
       </c>
       <c r="P42">
-        <v>-47.59721614846276</v>
+        <v>-58.41464655217436</v>
       </c>
       <c r="Q42">
-        <v>44.40278385153724</v>
+        <v>33.58535344782564</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1456915868011628</v>
+        <v>0.1473846645435554</v>
       </c>
       <c r="T42">
-        <v>0.9660279897484612</v>
+        <v>0.9824013455069095</v>
       </c>
       <c r="U42">
         <v>0.1631828270931482</v>
       </c>
       <c r="V42">
-        <v>0.2224996981884142</v>
+        <v>0.2170728762813797</v>
       </c>
       <c r="W42">
-        <v>0.1268746973153906</v>
+        <v>0.1277602614563115</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8899987927536569</v>
+        <v>0.8682915051255189</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1393386592777854</v>
+        <v>0.1405124875487169</v>
       </c>
       <c r="C43">
-        <v>3766.152068449844</v>
+        <v>3615.537827870043</v>
       </c>
       <c r="D43">
-        <v>5020.919068449845</v>
+        <v>4958.691827870044</v>
       </c>
       <c r="E43">
-        <v>502.5670000000005</v>
+        <v>590.9540000000006</v>
       </c>
       <c r="F43">
-        <v>3623.867000000001</v>
+        <v>3712.254000000001</v>
       </c>
       <c r="G43">
         <v>2369.1</v>
@@ -4819,37 +4819,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M43">
-        <v>591.3528620695658</v>
+        <v>605.776102607848</v>
       </c>
       <c r="N43">
-        <v>-77.88619540289915</v>
+        <v>-92.30943594118128</v>
       </c>
       <c r="O43">
-        <v>-19.47154885072479</v>
+        <v>-23.07735898529532</v>
       </c>
       <c r="P43">
-        <v>-58.41464655217436</v>
+        <v>-69.23207695588596</v>
       </c>
       <c r="Q43">
-        <v>33.58535344782564</v>
+        <v>22.76792304411404</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1473846645435554</v>
+        <v>0.149136124277065</v>
       </c>
       <c r="T43">
-        <v>0.9824013455069095</v>
+        <v>0.9993392997397874</v>
       </c>
       <c r="U43">
         <v>0.1631828270931482</v>
       </c>
       <c r="V43">
-        <v>0.2170728762813797</v>
+        <v>0.2119044744651564</v>
       </c>
       <c r="W43">
-        <v>0.1277602614563115</v>
+        <v>0.1286036558762362</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8682915051255189</v>
+        <v>0.8476178978606255</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1405124875487169</v>
+        <v>0.1416863158196484</v>
       </c>
       <c r="C44">
-        <v>3615.537827870043</v>
+        <v>3466.447143463827</v>
       </c>
       <c r="D44">
-        <v>4958.691827870044</v>
+        <v>4897.988143463827</v>
       </c>
       <c r="E44">
-        <v>590.9540000000002</v>
+        <v>679.3409999999999</v>
       </c>
       <c r="F44">
-        <v>3712.254</v>
+        <v>3800.641</v>
       </c>
       <c r="G44">
         <v>2369.1</v>
@@ -4901,37 +4901,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M44">
-        <v>605.7761026078479</v>
+        <v>620.1993431461299</v>
       </c>
       <c r="N44">
-        <v>-92.30943594118116</v>
+        <v>-106.7326764794632</v>
       </c>
       <c r="O44">
-        <v>-23.07735898529529</v>
+        <v>-26.68316911986579</v>
       </c>
       <c r="P44">
-        <v>-69.23207695588587</v>
+        <v>-80.04950735959738</v>
       </c>
       <c r="Q44">
-        <v>22.76792304411413</v>
+        <v>11.95049264040262</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.149136124277065</v>
+        <v>0.1509490387380661</v>
       </c>
       <c r="T44">
-        <v>0.9993392997397872</v>
+        <v>1.016871568156275</v>
       </c>
       <c r="U44">
         <v>0.1631828270931482</v>
       </c>
       <c r="V44">
-        <v>0.2119044744651564</v>
+        <v>0.206976463431083</v>
       </c>
       <c r="W44">
-        <v>0.1286036558762362</v>
+        <v>0.1294078226487225</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8476178978606257</v>
+        <v>0.8279058537243322</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1416863158196484</v>
+        <v>0.1428601440905798</v>
       </c>
       <c r="C45">
-        <v>3466.447143463827</v>
+        <v>3318.824738371912</v>
       </c>
       <c r="D45">
-        <v>4897.988143463827</v>
+        <v>4838.752738371913</v>
       </c>
       <c r="E45">
-        <v>679.3409999999999</v>
+        <v>767.7280000000001</v>
       </c>
       <c r="F45">
-        <v>3800.641</v>
+        <v>3889.028</v>
       </c>
       <c r="G45">
         <v>2369.1</v>
@@ -4983,37 +4983,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M45">
-        <v>620.1993431461299</v>
+        <v>634.622583684412</v>
       </c>
       <c r="N45">
-        <v>-106.7326764794632</v>
+        <v>-121.1559170177453</v>
       </c>
       <c r="O45">
-        <v>-26.68316911986579</v>
+        <v>-30.28897925443633</v>
       </c>
       <c r="P45">
-        <v>-80.04950735959738</v>
+        <v>-90.86693776330898</v>
       </c>
       <c r="Q45">
-        <v>11.95049264040262</v>
+        <v>1.133062236691018</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1509490387380661</v>
+        <v>0.152826700144103</v>
       </c>
       <c r="T45">
-        <v>1.016871568156275</v>
+        <v>1.035029989016208</v>
       </c>
       <c r="U45">
         <v>0.1631828270931482</v>
       </c>
       <c r="V45">
-        <v>0.206976463431083</v>
+        <v>0.2022724528985584</v>
       </c>
       <c r="W45">
-        <v>0.1294078226487225</v>
+        <v>0.1301754363860958</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8279058537243322</v>
+        <v>0.8090898115942337</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1428601440905798</v>
+        <v>0.1575867468365181</v>
       </c>
       <c r="C46">
-        <v>3318.824738371912</v>
+        <v>2592.988386097303</v>
       </c>
       <c r="D46">
-        <v>4838.752738371913</v>
+        <v>4201.303386097303</v>
       </c>
       <c r="E46">
-        <v>767.7280000000001</v>
+        <v>856.1150000000002</v>
       </c>
       <c r="F46">
-        <v>3889.028</v>
+        <v>3977.415</v>
       </c>
       <c r="G46">
         <v>2369.1</v>
@@ -5065,45 +5065,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M46">
-        <v>634.622583684412</v>
+        <v>761.2089272226942</v>
       </c>
       <c r="N46">
-        <v>-121.1559170177453</v>
+        <v>-247.7422605560275</v>
       </c>
       <c r="O46">
-        <v>-30.28897925443633</v>
+        <v>-61.93556513900688</v>
       </c>
       <c r="P46">
-        <v>-90.86693776330898</v>
+        <v>-185.8066954170206</v>
       </c>
       <c r="Q46">
-        <v>1.133062236691018</v>
+        <v>-93.80669541702065</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.152826700144103</v>
+        <v>0.1563413210103718</v>
       </c>
       <c r="T46">
-        <v>1.035029989016208</v>
+        <v>1.069019058955881</v>
       </c>
       <c r="U46">
-        <v>0.1631828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V46">
-        <v>0.2022724528985584</v>
+        <v>0.1686352617211392</v>
       </c>
       <c r="W46">
-        <v>0.1301754363860958</v>
+        <v>0.1591089339573636</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.8090898115942337</v>
+        <v>0.674541046884557</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1575867468365181</v>
+        <v>0.1590425751074496</v>
       </c>
       <c r="C47">
-        <v>2592.988386097303</v>
+        <v>2450.590107755767</v>
       </c>
       <c r="D47">
-        <v>4201.303386097303</v>
+        <v>4147.292107755768</v>
       </c>
       <c r="E47">
-        <v>856.1150000000002</v>
+        <v>944.5020000000004</v>
       </c>
       <c r="F47">
-        <v>3977.415</v>
+        <v>4065.802000000001</v>
       </c>
       <c r="G47">
         <v>2369.1</v>
@@ -5147,37 +5147,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M47">
-        <v>761.2089272226942</v>
+        <v>778.1246811609764</v>
       </c>
       <c r="N47">
-        <v>-247.7422605560275</v>
+        <v>-264.6580144943097</v>
       </c>
       <c r="O47">
-        <v>-61.93556513900688</v>
+        <v>-66.16450362357742</v>
       </c>
       <c r="P47">
-        <v>-185.8066954170206</v>
+        <v>-198.4935108707323</v>
       </c>
       <c r="Q47">
-        <v>-93.80669541702065</v>
+        <v>-106.4935108707323</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1563413210103718</v>
+        <v>0.1583883825105639</v>
       </c>
       <c r="T47">
-        <v>1.069019058955881</v>
+        <v>1.088815708195805</v>
       </c>
       <c r="U47">
         <v>0.1913828270931482</v>
       </c>
       <c r="V47">
-        <v>0.1686352617211392</v>
+        <v>0.1649692777706797</v>
       </c>
       <c r="W47">
-        <v>0.1591089339573636</v>
+        <v>0.1598105403298807</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.674541046884557</v>
+        <v>0.6598771110827187</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1590425751074496</v>
+        <v>0.1869770859282539</v>
       </c>
       <c r="C48">
-        <v>2450.590107755767</v>
+        <v>1541.584269369941</v>
       </c>
       <c r="D48">
-        <v>4147.292107755768</v>
+        <v>3326.673269369942</v>
       </c>
       <c r="E48">
-        <v>944.5020000000004</v>
+        <v>1032.889</v>
       </c>
       <c r="F48">
-        <v>4065.802000000001</v>
+        <v>4154.189</v>
       </c>
       <c r="G48">
         <v>2369.1</v>
@@ -5229,45 +5229,45 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M48">
-        <v>778.1246811609764</v>
+        <v>1019.366641099258</v>
       </c>
       <c r="N48">
-        <v>-264.6580144943097</v>
+        <v>-505.8999744325916</v>
       </c>
       <c r="O48">
-        <v>-66.16450362357742</v>
+        <v>-126.4749936081479</v>
       </c>
       <c r="P48">
-        <v>-198.4935108707323</v>
+        <v>-379.4249808244438</v>
       </c>
       <c r="Q48">
-        <v>-106.4935108707323</v>
+        <v>-287.4249808244438</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1583883825105639</v>
+        <v>0.162585677557693</v>
       </c>
       <c r="T48">
-        <v>1.088815708195805</v>
+        <v>1.129406759220256</v>
       </c>
       <c r="U48">
-        <v>0.1913828270931482</v>
+        <v>0.2453828270931482</v>
       </c>
       <c r="V48">
-        <v>0.1649692777706797</v>
+        <v>0.1259278668647028</v>
       </c>
       <c r="W48">
-        <v>0.1598105403298807</v>
+        <v>0.2144822911120778</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.6598771110827187</v>
+        <v>0.5037114674588112</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1869770859282539</v>
+        <v>0.1889729141991854</v>
       </c>
       <c r="C49">
-        <v>1541.584269369941</v>
+        <v>1406.82349402076</v>
       </c>
       <c r="D49">
-        <v>3326.673269369942</v>
+        <v>3280.299494020762</v>
       </c>
       <c r="E49">
-        <v>1032.889</v>
+        <v>1121.276000000001</v>
       </c>
       <c r="F49">
-        <v>4154.189</v>
+        <v>4242.576000000001</v>
       </c>
       <c r="G49">
         <v>2369.1</v>
@@ -5311,37 +5311,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M49">
-        <v>1019.366641099258</v>
+        <v>1041.055293037541</v>
       </c>
       <c r="N49">
-        <v>-505.8999744325916</v>
+        <v>-527.588626370874</v>
       </c>
       <c r="O49">
-        <v>-126.4749936081479</v>
+        <v>-131.8971565927185</v>
       </c>
       <c r="P49">
-        <v>-379.4249808244438</v>
+        <v>-395.6914697781555</v>
       </c>
       <c r="Q49">
-        <v>-287.4249808244438</v>
+        <v>-303.6914697781555</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.162585677557693</v>
+        <v>0.164831555972264</v>
       </c>
       <c r="T49">
-        <v>1.129406759220256</v>
+        <v>1.151126119974491</v>
       </c>
       <c r="U49">
         <v>0.2453828270931482</v>
       </c>
       <c r="V49">
-        <v>0.1259278668647028</v>
+        <v>0.1233043696383548</v>
       </c>
       <c r="W49">
-        <v>0.2144822911120778</v>
+        <v>0.2151260522783502</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5037114674588112</v>
+        <v>0.4932174785534191</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1889729141991854</v>
+        <v>0.1909687424701169</v>
       </c>
       <c r="C50">
-        <v>1406.823494020761</v>
+        <v>1273.337842920738</v>
       </c>
       <c r="D50">
-        <v>3280.299494020762</v>
+        <v>3235.200842920739</v>
       </c>
       <c r="E50">
-        <v>1121.276</v>
+        <v>1209.663</v>
       </c>
       <c r="F50">
-        <v>4242.576</v>
+        <v>4330.963000000001</v>
       </c>
       <c r="G50">
         <v>2369.1</v>
@@ -5393,37 +5393,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M50">
-        <v>1041.05529303754</v>
+        <v>1062.743944975823</v>
       </c>
       <c r="N50">
-        <v>-527.5886263708737</v>
+        <v>-549.2772783091559</v>
       </c>
       <c r="O50">
-        <v>-131.8971565927184</v>
+        <v>-137.319319577289</v>
       </c>
       <c r="P50">
-        <v>-395.6914697781553</v>
+        <v>-411.9579587318669</v>
       </c>
       <c r="Q50">
-        <v>-303.6914697781553</v>
+        <v>-319.9579587318669</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.164831555972264</v>
+        <v>0.1671655080501516</v>
       </c>
       <c r="T50">
-        <v>1.151126119974491</v>
+        <v>1.173697220366148</v>
       </c>
       <c r="U50">
         <v>0.2453828270931482</v>
       </c>
       <c r="V50">
-        <v>0.1233043696383548</v>
+        <v>0.1207879539314496</v>
       </c>
       <c r="W50">
-        <v>0.2151260522783502</v>
+        <v>0.2157435374786522</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4932174785534192</v>
+        <v>0.4831518157257985</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1909687424701169</v>
+        <v>0.1929645707410483</v>
       </c>
       <c r="C51">
-        <v>1273.337842920738</v>
+        <v>1141.075436823137</v>
       </c>
       <c r="D51">
-        <v>3235.200842920739</v>
+        <v>3191.325436823138</v>
       </c>
       <c r="E51">
-        <v>1209.663</v>
+        <v>1298.05</v>
       </c>
       <c r="F51">
-        <v>4330.963000000001</v>
+        <v>4419.35</v>
       </c>
       <c r="G51">
         <v>2369.1</v>
@@ -5475,37 +5475,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M51">
-        <v>1062.743944975823</v>
+        <v>1084.432596914105</v>
       </c>
       <c r="N51">
-        <v>-549.2772783091559</v>
+        <v>-570.9659302474379</v>
       </c>
       <c r="O51">
-        <v>-137.319319577289</v>
+        <v>-142.7414825618595</v>
       </c>
       <c r="P51">
-        <v>-411.9579587318669</v>
+        <v>-428.2244476855784</v>
       </c>
       <c r="Q51">
-        <v>-319.9579587318669</v>
+        <v>-336.2244476855784</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1671655080501516</v>
+        <v>0.1695928182111546</v>
       </c>
       <c r="T51">
-        <v>1.173697220366148</v>
+        <v>1.197171164773471</v>
       </c>
       <c r="U51">
         <v>0.2453828270931482</v>
       </c>
       <c r="V51">
-        <v>0.1207879539314496</v>
+        <v>0.1183721948528206</v>
       </c>
       <c r="W51">
-        <v>0.2157435374786522</v>
+        <v>0.2163363232709421</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4831518157257985</v>
+        <v>0.4734887794112825</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1929645707410483</v>
+        <v>0.1949603990119798</v>
       </c>
       <c r="C52">
-        <v>1141.075436823137</v>
+        <v>1009.987173144948</v>
       </c>
       <c r="D52">
-        <v>3191.325436823138</v>
+        <v>3148.624173144949</v>
       </c>
       <c r="E52">
-        <v>1298.05</v>
+        <v>1386.437</v>
       </c>
       <c r="F52">
-        <v>4419.35</v>
+        <v>4507.737</v>
       </c>
       <c r="G52">
         <v>2369.1</v>
@@ -5557,37 +5557,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M52">
-        <v>1084.432596914105</v>
+        <v>1106.121248852387</v>
       </c>
       <c r="N52">
-        <v>-570.9659302474379</v>
+        <v>-592.6545821857198</v>
       </c>
       <c r="O52">
-        <v>-142.7414825618595</v>
+        <v>-148.16364554643</v>
       </c>
       <c r="P52">
-        <v>-428.2244476855784</v>
+        <v>-444.4909366392899</v>
       </c>
       <c r="Q52">
-        <v>-336.2244476855784</v>
+        <v>-352.4909366392899</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1695928182111546</v>
+        <v>0.1721192022562802</v>
       </c>
       <c r="T52">
-        <v>1.197171164773471</v>
+        <v>1.221603229360685</v>
       </c>
       <c r="U52">
         <v>0.2453828270931482</v>
       </c>
       <c r="V52">
-        <v>0.1183721948528206</v>
+        <v>0.116051171424334</v>
       </c>
       <c r="W52">
-        <v>0.2163363232709421</v>
+        <v>0.2169058625615736</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4734887794112825</v>
+        <v>0.4642046856973359</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1949603990119798</v>
+        <v>0.1969562272829113</v>
       </c>
       <c r="C53">
-        <v>1009.987173144948</v>
+        <v>880.0265426550895</v>
       </c>
       <c r="D53">
-        <v>3148.624173144949</v>
+        <v>3107.05054265509</v>
       </c>
       <c r="E53">
-        <v>1386.437</v>
+        <v>1474.824000000001</v>
       </c>
       <c r="F53">
-        <v>4507.737</v>
+        <v>4596.124000000001</v>
       </c>
       <c r="G53">
         <v>2369.1</v>
@@ -5639,37 +5639,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M53">
-        <v>1106.121248852387</v>
+        <v>1127.809900790669</v>
       </c>
       <c r="N53">
-        <v>-592.6545821857198</v>
+        <v>-614.3432341240023</v>
       </c>
       <c r="O53">
-        <v>-148.16364554643</v>
+        <v>-153.5858085310006</v>
       </c>
       <c r="P53">
-        <v>-444.4909366392899</v>
+        <v>-460.7574255930017</v>
       </c>
       <c r="Q53">
-        <v>-352.4909366392899</v>
+        <v>-368.7574255930017</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1721192022562802</v>
+        <v>0.174750852303286</v>
       </c>
       <c r="T53">
-        <v>1.221603229360685</v>
+        <v>1.247053296639032</v>
       </c>
       <c r="U53">
         <v>0.2453828270931482</v>
       </c>
       <c r="V53">
-        <v>0.116051171424334</v>
+        <v>0.1138194181277121</v>
       </c>
       <c r="W53">
-        <v>0.2169058625615736</v>
+        <v>0.2174534964948731</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4642046856973359</v>
+        <v>0.4552776725108485</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1969562272829113</v>
+        <v>0.1989520555538428</v>
       </c>
       <c r="C54">
-        <v>880.0265426550895</v>
+        <v>751.1494604957679</v>
       </c>
       <c r="D54">
-        <v>3107.05054265509</v>
+        <v>3066.560460495768</v>
       </c>
       <c r="E54">
-        <v>1474.824000000001</v>
+        <v>1563.211</v>
       </c>
       <c r="F54">
-        <v>4596.124000000001</v>
+        <v>4684.511</v>
       </c>
       <c r="G54">
         <v>2369.1</v>
@@ -5721,37 +5721,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M54">
-        <v>1127.809900790669</v>
+        <v>1149.498552728951</v>
       </c>
       <c r="N54">
-        <v>-614.3432341240023</v>
+        <v>-636.0318860622842</v>
       </c>
       <c r="O54">
-        <v>-153.5858085310006</v>
+        <v>-159.0079715155711</v>
       </c>
       <c r="P54">
-        <v>-460.7574255930017</v>
+        <v>-477.0239145467132</v>
       </c>
       <c r="Q54">
-        <v>-368.7574255930017</v>
+        <v>-385.0239145467132</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.174750852303286</v>
+        <v>0.1774944874586751</v>
       </c>
       <c r="T54">
-        <v>1.247053296639032</v>
+        <v>1.273586345503693</v>
       </c>
       <c r="U54">
         <v>0.2453828270931482</v>
       </c>
       <c r="V54">
-        <v>0.1138194181277121</v>
+        <v>0.1116718819366232</v>
       </c>
       <c r="W54">
-        <v>0.2174534964948731</v>
+        <v>0.2179804649967273</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4552776725108485</v>
+        <v>0.4466875277464929</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1989520555538428</v>
+        <v>0.2009478838247743</v>
       </c>
       <c r="C55">
-        <v>751.1494604957679</v>
+        <v>623.3141102463342</v>
       </c>
       <c r="D55">
-        <v>3066.560460495768</v>
+        <v>3027.112110246335</v>
       </c>
       <c r="E55">
-        <v>1563.211</v>
+        <v>1651.598000000001</v>
       </c>
       <c r="F55">
-        <v>4684.511</v>
+        <v>4772.898000000001</v>
       </c>
       <c r="G55">
         <v>2369.1</v>
@@ -5803,37 +5803,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M55">
-        <v>1149.498552728951</v>
+        <v>1171.187204667233</v>
       </c>
       <c r="N55">
-        <v>-636.0318860622842</v>
+        <v>-657.7205380005664</v>
       </c>
       <c r="O55">
-        <v>-159.0079715155711</v>
+        <v>-164.4301345001416</v>
       </c>
       <c r="P55">
-        <v>-477.0239145467132</v>
+        <v>-493.2904035004248</v>
       </c>
       <c r="Q55">
-        <v>-385.0239145467132</v>
+        <v>-401.2904035004248</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1774944874586751</v>
+        <v>0.1803574110990811</v>
       </c>
       <c r="T55">
-        <v>1.273586345503693</v>
+        <v>1.301273005188555</v>
       </c>
       <c r="U55">
         <v>0.2453828270931482</v>
       </c>
       <c r="V55">
-        <v>0.1116718819366232</v>
+        <v>0.109603884122982</v>
       </c>
       <c r="W55">
-        <v>0.2179804649967273</v>
+        <v>0.218487916146661</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4466875277464929</v>
+        <v>0.4384155364919282</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2009478838247743</v>
+        <v>0.2029437120957057</v>
       </c>
       <c r="C56">
-        <v>623.3141102463342</v>
+        <v>496.4807998700771</v>
       </c>
       <c r="D56">
-        <v>3027.112110246335</v>
+        <v>2988.665799870078</v>
       </c>
       <c r="E56">
-        <v>1651.598000000001</v>
+        <v>1739.985000000001</v>
       </c>
       <c r="F56">
-        <v>4772.898000000001</v>
+        <v>4861.285000000001</v>
       </c>
       <c r="G56">
         <v>2369.1</v>
@@ -5885,37 +5885,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M56">
-        <v>1171.187204667233</v>
+        <v>1192.875856605515</v>
       </c>
       <c r="N56">
-        <v>-657.7205380005664</v>
+        <v>-679.4091899388484</v>
       </c>
       <c r="O56">
-        <v>-164.4301345001416</v>
+        <v>-169.8522974847121</v>
       </c>
       <c r="P56">
-        <v>-493.2904035004248</v>
+        <v>-509.5568924541363</v>
       </c>
       <c r="Q56">
-        <v>-401.2904035004248</v>
+        <v>-417.5568924541363</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1803574110990811</v>
+        <v>0.1833475757901718</v>
       </c>
       <c r="T56">
-        <v>1.301273005188555</v>
+        <v>1.330190183081635</v>
       </c>
       <c r="U56">
         <v>0.2453828270931482</v>
       </c>
       <c r="V56">
-        <v>0.109603884122982</v>
+        <v>0.1076110862298369</v>
       </c>
       <c r="W56">
-        <v>0.218487916146661</v>
+        <v>0.2189769145275063</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4384155364919282</v>
+        <v>0.4304443449193477</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2029437120957057</v>
+        <v>0.2049395403666373</v>
       </c>
       <c r="C57">
-        <v>496.4807998700771</v>
+        <v>370.6118285007715</v>
       </c>
       <c r="D57">
-        <v>2988.665799870078</v>
+        <v>2951.183828500772</v>
       </c>
       <c r="E57">
-        <v>1739.985000000001</v>
+        <v>1828.372</v>
       </c>
       <c r="F57">
-        <v>4861.285000000001</v>
+        <v>4949.672</v>
       </c>
       <c r="G57">
         <v>2369.1</v>
@@ -5967,37 +5967,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M57">
-        <v>1192.875856605515</v>
+        <v>1214.564508543797</v>
       </c>
       <c r="N57">
-        <v>-679.4091899388484</v>
+        <v>-701.0978418771306</v>
       </c>
       <c r="O57">
-        <v>-169.8522974847121</v>
+        <v>-175.2744604692826</v>
       </c>
       <c r="P57">
-        <v>-509.5568924541363</v>
+        <v>-525.8233814078479</v>
       </c>
       <c r="Q57">
-        <v>-417.5568924541363</v>
+        <v>-433.8233814078479</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1833475757901718</v>
+        <v>0.1864736570581303</v>
       </c>
       <c r="T57">
-        <v>1.330190183081635</v>
+        <v>1.360421778151672</v>
       </c>
       <c r="U57">
         <v>0.2453828270931482</v>
       </c>
       <c r="V57">
-        <v>0.1076110862298369</v>
+        <v>0.1056894596900184</v>
       </c>
       <c r="W57">
-        <v>0.2189769145275063</v>
+        <v>0.2194484486804642</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4304443449193477</v>
+        <v>0.4227578387600737</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2049395403666373</v>
+        <v>0.2069353686375687</v>
       </c>
       <c r="C58">
-        <v>370.6118285007715</v>
+        <v>245.6713631291441</v>
       </c>
       <c r="D58">
-        <v>2951.183828500772</v>
+        <v>2914.630363129145</v>
       </c>
       <c r="E58">
-        <v>1828.372</v>
+        <v>1916.759000000001</v>
       </c>
       <c r="F58">
-        <v>4949.672</v>
+        <v>5038.059000000001</v>
       </c>
       <c r="G58">
         <v>2369.1</v>
@@ -6049,37 +6049,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M58">
-        <v>1214.564508543797</v>
+        <v>1236.253160482079</v>
       </c>
       <c r="N58">
-        <v>-701.0978418771306</v>
+        <v>-722.7864938154128</v>
       </c>
       <c r="O58">
-        <v>-175.2744604692826</v>
+        <v>-180.6966234538532</v>
       </c>
       <c r="P58">
-        <v>-525.8233814078479</v>
+        <v>-542.0898703615596</v>
       </c>
       <c r="Q58">
-        <v>-433.8233814078479</v>
+        <v>-450.0898703615596</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1864736570581303</v>
+        <v>0.189745137454831</v>
       </c>
       <c r="T58">
-        <v>1.360421778151672</v>
+        <v>1.392059493922641</v>
       </c>
       <c r="U58">
         <v>0.2453828270931482</v>
       </c>
       <c r="V58">
-        <v>0.1056894596900184</v>
+        <v>0.1038352586428251</v>
       </c>
       <c r="W58">
-        <v>0.2194484486804642</v>
+        <v>0.2199034377754235</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4227578387600737</v>
+        <v>0.4153410345713003</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2069353686375687</v>
+        <v>0.2089311969085002</v>
       </c>
       <c r="C59">
-        <v>245.6713631291441</v>
+        <v>121.6253243414176</v>
       </c>
       <c r="D59">
-        <v>2914.630363129145</v>
+        <v>2878.971324341418</v>
       </c>
       <c r="E59">
-        <v>1916.759000000001</v>
+        <v>2005.146000000001</v>
       </c>
       <c r="F59">
-        <v>5038.059000000001</v>
+        <v>5126.446000000001</v>
       </c>
       <c r="G59">
         <v>2369.1</v>
@@ -6131,37 +6131,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M59">
-        <v>1236.253160482079</v>
+        <v>1257.941812420361</v>
       </c>
       <c r="N59">
-        <v>-722.7864938154128</v>
+        <v>-744.4751457536947</v>
       </c>
       <c r="O59">
-        <v>-180.6966234538532</v>
+        <v>-186.1187864384237</v>
       </c>
       <c r="P59">
-        <v>-542.0898703615596</v>
+        <v>-558.356359315271</v>
       </c>
       <c r="Q59">
-        <v>-450.0898703615596</v>
+        <v>-466.356359315271</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.189745137454831</v>
+        <v>0.193172402632327</v>
       </c>
       <c r="T59">
-        <v>1.392059493922641</v>
+        <v>1.425203767587466</v>
       </c>
       <c r="U59">
         <v>0.2453828270931482</v>
       </c>
       <c r="V59">
-        <v>0.1038352586428251</v>
+        <v>0.1020449955627764</v>
       </c>
       <c r="W59">
-        <v>0.2199034377754235</v>
+        <v>0.2203427375912464</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4153410345713003</v>
+        <v>0.4081799822511055</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2089311969085002</v>
+        <v>0.2109270251794317</v>
       </c>
       <c r="C60">
-        <v>121.6253243414194</v>
+        <v>-1.558719655939967</v>
       </c>
       <c r="D60">
-        <v>2878.971324341419</v>
+        <v>2844.174280344061</v>
       </c>
       <c r="E60">
-        <v>2005.146</v>
+        <v>2093.533</v>
       </c>
       <c r="F60">
-        <v>5126.446</v>
+        <v>5214.833000000001</v>
       </c>
       <c r="G60">
         <v>2369.1</v>
@@ -6213,37 +6213,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M60">
-        <v>1257.941812420361</v>
+        <v>1279.630464358643</v>
       </c>
       <c r="N60">
-        <v>-744.4751457536945</v>
+        <v>-766.1637976919767</v>
       </c>
       <c r="O60">
-        <v>-186.1187864384236</v>
+        <v>-191.5409494229942</v>
       </c>
       <c r="P60">
-        <v>-558.3563593152709</v>
+        <v>-574.6228482689826</v>
       </c>
       <c r="Q60">
-        <v>-466.3563593152709</v>
+        <v>-482.6228482689826</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1931724026323269</v>
+        <v>0.1967668514770178</v>
       </c>
       <c r="T60">
-        <v>1.425203767587465</v>
+        <v>1.459964835089599</v>
       </c>
       <c r="U60">
         <v>0.2453828270931482</v>
       </c>
       <c r="V60">
-        <v>0.1020449955627764</v>
+        <v>0.1003154193667971</v>
       </c>
       <c r="W60">
-        <v>0.2203427375912464</v>
+        <v>0.2207671458878888</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4081799822511056</v>
+        <v>0.4012616774671885</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2109270251794317</v>
+        <v>0.2129228534503632</v>
       </c>
       <c r="C61">
-        <v>-1.558719655939967</v>
+        <v>-123.9116514179468</v>
       </c>
       <c r="D61">
-        <v>2844.174280344061</v>
+        <v>2810.208348582054</v>
       </c>
       <c r="E61">
-        <v>2093.533</v>
+        <v>2181.92</v>
       </c>
       <c r="F61">
-        <v>5214.833000000001</v>
+        <v>5303.22</v>
       </c>
       <c r="G61">
         <v>2369.1</v>
@@ -6295,37 +6295,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M61">
-        <v>1279.630464358643</v>
+        <v>1301.319116296926</v>
       </c>
       <c r="N61">
-        <v>-766.1637976919767</v>
+        <v>-787.8524496302589</v>
       </c>
       <c r="O61">
-        <v>-191.5409494229942</v>
+        <v>-196.9631124075647</v>
       </c>
       <c r="P61">
-        <v>-574.6228482689826</v>
+        <v>-590.8893372226942</v>
       </c>
       <c r="Q61">
-        <v>-482.6228482689826</v>
+        <v>-498.8893372226942</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1967668514770178</v>
+        <v>0.2005410227639432</v>
       </c>
       <c r="T61">
-        <v>1.459964835089599</v>
+        <v>1.496463955966838</v>
       </c>
       <c r="U61">
         <v>0.2453828270931482</v>
       </c>
       <c r="V61">
-        <v>0.1003154193667971</v>
+        <v>0.09864349571068384</v>
       </c>
       <c r="W61">
-        <v>0.2207671458878888</v>
+        <v>0.2211774072413098</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4012616774671885</v>
+        <v>0.3945739828427354</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2129228534503632</v>
+        <v>0.2149186817212946</v>
       </c>
       <c r="C62">
-        <v>-123.9116514179468</v>
+        <v>-245.4628956766073</v>
       </c>
       <c r="D62">
-        <v>2810.208348582054</v>
+        <v>2777.044104323393</v>
       </c>
       <c r="E62">
-        <v>2181.92</v>
+        <v>2270.307</v>
       </c>
       <c r="F62">
-        <v>5303.22</v>
+        <v>5391.607</v>
       </c>
       <c r="G62">
         <v>2369.1</v>
@@ -6377,37 +6377,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M62">
-        <v>1301.319116296926</v>
+        <v>1323.007768235208</v>
       </c>
       <c r="N62">
-        <v>-787.8524496302589</v>
+        <v>-809.5411015685409</v>
       </c>
       <c r="O62">
-        <v>-196.9631124075647</v>
+        <v>-202.3852753921352</v>
       </c>
       <c r="P62">
-        <v>-590.8893372226942</v>
+        <v>-607.1558261764056</v>
       </c>
       <c r="Q62">
-        <v>-498.8893372226942</v>
+        <v>-515.1558261764056</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2005410227639432</v>
+        <v>0.204508741296352</v>
       </c>
       <c r="T62">
-        <v>1.496463955966838</v>
+        <v>1.534834826632655</v>
       </c>
       <c r="U62">
         <v>0.2453828270931482</v>
       </c>
       <c r="V62">
-        <v>0.09864349571068384</v>
+        <v>0.09702638922362347</v>
       </c>
       <c r="W62">
-        <v>0.2211774072413098</v>
+        <v>0.2215742174028153</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3945739828427354</v>
+        <v>0.3881055568944939</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2149186817212946</v>
+        <v>0.2169145099922261</v>
       </c>
       <c r="C63">
-        <v>-245.4628956766073</v>
+        <v>-366.2405043589688</v>
       </c>
       <c r="D63">
-        <v>2777.044104323393</v>
+        <v>2744.653495641032</v>
       </c>
       <c r="E63">
-        <v>2270.307</v>
+        <v>2358.694</v>
       </c>
       <c r="F63">
-        <v>5391.607</v>
+        <v>5479.994000000001</v>
       </c>
       <c r="G63">
         <v>2369.1</v>
@@ -6459,37 +6459,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M63">
-        <v>1323.007768235208</v>
+        <v>1344.69642017349</v>
       </c>
       <c r="N63">
-        <v>-809.5411015685409</v>
+        <v>-831.229753506823</v>
       </c>
       <c r="O63">
-        <v>-202.3852753921352</v>
+        <v>-207.8074383767058</v>
       </c>
       <c r="P63">
-        <v>-607.1558261764056</v>
+        <v>-623.4223151301173</v>
       </c>
       <c r="Q63">
-        <v>-515.1558261764056</v>
+        <v>-531.4223151301173</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.204508741296352</v>
+        <v>0.2086852871199403</v>
       </c>
       <c r="T63">
-        <v>1.534834826632655</v>
+        <v>1.575225216807199</v>
       </c>
       <c r="U63">
         <v>0.2453828270931482</v>
       </c>
       <c r="V63">
-        <v>0.09702638922362347</v>
+        <v>0.09546144746195211</v>
       </c>
       <c r="W63">
-        <v>0.2215742174028153</v>
+        <v>0.2219582272365304</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3881055568944939</v>
+        <v>0.3818457898478085</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2169145099922261</v>
+        <v>0.2189103382631576</v>
       </c>
       <c r="C64">
-        <v>-366.2405043589688</v>
+        <v>-486.2712357240134</v>
       </c>
       <c r="D64">
-        <v>2744.653495641032</v>
+        <v>2713.009764275987</v>
       </c>
       <c r="E64">
-        <v>2358.694</v>
+        <v>2447.081</v>
       </c>
       <c r="F64">
-        <v>5479.994000000001</v>
+        <v>5568.381</v>
       </c>
       <c r="G64">
         <v>2369.1</v>
@@ -6541,37 +6541,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M64">
-        <v>1344.69642017349</v>
+        <v>1366.385072111772</v>
       </c>
       <c r="N64">
-        <v>-831.229753506823</v>
+        <v>-852.918405445105</v>
       </c>
       <c r="O64">
-        <v>-207.8074383767058</v>
+        <v>-213.2296013612763</v>
       </c>
       <c r="P64">
-        <v>-623.4223151301173</v>
+        <v>-639.6888040838287</v>
       </c>
       <c r="Q64">
-        <v>-531.4223151301173</v>
+        <v>-547.6888040838287</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2086852871199403</v>
+        <v>0.2130875921772359</v>
       </c>
       <c r="T64">
-        <v>1.575225216807199</v>
+        <v>1.617798871315501</v>
       </c>
       <c r="U64">
         <v>0.2453828270931482</v>
       </c>
       <c r="V64">
-        <v>0.09546144746195211</v>
+        <v>0.09394618639112748</v>
       </c>
       <c r="W64">
-        <v>0.2219582272365304</v>
+        <v>0.2223300462818735</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3818457898478085</v>
+        <v>0.3757847455645099</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2189103382631576</v>
+        <v>0.2209061665340891</v>
       </c>
       <c r="C65">
-        <v>-486.2712357240134</v>
+        <v>-605.5806280876259</v>
       </c>
       <c r="D65">
-        <v>2713.009764275987</v>
+        <v>2682.087371912375</v>
       </c>
       <c r="E65">
-        <v>2447.081</v>
+        <v>2535.468000000001</v>
       </c>
       <c r="F65">
-        <v>5568.381</v>
+        <v>5656.768000000001</v>
       </c>
       <c r="G65">
         <v>2369.1</v>
@@ -6623,37 +6623,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M65">
-        <v>1366.385072111772</v>
+        <v>1388.073724050054</v>
       </c>
       <c r="N65">
-        <v>-852.918405445105</v>
+        <v>-874.6070573833874</v>
       </c>
       <c r="O65">
-        <v>-213.2296013612763</v>
+        <v>-218.6517643458469</v>
       </c>
       <c r="P65">
-        <v>-639.6888040838287</v>
+        <v>-655.9552930375405</v>
       </c>
       <c r="Q65">
-        <v>-547.6888040838287</v>
+        <v>-563.9552930375405</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2130875921772359</v>
+        <v>0.2177344697377147</v>
       </c>
       <c r="T65">
-        <v>1.617798871315501</v>
+        <v>1.662737728852043</v>
       </c>
       <c r="U65">
         <v>0.2453828270931482</v>
       </c>
       <c r="V65">
-        <v>0.09394618639112748</v>
+        <v>0.0924782772287661</v>
       </c>
       <c r="W65">
-        <v>0.2223300462818735</v>
+        <v>0.2226902459820497</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3757847455645099</v>
+        <v>0.3699131089150643</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2209061665340891</v>
+        <v>0.2229019948050205</v>
       </c>
       <c r="C66">
-        <v>-605.5806280876259</v>
+        <v>-724.1930685625584</v>
       </c>
       <c r="D66">
-        <v>2682.087371912375</v>
+        <v>2651.861931437442</v>
       </c>
       <c r="E66">
-        <v>2535.468000000001</v>
+        <v>2623.855</v>
       </c>
       <c r="F66">
-        <v>5656.768000000001</v>
+        <v>5745.155000000001</v>
       </c>
       <c r="G66">
         <v>2369.1</v>
@@ -6705,37 +6705,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M66">
-        <v>1388.073724050054</v>
+        <v>1409.762375988336</v>
       </c>
       <c r="N66">
-        <v>-874.6070573833874</v>
+        <v>-896.2957093216694</v>
       </c>
       <c r="O66">
-        <v>-218.6517643458469</v>
+        <v>-224.0739273304173</v>
       </c>
       <c r="P66">
-        <v>-655.9552930375405</v>
+        <v>-672.2217819912521</v>
       </c>
       <c r="Q66">
-        <v>-563.9552930375405</v>
+        <v>-580.2217819912521</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2177344697377147</v>
+        <v>0.2226468831587923</v>
       </c>
       <c r="T66">
-        <v>1.662737728852043</v>
+        <v>1.710244521104959</v>
       </c>
       <c r="U66">
         <v>0.2453828270931482</v>
       </c>
       <c r="V66">
-        <v>0.0924782772287661</v>
+        <v>0.0910555345021697</v>
       </c>
       <c r="W66">
-        <v>0.2226902459820497</v>
+        <v>0.2230393626145281</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3699131089150643</v>
+        <v>0.3642221380086789</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2229019948050205</v>
+        <v>0.224897823075952</v>
       </c>
       <c r="C67">
-        <v>-724.1930685625584</v>
+        <v>-842.1318572022519</v>
       </c>
       <c r="D67">
-        <v>2651.861931437442</v>
+        <v>2622.310142797749</v>
       </c>
       <c r="E67">
-        <v>2623.855</v>
+        <v>2712.242</v>
       </c>
       <c r="F67">
-        <v>5745.155000000001</v>
+        <v>5833.542</v>
       </c>
       <c r="G67">
         <v>2369.1</v>
@@ -6787,37 +6787,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M67">
-        <v>1409.762375988336</v>
+        <v>1431.451027926618</v>
       </c>
       <c r="N67">
-        <v>-896.2957093216694</v>
+        <v>-917.9843612599514</v>
       </c>
       <c r="O67">
-        <v>-224.0739273304173</v>
+        <v>-229.4960903149878</v>
       </c>
       <c r="P67">
-        <v>-672.2217819912521</v>
+        <v>-688.4882709449635</v>
       </c>
       <c r="Q67">
-        <v>-580.2217819912521</v>
+        <v>-596.4882709449635</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2226468831587923</v>
+        <v>0.2278482620752273</v>
       </c>
       <c r="T67">
-        <v>1.710244521104959</v>
+        <v>1.760545830549222</v>
       </c>
       <c r="U67">
         <v>0.2453828270931482</v>
       </c>
       <c r="V67">
-        <v>0.0910555345021697</v>
+        <v>0.08967590519153078</v>
       </c>
       <c r="W67">
-        <v>0.2230393626145281</v>
+        <v>0.2233778999551133</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3642221380086789</v>
+        <v>0.3587036207661231</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.224897823075952</v>
+        <v>0.2268936513468836</v>
       </c>
       <c r="C68">
-        <v>-842.1318572022519</v>
+        <v>-959.4192669030936</v>
       </c>
       <c r="D68">
-        <v>2622.310142797749</v>
+        <v>2593.409733096907</v>
       </c>
       <c r="E68">
-        <v>2712.242</v>
+        <v>2800.629000000001</v>
       </c>
       <c r="F68">
-        <v>5833.542</v>
+        <v>5921.929000000001</v>
       </c>
       <c r="G68">
         <v>2369.1</v>
@@ -6869,37 +6869,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M68">
-        <v>1431.451027926618</v>
+        <v>1453.1396798649</v>
       </c>
       <c r="N68">
-        <v>-917.9843612599514</v>
+        <v>-939.6730131982335</v>
       </c>
       <c r="O68">
-        <v>-229.4960903149878</v>
+        <v>-234.9182532995584</v>
       </c>
       <c r="P68">
-        <v>-688.4882709449635</v>
+        <v>-704.7547598986752</v>
       </c>
       <c r="Q68">
-        <v>-596.4882709449635</v>
+        <v>-612.7547598986752</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2278482620752273</v>
+        <v>0.233364876077507</v>
       </c>
       <c r="T68">
-        <v>1.760545830549222</v>
+        <v>1.813895704202229</v>
       </c>
       <c r="U68">
         <v>0.2453828270931482</v>
       </c>
       <c r="V68">
-        <v>0.08967590519153078</v>
+        <v>0.08833745884538852</v>
       </c>
       <c r="W68">
-        <v>0.2233778999551133</v>
+        <v>0.2237063317034421</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3587036207661231</v>
+        <v>0.3533498353815541</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2268936513468836</v>
+        <v>0.228889479617815</v>
       </c>
       <c r="C69">
-        <v>-959.4192669030936</v>
+        <v>-1076.076599388762</v>
       </c>
       <c r="D69">
-        <v>2593.409733096907</v>
+        <v>2565.139400611239</v>
       </c>
       <c r="E69">
-        <v>2800.629000000001</v>
+        <v>2889.016000000001</v>
       </c>
       <c r="F69">
-        <v>5921.929000000001</v>
+        <v>6010.316000000001</v>
       </c>
       <c r="G69">
         <v>2369.1</v>
@@ -6951,37 +6951,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M69">
-        <v>1453.1396798649</v>
+        <v>1474.828331803182</v>
       </c>
       <c r="N69">
-        <v>-939.6730131982335</v>
+        <v>-961.3616651365157</v>
       </c>
       <c r="O69">
-        <v>-234.9182532995584</v>
+        <v>-240.3404162841289</v>
       </c>
       <c r="P69">
-        <v>-704.7547598986752</v>
+        <v>-721.0212488523869</v>
       </c>
       <c r="Q69">
-        <v>-612.7547598986752</v>
+        <v>-629.0212488523869</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.233364876077507</v>
+        <v>0.2392262784549291</v>
       </c>
       <c r="T69">
-        <v>1.813895704202229</v>
+        <v>1.870579944958549</v>
       </c>
       <c r="U69">
         <v>0.2453828270931482</v>
       </c>
       <c r="V69">
-        <v>0.08833745884538852</v>
+        <v>0.08703837856825045</v>
       </c>
       <c r="W69">
-        <v>0.2237063317034421</v>
+        <v>0.2240251036944672</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3533498353815541</v>
+        <v>0.3481535142730018</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.228889479617815</v>
+        <v>0.2308853078887465</v>
       </c>
       <c r="C70">
-        <v>-1076.076599388762</v>
+        <v>-1192.124237572413</v>
       </c>
       <c r="D70">
-        <v>2565.139400611239</v>
+        <v>2537.478762427588</v>
       </c>
       <c r="E70">
-        <v>2889.016000000001</v>
+        <v>2977.403000000001</v>
       </c>
       <c r="F70">
-        <v>6010.316000000001</v>
+        <v>6098.703000000001</v>
       </c>
       <c r="G70">
         <v>2369.1</v>
@@ -7033,37 +7033,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M70">
-        <v>1474.828331803182</v>
+        <v>1496.516983741465</v>
       </c>
       <c r="N70">
-        <v>-961.3616651365157</v>
+        <v>-983.0503170747979</v>
       </c>
       <c r="O70">
-        <v>-240.3404162841289</v>
+        <v>-245.7625792686995</v>
       </c>
       <c r="P70">
-        <v>-721.0212488523869</v>
+        <v>-737.2877378060984</v>
       </c>
       <c r="Q70">
-        <v>-629.0212488523869</v>
+        <v>-645.2877378060984</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2392262784549291</v>
+        <v>0.2454658358244429</v>
       </c>
       <c r="T70">
-        <v>1.870579944958549</v>
+        <v>1.930921233505599</v>
       </c>
       <c r="U70">
         <v>0.2453828270931482</v>
       </c>
       <c r="V70">
-        <v>0.08703837856825045</v>
+        <v>0.08577695279189898</v>
       </c>
       <c r="W70">
-        <v>0.2240251036944672</v>
+        <v>0.2243346359176365</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3481535142730018</v>
+        <v>0.3431078111675959</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2308853078887465</v>
+        <v>0.232881136159678</v>
       </c>
       <c r="C71">
-        <v>-1192.124237572413</v>
+        <v>-1307.581694567171</v>
       </c>
       <c r="D71">
-        <v>2537.478762427588</v>
+        <v>2510.408305432829</v>
       </c>
       <c r="E71">
-        <v>2977.403000000001</v>
+        <v>3065.790000000001</v>
       </c>
       <c r="F71">
-        <v>6098.703000000001</v>
+        <v>6187.090000000001</v>
       </c>
       <c r="G71">
         <v>2369.1</v>
@@ -7115,37 +7115,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M71">
-        <v>1496.516983741465</v>
+        <v>1518.205635679747</v>
       </c>
       <c r="N71">
-        <v>-983.0503170747979</v>
+        <v>-1004.73896901308</v>
       </c>
       <c r="O71">
-        <v>-245.7625792686995</v>
+        <v>-251.18474225327</v>
       </c>
       <c r="P71">
-        <v>-737.2877378060984</v>
+        <v>-753.5542267598099</v>
       </c>
       <c r="Q71">
-        <v>-645.2877378060984</v>
+        <v>-661.5542267598099</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2454658358244429</v>
+        <v>0.2521213636852577</v>
       </c>
       <c r="T71">
-        <v>1.930921233505599</v>
+        <v>1.995285274622452</v>
       </c>
       <c r="U71">
         <v>0.2453828270931482</v>
       </c>
       <c r="V71">
-        <v>0.08577695279189898</v>
+        <v>0.08455156775201472</v>
       </c>
       <c r="W71">
-        <v>0.2243346359176365</v>
+        <v>0.224635324363001</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3431078111675959</v>
+        <v>0.3382062710080589</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.232881136159678</v>
+        <v>0.2348769644306095</v>
       </c>
       <c r="C72">
-        <v>-1307.581694567171</v>
+        <v>-1422.467659592617</v>
       </c>
       <c r="D72">
-        <v>2510.408305432829</v>
+        <v>2483.909340407384</v>
       </c>
       <c r="E72">
-        <v>3065.790000000001</v>
+        <v>3154.177000000001</v>
       </c>
       <c r="F72">
-        <v>6187.090000000001</v>
+        <v>6275.477000000001</v>
       </c>
       <c r="G72">
         <v>2369.1</v>
@@ -7197,37 +7197,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M72">
-        <v>1518.205635679747</v>
+        <v>1539.894287618029</v>
       </c>
       <c r="N72">
-        <v>-1004.73896901308</v>
+        <v>-1026.427620951362</v>
       </c>
       <c r="O72">
-        <v>-251.18474225327</v>
+        <v>-256.6069052378405</v>
       </c>
       <c r="P72">
-        <v>-753.5542267598099</v>
+        <v>-769.8207157135214</v>
       </c>
       <c r="Q72">
-        <v>-661.5542267598099</v>
+        <v>-677.8207157135214</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2521213636852577</v>
+        <v>0.259235893467508</v>
       </c>
       <c r="T72">
-        <v>1.995285274622452</v>
+        <v>2.064088215126675</v>
       </c>
       <c r="U72">
         <v>0.2453828270931482</v>
       </c>
       <c r="V72">
-        <v>0.08455156775201472</v>
+        <v>0.0833607006005779</v>
       </c>
       <c r="W72">
-        <v>0.224635324363001</v>
+        <v>0.2249275427113129</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3382062710080589</v>
+        <v>0.3334428024023116</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2348769644306095</v>
+        <v>0.2368727927015409</v>
       </c>
       <c r="C73">
-        <v>-1422.467659592616</v>
+        <v>-1536.800041004189</v>
       </c>
       <c r="D73">
-        <v>2483.909340407384</v>
+        <v>2457.963958995812</v>
       </c>
       <c r="E73">
-        <v>3154.177</v>
+        <v>3242.564</v>
       </c>
       <c r="F73">
-        <v>6275.477</v>
+        <v>6363.864</v>
       </c>
       <c r="G73">
         <v>2369.1</v>
@@ -7279,37 +7279,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M73">
-        <v>1539.894287618028</v>
+        <v>1561.582939556311</v>
       </c>
       <c r="N73">
-        <v>-1026.427620951362</v>
+        <v>-1048.116272889644</v>
       </c>
       <c r="O73">
-        <v>-256.6069052378404</v>
+        <v>-262.029068222411</v>
       </c>
       <c r="P73">
-        <v>-769.8207157135212</v>
+        <v>-786.087204667233</v>
       </c>
       <c r="Q73">
-        <v>-677.8207157135212</v>
+        <v>-694.087204667233</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2592358934675079</v>
+        <v>0.2668586039484903</v>
       </c>
       <c r="T73">
-        <v>2.064088215126674</v>
+        <v>2.137805651381198</v>
       </c>
       <c r="U73">
         <v>0.2453828270931482</v>
       </c>
       <c r="V73">
-        <v>0.08336070060057792</v>
+        <v>0.08220291309223654</v>
       </c>
       <c r="W73">
-        <v>0.2249275427113129</v>
+        <v>0.2252116438832828</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3334428024023116</v>
+        <v>0.3288116523689462</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2368727927015409</v>
+        <v>0.2388686209724724</v>
       </c>
       <c r="C74">
-        <v>-1536.800041004189</v>
+        <v>-1650.596006653734</v>
       </c>
       <c r="D74">
-        <v>2457.963958995812</v>
+        <v>2432.554993346267</v>
       </c>
       <c r="E74">
-        <v>3242.564</v>
+        <v>3330.951</v>
       </c>
       <c r="F74">
-        <v>6363.864</v>
+        <v>6452.251</v>
       </c>
       <c r="G74">
         <v>2369.1</v>
@@ -7361,37 +7361,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M74">
-        <v>1561.582939556311</v>
+        <v>1583.271591494593</v>
       </c>
       <c r="N74">
-        <v>-1048.116272889644</v>
+        <v>-1069.804924827926</v>
       </c>
       <c r="O74">
-        <v>-262.029068222411</v>
+        <v>-267.4512312069815</v>
       </c>
       <c r="P74">
-        <v>-786.087204667233</v>
+        <v>-802.3536936209446</v>
       </c>
       <c r="Q74">
-        <v>-694.087204667233</v>
+        <v>-710.3536936209446</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2668586039484903</v>
+        <v>0.2750459596502863</v>
       </c>
       <c r="T74">
-        <v>2.137805651381198</v>
+        <v>2.216983638469391</v>
       </c>
       <c r="U74">
         <v>0.2453828270931482</v>
       </c>
       <c r="V74">
-        <v>0.08220291309223654</v>
+        <v>0.08107684578960317</v>
       </c>
       <c r="W74">
-        <v>0.2252116438832828</v>
+        <v>0.2254879614615002</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3288116523689462</v>
+        <v>0.3243073831584127</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2388686209724724</v>
+        <v>0.2408644492434039</v>
       </c>
       <c r="C75">
-        <v>-1650.596006653734</v>
+        <v>-1763.872021772311</v>
       </c>
       <c r="D75">
-        <v>2432.554993346267</v>
+        <v>2407.66597822769</v>
       </c>
       <c r="E75">
-        <v>3330.951</v>
+        <v>3419.338000000001</v>
       </c>
       <c r="F75">
-        <v>6452.251</v>
+        <v>6540.638000000001</v>
       </c>
       <c r="G75">
         <v>2369.1</v>
@@ -7443,37 +7443,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M75">
-        <v>1583.271591494593</v>
+        <v>1604.960243432875</v>
       </c>
       <c r="N75">
-        <v>-1069.804924827926</v>
+        <v>-1091.493576766208</v>
       </c>
       <c r="O75">
-        <v>-267.4512312069815</v>
+        <v>-272.8733941915521</v>
       </c>
       <c r="P75">
-        <v>-802.3536936209446</v>
+        <v>-818.6201825746562</v>
       </c>
       <c r="Q75">
-        <v>-710.3536936209446</v>
+        <v>-726.6201825746562</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2750459596502863</v>
+        <v>0.2838631119445281</v>
       </c>
       <c r="T75">
-        <v>2.216983638469391</v>
+        <v>2.302252239948983</v>
       </c>
       <c r="U75">
         <v>0.2453828270931482</v>
       </c>
       <c r="V75">
-        <v>0.08107684578960317</v>
+        <v>0.0799812127383923</v>
       </c>
       <c r="W75">
-        <v>0.2254879614615002</v>
+        <v>0.225756810997063</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3243073831584127</v>
+        <v>0.3199248509535693</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2408644492434039</v>
+        <v>0.2428602775143354</v>
       </c>
       <c r="C76">
-        <v>-1763.872021772311</v>
+        <v>-1876.643884550945</v>
       </c>
       <c r="D76">
-        <v>2407.66597822769</v>
+        <v>2383.281115449056</v>
       </c>
       <c r="E76">
-        <v>3419.338000000001</v>
+        <v>3507.725</v>
       </c>
       <c r="F76">
-        <v>6540.638000000001</v>
+        <v>6629.025000000001</v>
       </c>
       <c r="G76">
         <v>2369.1</v>
@@ -7525,37 +7525,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M76">
-        <v>1604.960243432875</v>
+        <v>1626.648895371157</v>
       </c>
       <c r="N76">
-        <v>-1091.493576766208</v>
+        <v>-1113.18222870449</v>
       </c>
       <c r="O76">
-        <v>-272.8733941915521</v>
+        <v>-278.2955571761225</v>
       </c>
       <c r="P76">
-        <v>-818.6201825746562</v>
+        <v>-834.8866715283676</v>
       </c>
       <c r="Q76">
-        <v>-726.6201825746562</v>
+        <v>-742.8866715283676</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2838631119445281</v>
+        <v>0.2933856364223092</v>
       </c>
       <c r="T76">
-        <v>2.302252239948983</v>
+        <v>2.394342329546942</v>
       </c>
       <c r="U76">
         <v>0.2453828270931482</v>
       </c>
       <c r="V76">
-        <v>0.0799812127383923</v>
+        <v>0.07891479656854708</v>
       </c>
       <c r="W76">
-        <v>0.225756810997063</v>
+        <v>0.2260184912116775</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3199248509535693</v>
+        <v>0.3156591862741883</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2428602775143354</v>
+        <v>0.2448561057852669</v>
       </c>
       <c r="C77">
-        <v>-1876.643884550945</v>
+        <v>-1988.92675958088</v>
       </c>
       <c r="D77">
-        <v>2383.281115449056</v>
+        <v>2359.38524041912</v>
       </c>
       <c r="E77">
-        <v>3507.725</v>
+        <v>3596.112</v>
       </c>
       <c r="F77">
-        <v>6629.025000000001</v>
+        <v>6717.412</v>
       </c>
       <c r="G77">
         <v>2369.1</v>
@@ -7607,37 +7607,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M77">
-        <v>1626.648895371157</v>
+        <v>1648.337547309439</v>
       </c>
       <c r="N77">
-        <v>-1113.18222870449</v>
+        <v>-1134.870880642772</v>
       </c>
       <c r="O77">
-        <v>-278.2955571761225</v>
+        <v>-283.7177201606931</v>
       </c>
       <c r="P77">
-        <v>-834.8866715283676</v>
+        <v>-851.1531604820793</v>
       </c>
       <c r="Q77">
-        <v>-742.8866715283676</v>
+        <v>-759.1531604820793</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2933856364223092</v>
+        <v>0.3037017046065721</v>
       </c>
       <c r="T77">
-        <v>2.394342329546942</v>
+        <v>2.494106593278065</v>
       </c>
       <c r="U77">
         <v>0.2453828270931482</v>
       </c>
       <c r="V77">
-        <v>0.07891479656854708</v>
+        <v>0.07787644398211883</v>
       </c>
       <c r="W77">
-        <v>0.2260184912116775</v>
+        <v>0.2262732851048547</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3156591862741883</v>
+        <v>0.3115057759284753</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2448561057852669</v>
+        <v>0.2468519340561984</v>
       </c>
       <c r="C78">
-        <v>-1988.92675958088</v>
+        <v>-2100.735209302079</v>
       </c>
       <c r="D78">
-        <v>2359.38524041912</v>
+        <v>2335.963790697922</v>
       </c>
       <c r="E78">
-        <v>3596.112</v>
+        <v>3684.499000000001</v>
       </c>
       <c r="F78">
-        <v>6717.412</v>
+        <v>6805.799000000001</v>
       </c>
       <c r="G78">
         <v>2369.1</v>
@@ -7689,37 +7689,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M78">
-        <v>1648.337547309439</v>
+        <v>1670.026199247721</v>
       </c>
       <c r="N78">
-        <v>-1134.870880642772</v>
+        <v>-1156.559532581055</v>
       </c>
       <c r="O78">
-        <v>-283.7177201606931</v>
+        <v>-289.1398831452636</v>
       </c>
       <c r="P78">
-        <v>-851.1531604820793</v>
+        <v>-867.4196494357909</v>
       </c>
       <c r="Q78">
-        <v>-759.1531604820793</v>
+        <v>-775.4196494357909</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3037017046065721</v>
+        <v>0.3149148221981622</v>
       </c>
       <c r="T78">
-        <v>2.494106593278065</v>
+        <v>2.602546010377111</v>
       </c>
       <c r="U78">
         <v>0.2453828270931482</v>
       </c>
       <c r="V78">
-        <v>0.07787644398211883</v>
+        <v>0.07686506159274066</v>
       </c>
       <c r="W78">
-        <v>0.2262732851048547</v>
+        <v>0.2265214609748326</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3115057759284753</v>
+        <v>0.3074602463709626</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2468519340561984</v>
+        <v>0.2488477623271299</v>
       </c>
       <c r="C79">
-        <v>-2100.735209302079</v>
+        <v>-2212.083223597011</v>
       </c>
       <c r="D79">
-        <v>2335.963790697922</v>
+        <v>2313.00277640299</v>
       </c>
       <c r="E79">
-        <v>3684.499000000001</v>
+        <v>3772.886</v>
       </c>
       <c r="F79">
-        <v>6805.799000000001</v>
+        <v>6894.186000000001</v>
       </c>
       <c r="G79">
         <v>2369.1</v>
@@ -7771,37 +7771,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M79">
-        <v>1670.026199247721</v>
+        <v>1691.714851186003</v>
       </c>
       <c r="N79">
-        <v>-1156.559532581055</v>
+        <v>-1178.248184519337</v>
       </c>
       <c r="O79">
-        <v>-289.1398831452636</v>
+        <v>-294.5620461298341</v>
       </c>
       <c r="P79">
-        <v>-867.4196494357909</v>
+        <v>-883.6861383895024</v>
       </c>
       <c r="Q79">
-        <v>-775.4196494357909</v>
+        <v>-791.6861383895024</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3149148221981622</v>
+        <v>0.3271473141162605</v>
       </c>
       <c r="T79">
-        <v>2.602546010377111</v>
+        <v>2.720843556303344</v>
       </c>
       <c r="U79">
         <v>0.2453828270931482</v>
       </c>
       <c r="V79">
-        <v>0.07686506159274066</v>
+        <v>0.07587961208514142</v>
       </c>
       <c r="W79">
-        <v>0.2265214609748326</v>
+        <v>0.2267632733609648</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3074602463709626</v>
+        <v>0.3035184483405657</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2488477623271299</v>
+        <v>0.2508435905980613</v>
       </c>
       <c r="C80">
-        <v>-2212.083223597011</v>
+        <v>-2322.984247656107</v>
       </c>
       <c r="D80">
-        <v>2313.00277640299</v>
+        <v>2290.488752343894</v>
       </c>
       <c r="E80">
-        <v>3772.886</v>
+        <v>3861.273000000001</v>
       </c>
       <c r="F80">
-        <v>6894.186000000001</v>
+        <v>6982.573000000001</v>
       </c>
       <c r="G80">
         <v>2369.1</v>
@@ -7853,37 +7853,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M80">
-        <v>1691.714851186003</v>
+        <v>1713.403503124285</v>
       </c>
       <c r="N80">
-        <v>-1178.248184519337</v>
+        <v>-1199.936836457619</v>
       </c>
       <c r="O80">
-        <v>-294.5620461298341</v>
+        <v>-299.9842091144047</v>
       </c>
       <c r="P80">
-        <v>-883.6861383895024</v>
+        <v>-899.9526273432141</v>
       </c>
       <c r="Q80">
-        <v>-791.6861383895024</v>
+        <v>-807.9526273432141</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3271473141162605</v>
+        <v>0.3405448052646539</v>
       </c>
       <c r="T80">
-        <v>2.720843556303344</v>
+        <v>2.850407535174932</v>
       </c>
       <c r="U80">
         <v>0.2453828270931482</v>
       </c>
       <c r="V80">
-        <v>0.07587961208514142</v>
+        <v>0.07491911066634216</v>
       </c>
       <c r="W80">
-        <v>0.2267632733609648</v>
+        <v>0.2269989639145367</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3035184483405657</v>
+        <v>0.2996764426653686</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2508435905980613</v>
+        <v>0.2528394188689928</v>
       </c>
       <c r="C81">
-        <v>-2322.984247656107</v>
+        <v>-2433.451208231494</v>
       </c>
       <c r="D81">
-        <v>2290.488752343894</v>
+        <v>2268.408791768507</v>
       </c>
       <c r="E81">
-        <v>3861.273000000001</v>
+        <v>3949.660000000001</v>
       </c>
       <c r="F81">
-        <v>6982.573000000001</v>
+        <v>7070.960000000001</v>
       </c>
       <c r="G81">
         <v>2369.1</v>
@@ -7935,37 +7935,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M81">
-        <v>1713.403503124285</v>
+        <v>1735.092155062568</v>
       </c>
       <c r="N81">
-        <v>-1199.936836457619</v>
+        <v>-1221.625488395901</v>
       </c>
       <c r="O81">
-        <v>-299.9842091144047</v>
+        <v>-305.4063720989752</v>
       </c>
       <c r="P81">
-        <v>-899.9526273432141</v>
+        <v>-916.2191162969257</v>
       </c>
       <c r="Q81">
-        <v>-807.9526273432141</v>
+        <v>-824.2191162969257</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3405448052646539</v>
+        <v>0.3552820455278866</v>
       </c>
       <c r="T81">
-        <v>2.850407535174932</v>
+        <v>2.992927911933678</v>
       </c>
       <c r="U81">
         <v>0.2453828270931482</v>
       </c>
       <c r="V81">
-        <v>0.07491911066634216</v>
+        <v>0.07398262178301288</v>
       </c>
       <c r="W81">
-        <v>0.2269989639145367</v>
+        <v>0.2272287622042694</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2996764426653686</v>
+        <v>0.2959304871320515</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2528394188689928</v>
+        <v>0.2548352471399243</v>
       </c>
       <c r="C82">
-        <v>-2433.451208231494</v>
+        <v>-2543.496538386747</v>
       </c>
       <c r="D82">
-        <v>2268.408791768507</v>
+        <v>2246.750461613255</v>
       </c>
       <c r="E82">
-        <v>3949.660000000001</v>
+        <v>4038.047</v>
       </c>
       <c r="F82">
-        <v>7070.960000000001</v>
+        <v>7159.347000000001</v>
       </c>
       <c r="G82">
         <v>2369.1</v>
@@ -8017,37 +8017,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M82">
-        <v>1735.092155062568</v>
+        <v>1756.78080700085</v>
       </c>
       <c r="N82">
-        <v>-1221.625488395901</v>
+        <v>-1243.314140334183</v>
       </c>
       <c r="O82">
-        <v>-305.4063720989752</v>
+        <v>-310.8285350835457</v>
       </c>
       <c r="P82">
-        <v>-916.2191162969257</v>
+        <v>-932.4856052506371</v>
       </c>
       <c r="Q82">
-        <v>-824.2191162969257</v>
+        <v>-840.4856052506371</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3552820455278866</v>
+        <v>0.3715705742398807</v>
       </c>
       <c r="T82">
-        <v>2.992927911933678</v>
+        <v>3.150450433614399</v>
       </c>
       <c r="U82">
         <v>0.2453828270931482</v>
       </c>
       <c r="V82">
-        <v>0.07398262178301288</v>
+        <v>0.07306925608198804</v>
       </c>
       <c r="W82">
-        <v>0.2272287622042694</v>
+        <v>0.2274528864621568</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2959304871320515</v>
+        <v>0.2922770243279521</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2548352471399243</v>
+        <v>0.2568310754108558</v>
       </c>
       <c r="C83">
-        <v>-2543.496538386747</v>
+        <v>-2653.132200842197</v>
       </c>
       <c r="D83">
-        <v>2246.750461613255</v>
+        <v>2225.501799157804</v>
       </c>
       <c r="E83">
-        <v>4038.047</v>
+        <v>4126.434000000001</v>
       </c>
       <c r="F83">
-        <v>7159.347000000001</v>
+        <v>7247.734000000001</v>
       </c>
       <c r="G83">
         <v>2369.1</v>
@@ -8099,37 +8099,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M83">
-        <v>1756.78080700085</v>
+        <v>1778.469458939132</v>
       </c>
       <c r="N83">
-        <v>-1243.314140334183</v>
+        <v>-1265.002792272465</v>
       </c>
       <c r="O83">
-        <v>-310.8285350835457</v>
+        <v>-316.2506980681163</v>
       </c>
       <c r="P83">
-        <v>-932.4856052506371</v>
+        <v>-948.7520942043489</v>
       </c>
       <c r="Q83">
-        <v>-840.4856052506371</v>
+        <v>-856.7520942043489</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3715705742398807</v>
+        <v>0.3896689394754295</v>
       </c>
       <c r="T83">
-        <v>3.150450433614399</v>
+        <v>3.325475457704087</v>
       </c>
       <c r="U83">
         <v>0.2453828270931482</v>
       </c>
       <c r="V83">
-        <v>0.07306925608198804</v>
+        <v>0.0721781675931833</v>
       </c>
       <c r="W83">
-        <v>0.2274528864621568</v>
+        <v>0.2276715442747298</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2922770243279521</v>
+        <v>0.2887126703727332</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2568310754108558</v>
+        <v>0.2588269036817873</v>
       </c>
       <c r="C84">
-        <v>-2653.132200842197</v>
+        <v>-2762.369710007945</v>
       </c>
       <c r="D84">
-        <v>2225.501799157804</v>
+        <v>2204.651289992056</v>
       </c>
       <c r="E84">
-        <v>4126.434000000001</v>
+        <v>4214.821000000001</v>
       </c>
       <c r="F84">
-        <v>7247.734000000001</v>
+        <v>7336.121000000001</v>
       </c>
       <c r="G84">
         <v>2369.1</v>
@@ -8181,37 +8181,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M84">
-        <v>1778.469458939132</v>
+        <v>1800.158110877414</v>
       </c>
       <c r="N84">
-        <v>-1265.002792272465</v>
+        <v>-1286.691444210747</v>
       </c>
       <c r="O84">
-        <v>-316.2506980681163</v>
+        <v>-321.6728610526868</v>
       </c>
       <c r="P84">
-        <v>-948.7520942043489</v>
+        <v>-965.0185831580602</v>
       </c>
       <c r="Q84">
-        <v>-856.7520942043489</v>
+        <v>-873.0185831580602</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3896689394754295</v>
+        <v>0.4098965241504549</v>
       </c>
       <c r="T84">
-        <v>3.325475457704087</v>
+        <v>3.521091661098446</v>
       </c>
       <c r="U84">
         <v>0.2453828270931482</v>
       </c>
       <c r="V84">
-        <v>0.0721781675931833</v>
+        <v>0.071308551116157</v>
       </c>
       <c r="W84">
-        <v>0.2276715442747298</v>
+        <v>0.2278849332243493</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2887126703727332</v>
+        <v>0.285234204464628</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2588269036817873</v>
+        <v>0.2608227319527188</v>
       </c>
       <c r="C85">
-        <v>-2762.369710007945</v>
+        <v>-2871.220152789798</v>
       </c>
       <c r="D85">
-        <v>2204.651289992056</v>
+        <v>2184.187847210204</v>
       </c>
       <c r="E85">
-        <v>4214.821000000001</v>
+        <v>4303.208000000001</v>
       </c>
       <c r="F85">
-        <v>7336.121000000001</v>
+        <v>7424.508000000002</v>
       </c>
       <c r="G85">
         <v>2369.1</v>
@@ -8263,37 +8263,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M85">
-        <v>1800.158110877414</v>
+        <v>1821.846762815696</v>
       </c>
       <c r="N85">
-        <v>-1286.691444210747</v>
+        <v>-1308.380096149029</v>
       </c>
       <c r="O85">
-        <v>-321.6728610526868</v>
+        <v>-327.0950240372573</v>
       </c>
       <c r="P85">
-        <v>-965.0185831580602</v>
+        <v>-981.2850721117719</v>
       </c>
       <c r="Q85">
-        <v>-873.0185831580602</v>
+        <v>-889.2850721117719</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4098965241504549</v>
+        <v>0.4326525569098583</v>
       </c>
       <c r="T85">
-        <v>3.521091661098446</v>
+        <v>3.741159889917099</v>
       </c>
       <c r="U85">
         <v>0.2453828270931482</v>
       </c>
       <c r="V85">
-        <v>0.071308551116157</v>
+        <v>0.0704596397933456</v>
       </c>
       <c r="W85">
-        <v>0.2278849332243493</v>
+        <v>0.2280932414846922</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.285234204464628</v>
+        <v>0.2818385591733824</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2608227319527188</v>
+        <v>0.2628185602236502</v>
       </c>
       <c r="C86">
-        <v>-2871.220152789797</v>
+        <v>-2979.694208247147</v>
       </c>
       <c r="D86">
-        <v>2184.187847210204</v>
+        <v>2164.100791752854</v>
       </c>
       <c r="E86">
-        <v>4303.208000000001</v>
+        <v>4391.595</v>
       </c>
       <c r="F86">
-        <v>7424.508000000001</v>
+        <v>7512.895</v>
       </c>
       <c r="G86">
         <v>2369.1</v>
@@ -8345,37 +8345,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M86">
-        <v>1821.846762815696</v>
+        <v>1843.535414753978</v>
       </c>
       <c r="N86">
-        <v>-1308.380096149029</v>
+        <v>-1330.068748087311</v>
       </c>
       <c r="O86">
-        <v>-327.0950240372573</v>
+        <v>-332.5171870218278</v>
       </c>
       <c r="P86">
-        <v>-981.2850721117719</v>
+        <v>-997.5515610654834</v>
       </c>
       <c r="Q86">
-        <v>-889.2850721117719</v>
+        <v>-905.5515610654834</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4326525569098581</v>
+        <v>0.4584427273705153</v>
       </c>
       <c r="T86">
-        <v>3.741159889917097</v>
+        <v>3.990570549244903</v>
       </c>
       <c r="U86">
         <v>0.2453828270931482</v>
       </c>
       <c r="V86">
-        <v>0.0704596397933456</v>
+        <v>0.06963070285460037</v>
       </c>
       <c r="W86">
-        <v>0.2280932414846922</v>
+        <v>0.2282966483742034</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2818385591733824</v>
+        <v>0.2785228114184014</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2628185602236502</v>
+        <v>0.2648143884945817</v>
       </c>
       <c r="C87">
-        <v>-2979.694208247147</v>
+        <v>-3087.802166176048</v>
       </c>
       <c r="D87">
-        <v>2164.100791752854</v>
+        <v>2144.379833823953</v>
       </c>
       <c r="E87">
-        <v>4391.595</v>
+        <v>4479.982</v>
       </c>
       <c r="F87">
-        <v>7512.895</v>
+        <v>7601.282</v>
       </c>
       <c r="G87">
         <v>2369.1</v>
@@ -8427,37 +8427,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M87">
-        <v>1843.535414753978</v>
+        <v>1865.22406669226</v>
       </c>
       <c r="N87">
-        <v>-1330.068748087311</v>
+        <v>-1351.757400025593</v>
       </c>
       <c r="O87">
-        <v>-332.5171870218278</v>
+        <v>-337.9393500063983</v>
       </c>
       <c r="P87">
-        <v>-997.5515610654834</v>
+        <v>-1013.818050019195</v>
       </c>
       <c r="Q87">
-        <v>-905.5515610654834</v>
+        <v>-921.8180500191949</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4584427273705153</v>
+        <v>0.4879172078969807</v>
       </c>
       <c r="T87">
-        <v>3.990570549244903</v>
+        <v>4.275611302762396</v>
       </c>
       <c r="U87">
         <v>0.2453828270931482</v>
       </c>
       <c r="V87">
-        <v>0.06963070285460037</v>
+        <v>0.06882104351908176</v>
       </c>
       <c r="W87">
-        <v>0.2282966483742034</v>
+        <v>0.2284953248709353</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2785228114184014</v>
+        <v>0.275284174076327</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2648143884945817</v>
+        <v>0.2668102167655132</v>
       </c>
       <c r="C88">
-        <v>-3087.802166176048</v>
+        <v>-3195.553944685369</v>
       </c>
       <c r="D88">
-        <v>2144.379833823953</v>
+        <v>2125.015055314632</v>
       </c>
       <c r="E88">
-        <v>4479.982</v>
+        <v>4568.369000000001</v>
       </c>
       <c r="F88">
-        <v>7601.282</v>
+        <v>7689.669000000001</v>
       </c>
       <c r="G88">
         <v>2369.1</v>
@@ -8509,37 +8509,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M88">
-        <v>1865.22406669226</v>
+        <v>1886.912718630542</v>
       </c>
       <c r="N88">
-        <v>-1351.757400025593</v>
+        <v>-1373.446051963875</v>
       </c>
       <c r="O88">
-        <v>-337.9393500063983</v>
+        <v>-343.3615129909688</v>
       </c>
       <c r="P88">
-        <v>-1013.818050019195</v>
+        <v>-1030.084538972907</v>
       </c>
       <c r="Q88">
-        <v>-921.8180500191949</v>
+        <v>-938.0845389729066</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4879172078969807</v>
+        <v>0.5219262238890561</v>
       </c>
       <c r="T88">
-        <v>4.275611302762396</v>
+        <v>4.604504479897965</v>
       </c>
       <c r="U88">
         <v>0.2453828270931482</v>
       </c>
       <c r="V88">
-        <v>0.06882104351908176</v>
+        <v>0.06802999704185093</v>
       </c>
       <c r="W88">
-        <v>0.2284953248709353</v>
+        <v>0.2286894340918803</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.275284174076327</v>
+        <v>0.2721199881674037</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2668102167655132</v>
+        <v>0.2688060450364447</v>
       </c>
       <c r="C89">
-        <v>-3195.553944685369</v>
+        <v>-3302.959106829175</v>
       </c>
       <c r="D89">
-        <v>2125.015055314632</v>
+        <v>2105.996893170826</v>
       </c>
       <c r="E89">
-        <v>4568.369000000001</v>
+        <v>4656.756</v>
       </c>
       <c r="F89">
-        <v>7689.669000000001</v>
+        <v>7778.056</v>
       </c>
       <c r="G89">
         <v>2369.1</v>
@@ -8591,37 +8591,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M89">
-        <v>1886.912718630542</v>
+        <v>1908.601370568824</v>
       </c>
       <c r="N89">
-        <v>-1373.446051963875</v>
+        <v>-1395.134703902157</v>
       </c>
       <c r="O89">
-        <v>-343.3615129909688</v>
+        <v>-348.7836759755393</v>
       </c>
       <c r="P89">
-        <v>-1030.084538972907</v>
+        <v>-1046.351027926618</v>
       </c>
       <c r="Q89">
-        <v>-938.0845389729066</v>
+        <v>-954.3510279266179</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5219262238890561</v>
+        <v>0.5616034092131441</v>
       </c>
       <c r="T89">
-        <v>4.604504479897965</v>
+        <v>4.98821318655613</v>
       </c>
       <c r="U89">
         <v>0.2453828270931482</v>
       </c>
       <c r="V89">
-        <v>0.06802999704185093</v>
+        <v>0.06725692889364808</v>
       </c>
       <c r="W89">
-        <v>0.2286894340918803</v>
+        <v>0.228879131739622</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2721199881674037</v>
+        <v>0.2690277155745924</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2688060450364447</v>
+        <v>0.2708018733073762</v>
       </c>
       <c r="C90">
-        <v>-3302.959106829175</v>
+        <v>-3410.02687635389</v>
       </c>
       <c r="D90">
-        <v>2105.996893170826</v>
+        <v>2087.316123646111</v>
       </c>
       <c r="E90">
-        <v>4656.756</v>
+        <v>4745.143000000001</v>
       </c>
       <c r="F90">
-        <v>7778.056</v>
+        <v>7866.443000000001</v>
       </c>
       <c r="G90">
         <v>2369.1</v>
@@ -8673,37 +8673,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M90">
-        <v>1908.601370568824</v>
+        <v>1930.290022507106</v>
       </c>
       <c r="N90">
-        <v>-1395.134703902157</v>
+        <v>-1416.82335584044</v>
       </c>
       <c r="O90">
-        <v>-348.7836759755393</v>
+        <v>-354.2058389601099</v>
       </c>
       <c r="P90">
-        <v>-1046.351027926618</v>
+        <v>-1062.61751688033</v>
       </c>
       <c r="Q90">
-        <v>-954.3510279266179</v>
+        <v>-970.6175168803297</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5616034092131441</v>
+        <v>0.608494628232521</v>
       </c>
       <c r="T90">
-        <v>4.98821318655613</v>
+        <v>5.441687112606687</v>
       </c>
       <c r="U90">
         <v>0.2453828270931482</v>
       </c>
       <c r="V90">
-        <v>0.06725692889364808</v>
+        <v>0.06650123306338236</v>
       </c>
       <c r="W90">
-        <v>0.228879131739622</v>
+        <v>0.2290645665188751</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2690277155745924</v>
+        <v>0.2660049322535295</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2708018733073762</v>
+        <v>0.2727977015783076</v>
       </c>
       <c r="C91">
-        <v>-3410.02687635389</v>
+        <v>-3516.766152614744</v>
       </c>
       <c r="D91">
-        <v>2087.316123646111</v>
+        <v>2068.963847385257</v>
       </c>
       <c r="E91">
-        <v>4745.143000000001</v>
+        <v>4833.530000000001</v>
       </c>
       <c r="F91">
-        <v>7866.443000000001</v>
+        <v>7954.830000000001</v>
       </c>
       <c r="G91">
         <v>2369.1</v>
@@ -8755,37 +8755,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M91">
-        <v>1930.290022507106</v>
+        <v>1951.978674445388</v>
       </c>
       <c r="N91">
-        <v>-1416.82335584044</v>
+        <v>-1438.512007778722</v>
       </c>
       <c r="O91">
-        <v>-354.2058389601099</v>
+        <v>-359.6280019446804</v>
       </c>
       <c r="P91">
-        <v>-1062.61751688033</v>
+        <v>-1078.884005834041</v>
       </c>
       <c r="Q91">
-        <v>-970.6175168803297</v>
+        <v>-986.8840058340413</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.608494628232521</v>
+        <v>0.6647640910557731</v>
       </c>
       <c r="T91">
-        <v>5.441687112606687</v>
+        <v>5.985855823867356</v>
       </c>
       <c r="U91">
         <v>0.2453828270931482</v>
       </c>
       <c r="V91">
-        <v>0.06650123306338236</v>
+        <v>0.06576233047378924</v>
       </c>
       <c r="W91">
-        <v>0.2290645665188751</v>
+        <v>0.2292458805252559</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2660049322535295</v>
+        <v>0.263049321895157</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2727977015783076</v>
+        <v>0.2747935298492391</v>
       </c>
       <c r="C92">
-        <v>-3516.766152614744</v>
+        <v>-3623.185524712179</v>
       </c>
       <c r="D92">
-        <v>2068.963847385257</v>
+        <v>2050.931475287821</v>
       </c>
       <c r="E92">
-        <v>4833.530000000001</v>
+        <v>4921.917</v>
       </c>
       <c r="F92">
-        <v>7954.830000000001</v>
+        <v>8043.217000000001</v>
       </c>
       <c r="G92">
         <v>2369.1</v>
@@ -8837,37 +8837,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M92">
-        <v>1951.978674445388</v>
+        <v>1973.66732638367</v>
       </c>
       <c r="N92">
-        <v>-1438.512007778722</v>
+        <v>-1460.200659717004</v>
       </c>
       <c r="O92">
-        <v>-359.6280019446804</v>
+        <v>-365.0501649292509</v>
       </c>
       <c r="P92">
-        <v>-1078.884005834041</v>
+        <v>-1095.150494787753</v>
       </c>
       <c r="Q92">
-        <v>-986.8840058340413</v>
+        <v>-1003.150494787753</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6647640910557731</v>
+        <v>0.733537878950859</v>
       </c>
       <c r="T92">
-        <v>5.985855823867356</v>
+        <v>6.650950915408174</v>
       </c>
       <c r="U92">
         <v>0.2453828270931482</v>
       </c>
       <c r="V92">
-        <v>0.06576233047378924</v>
+        <v>0.0650396675015498</v>
       </c>
       <c r="W92">
-        <v>0.2292458805252559</v>
+        <v>0.2294232096084196</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.263049321895157</v>
+        <v>0.2601586700061992</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2747935298492391</v>
+        <v>0.2767893581201706</v>
       </c>
       <c r="C93">
-        <v>-3623.185524712179</v>
+        <v>-3729.293284895396</v>
       </c>
       <c r="D93">
-        <v>2050.931475287821</v>
+        <v>2033.210715104605</v>
       </c>
       <c r="E93">
-        <v>4921.917</v>
+        <v>5010.304000000001</v>
       </c>
       <c r="F93">
-        <v>8043.217000000001</v>
+        <v>8131.604000000001</v>
       </c>
       <c r="G93">
         <v>2369.1</v>
@@ -8919,37 +8919,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M93">
-        <v>1973.66732638367</v>
+        <v>1995.355978321953</v>
       </c>
       <c r="N93">
-        <v>-1460.200659717004</v>
+        <v>-1481.889311655286</v>
       </c>
       <c r="O93">
-        <v>-365.0501649292509</v>
+        <v>-370.4723279138215</v>
       </c>
       <c r="P93">
-        <v>-1095.150494787753</v>
+        <v>-1111.416983741464</v>
       </c>
       <c r="Q93">
-        <v>-1003.150494787753</v>
+        <v>-1019.416983741464</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.733537878950859</v>
+        <v>0.8195051138197166</v>
       </c>
       <c r="T93">
-        <v>6.650950915408174</v>
+        <v>7.482319779834198</v>
       </c>
       <c r="U93">
         <v>0.2453828270931482</v>
       </c>
       <c r="V93">
-        <v>0.0650396675015498</v>
+        <v>0.06433271459392426</v>
       </c>
       <c r="W93">
-        <v>0.2294232096084196</v>
+        <v>0.2295966837115144</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2601586700061992</v>
+        <v>0.257330858375697</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2767893581201706</v>
+        <v>0.2787851863911021</v>
       </c>
       <c r="C94">
-        <v>-3729.293284895396</v>
+        <v>-3835.097441276982</v>
       </c>
       <c r="D94">
-        <v>2033.210715104605</v>
+        <v>2015.79355872302</v>
       </c>
       <c r="E94">
-        <v>5010.304000000001</v>
+        <v>5098.691000000002</v>
       </c>
       <c r="F94">
-        <v>8131.604000000001</v>
+        <v>8219.991000000002</v>
       </c>
       <c r="G94">
         <v>2369.1</v>
@@ -9001,37 +9001,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M94">
-        <v>1995.355978321953</v>
+        <v>2017.044630260235</v>
       </c>
       <c r="N94">
-        <v>-1481.889311655286</v>
+        <v>-1503.577963593568</v>
       </c>
       <c r="O94">
-        <v>-370.4723279138215</v>
+        <v>-375.8944908983921</v>
       </c>
       <c r="P94">
-        <v>-1111.416983741464</v>
+        <v>-1127.683472695176</v>
       </c>
       <c r="Q94">
-        <v>-1019.416983741464</v>
+        <v>-1035.683472695176</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8195051138197166</v>
+        <v>0.9300344157939618</v>
       </c>
       <c r="T94">
-        <v>7.482319779834198</v>
+        <v>8.551222605524798</v>
       </c>
       <c r="U94">
         <v>0.2453828270931482</v>
       </c>
       <c r="V94">
-        <v>0.06433271459392426</v>
+        <v>0.06364096497463473</v>
       </c>
       <c r="W94">
-        <v>0.2295966837115144</v>
+        <v>0.2297664271887363</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.257330858375697</v>
+        <v>0.2545638598985389</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2787851863911021</v>
+        <v>0.2807810146620336</v>
       </c>
       <c r="C95">
-        <v>-3835.097441276982</v>
+        <v>-3940.605729899586</v>
       </c>
       <c r="D95">
-        <v>2015.79355872302</v>
+        <v>1998.672270100416</v>
       </c>
       <c r="E95">
-        <v>5098.691000000002</v>
+        <v>5187.078</v>
       </c>
       <c r="F95">
-        <v>8219.991000000002</v>
+        <v>8308.378000000001</v>
       </c>
       <c r="G95">
         <v>2369.1</v>
@@ -9083,37 +9083,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M95">
-        <v>2017.044630260235</v>
+        <v>2038.733282198517</v>
       </c>
       <c r="N95">
-        <v>-1503.577963593568</v>
+        <v>-1525.26661553185</v>
       </c>
       <c r="O95">
-        <v>-375.8944908983921</v>
+        <v>-381.3166538829625</v>
       </c>
       <c r="P95">
-        <v>-1127.683472695176</v>
+        <v>-1143.949961648887</v>
       </c>
       <c r="Q95">
-        <v>-1035.683472695176</v>
+        <v>-1051.949961648887</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9300344157939618</v>
+        <v>1.077406818426289</v>
       </c>
       <c r="T95">
-        <v>8.551222605524798</v>
+        <v>9.976426373112268</v>
       </c>
       <c r="U95">
         <v>0.2453828270931482</v>
       </c>
       <c r="V95">
-        <v>0.06364096497463473</v>
+        <v>0.06296393343235139</v>
       </c>
       <c r="W95">
-        <v>0.2297664271887363</v>
+        <v>0.229932559102613</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2545638598985389</v>
+        <v>0.2518557337294056</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2807810146620336</v>
+        <v>0.2827768429329651</v>
       </c>
       <c r="C96">
-        <v>-3940.605729899586</v>
+        <v>-4045.825626192839</v>
       </c>
       <c r="D96">
-        <v>1998.672270100416</v>
+        <v>1981.839373807162</v>
       </c>
       <c r="E96">
-        <v>5187.078</v>
+        <v>5275.465000000001</v>
       </c>
       <c r="F96">
-        <v>8308.378000000001</v>
+        <v>8396.765000000001</v>
       </c>
       <c r="G96">
         <v>2369.1</v>
@@ -9165,37 +9165,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M96">
-        <v>2038.733282198517</v>
+        <v>2060.421934136799</v>
       </c>
       <c r="N96">
-        <v>-1525.26661553185</v>
+        <v>-1546.955267470132</v>
       </c>
       <c r="O96">
-        <v>-381.3166538829625</v>
+        <v>-386.738816867533</v>
       </c>
       <c r="P96">
-        <v>-1143.949961648887</v>
+        <v>-1160.216450602599</v>
       </c>
       <c r="Q96">
-        <v>-1051.949961648887</v>
+        <v>-1068.216450602599</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.077406818426289</v>
+        <v>1.283728182111548</v>
       </c>
       <c r="T96">
-        <v>9.976426373112268</v>
+        <v>11.97171164773473</v>
       </c>
       <c r="U96">
         <v>0.2453828270931482</v>
       </c>
       <c r="V96">
-        <v>0.06296393343235139</v>
+        <v>0.06230115518569506</v>
       </c>
       <c r="W96">
-        <v>0.229932559102613</v>
+        <v>0.2300951935025134</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2518557337294056</v>
+        <v>0.2492046207427803</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2827768429329651</v>
+        <v>0.2847726712038965</v>
       </c>
       <c r="C97">
-        <v>-4045.825626192839</v>
+        <v>-4150.764355856164</v>
       </c>
       <c r="D97">
-        <v>1981.839373807162</v>
+        <v>1965.287644143838</v>
       </c>
       <c r="E97">
-        <v>5275.465000000001</v>
+        <v>5363.852000000002</v>
       </c>
       <c r="F97">
-        <v>8396.765000000001</v>
+        <v>8485.152000000002</v>
       </c>
       <c r="G97">
         <v>2369.1</v>
@@ -9247,37 +9247,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M97">
-        <v>2060.421934136799</v>
+        <v>2082.110586075081</v>
       </c>
       <c r="N97">
-        <v>-1546.955267470132</v>
+        <v>-1568.643919408415</v>
       </c>
       <c r="O97">
-        <v>-386.738816867533</v>
+        <v>-392.1609798521037</v>
       </c>
       <c r="P97">
-        <v>-1160.216450602599</v>
+        <v>-1176.482939556311</v>
       </c>
       <c r="Q97">
-        <v>-1068.216450602599</v>
+        <v>-1084.482939556311</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.283728182111548</v>
+        <v>1.593210227639436</v>
       </c>
       <c r="T97">
-        <v>11.97171164773473</v>
+        <v>14.96463955966842</v>
       </c>
       <c r="U97">
         <v>0.2453828270931482</v>
       </c>
       <c r="V97">
-        <v>0.06230115518569506</v>
+        <v>0.06165218481917739</v>
       </c>
       <c r="W97">
-        <v>0.2300951935025134</v>
+        <v>0.2302544396857492</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2492046207427803</v>
+        <v>0.2466087392767096</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2847726712038965</v>
+        <v>0.286768499474828</v>
       </c>
       <c r="C98">
-        <v>-4150.764355856162</v>
+        <v>-4255.428905200758</v>
       </c>
       <c r="D98">
-        <v>1965.287644143838</v>
+        <v>1949.010094799243</v>
       </c>
       <c r="E98">
-        <v>5363.852</v>
+        <v>5452.239</v>
       </c>
       <c r="F98">
-        <v>8485.152</v>
+        <v>8573.539000000001</v>
       </c>
       <c r="G98">
         <v>2369.1</v>
@@ -9329,37 +9329,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M98">
-        <v>2082.110586075081</v>
+        <v>2103.799238013363</v>
       </c>
       <c r="N98">
-        <v>-1568.643919408414</v>
+        <v>-1590.332571346696</v>
       </c>
       <c r="O98">
-        <v>-392.1609798521035</v>
+        <v>-397.583142836674</v>
       </c>
       <c r="P98">
-        <v>-1176.482939556311</v>
+        <v>-1192.749428510022</v>
       </c>
       <c r="Q98">
-        <v>-1084.482939556311</v>
+        <v>-1100.749428510022</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.593210227639431</v>
+        <v>2.109013636852575</v>
       </c>
       <c r="T98">
-        <v>14.96463955966838</v>
+        <v>19.9528527462245</v>
       </c>
       <c r="U98">
         <v>0.2453828270931482</v>
       </c>
       <c r="V98">
-        <v>0.06165218481917741</v>
+        <v>0.06101659528495909</v>
       </c>
       <c r="W98">
-        <v>0.2302544396857492</v>
+        <v>0.2304104024425265</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2466087392767097</v>
+        <v>0.2440663811398364</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.286768499474828</v>
+        <v>0.2887643277457595</v>
       </c>
       <c r="C99">
-        <v>-4255.428905200758</v>
+        <v>-4359.826030981864</v>
       </c>
       <c r="D99">
-        <v>1949.010094799243</v>
+        <v>1932.999969018137</v>
       </c>
       <c r="E99">
-        <v>5452.239</v>
+        <v>5540.626000000001</v>
       </c>
       <c r="F99">
-        <v>8573.539000000001</v>
+        <v>8661.926000000001</v>
       </c>
       <c r="G99">
         <v>2369.1</v>
@@ -9411,37 +9411,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M99">
-        <v>2103.799238013363</v>
+        <v>2125.487889951645</v>
       </c>
       <c r="N99">
-        <v>-1590.332571346696</v>
+        <v>-1612.021223284979</v>
       </c>
       <c r="O99">
-        <v>-397.583142836674</v>
+        <v>-403.0053058212446</v>
       </c>
       <c r="P99">
-        <v>-1192.749428510022</v>
+        <v>-1209.015917463734</v>
       </c>
       <c r="Q99">
-        <v>-1100.749428510022</v>
+        <v>-1117.015917463734</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.109013636852575</v>
+        <v>3.140620455278862</v>
       </c>
       <c r="T99">
-        <v>19.9528527462245</v>
+        <v>29.92927911933675</v>
       </c>
       <c r="U99">
         <v>0.2453828270931482</v>
       </c>
       <c r="V99">
-        <v>0.06101659528495909</v>
+        <v>0.0603939769657248</v>
       </c>
       <c r="W99">
-        <v>0.2304104024425265</v>
+        <v>0.2305631822859002</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2440663811398364</v>
+        <v>0.2415759078628992</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2887643277457595</v>
+        <v>0.290760156016691</v>
       </c>
       <c r="C100">
-        <v>-4359.826030981864</v>
+        <v>-4463.962269750364</v>
       </c>
       <c r="D100">
-        <v>1932.999969018137</v>
+        <v>1917.250730249636</v>
       </c>
       <c r="E100">
-        <v>5540.626000000001</v>
+        <v>5629.013</v>
       </c>
       <c r="F100">
-        <v>8661.926000000001</v>
+        <v>8750.313</v>
       </c>
       <c r="G100">
         <v>2369.1</v>
@@ -9493,37 +9493,37 @@
         <v>513.4666666666667</v>
       </c>
       <c r="M100">
-        <v>2125.487889951645</v>
+        <v>2147.176541889927</v>
       </c>
       <c r="N100">
-        <v>-1612.021223284979</v>
+        <v>-1633.70987522326</v>
       </c>
       <c r="O100">
-        <v>-403.0053058212446</v>
+        <v>-408.4274688058151</v>
       </c>
       <c r="P100">
-        <v>-1209.015917463734</v>
+        <v>-1225.282406417445</v>
       </c>
       <c r="Q100">
-        <v>-1117.015917463734</v>
+        <v>-1133.282406417445</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.140620455278862</v>
+        <v>6.235440910557725</v>
       </c>
       <c r="T100">
-        <v>29.92927911933675</v>
+        <v>59.8585582386735</v>
       </c>
       <c r="U100">
         <v>0.2453828270931482</v>
       </c>
       <c r="V100">
-        <v>0.0603939769657248</v>
+        <v>0.05978393679435385</v>
       </c>
       <c r="W100">
-        <v>0.2305631822859002</v>
+        <v>0.2307128756677916</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2415759078628992</v>
+        <v>0.2391357471774154</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.290760156016691</v>
-      </c>
-      <c r="C101">
-        <v>-4463.962269750364</v>
-      </c>
-      <c r="D101">
-        <v>1917.250730249636</v>
-      </c>
-      <c r="E101">
-        <v>5629.013</v>
-      </c>
-      <c r="F101">
-        <v>8750.313</v>
-      </c>
-      <c r="G101">
-        <v>2369.1</v>
-      </c>
-      <c r="H101">
-        <v>5717.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>605.4666666666667</v>
-      </c>
-      <c r="K101">
-        <v>92</v>
-      </c>
-      <c r="L101">
-        <v>513.4666666666667</v>
-      </c>
-      <c r="M101">
-        <v>2147.176541889927</v>
-      </c>
-      <c r="N101">
-        <v>-1633.70987522326</v>
-      </c>
-      <c r="O101">
-        <v>-408.4274688058151</v>
-      </c>
-      <c r="P101">
-        <v>-1225.282406417445</v>
-      </c>
-      <c r="Q101">
-        <v>-1133.282406417445</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.235440910557725</v>
-      </c>
-      <c r="T101">
-        <v>59.8585582386735</v>
-      </c>
-      <c r="U101">
-        <v>0.2453828270931482</v>
-      </c>
-      <c r="V101">
-        <v>0.05978393679435385</v>
-      </c>
-      <c r="W101">
-        <v>0.2307128756677916</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2391357471774154</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
